--- a/output/census_targets_wide_adults_hispanic.xlsx
+++ b/output/census_targets_wide_adults_hispanic.xlsx
@@ -16855,7 +16855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:MW26"/>
+  <dimension ref="A1:MW27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:361" s="1" customFormat="1">
@@ -39648,1084 +39648,1084 @@
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>28888</v>
+        <v>66320</v>
       </c>
       <c r="C22">
-        <v>69461</v>
+        <v>155940</v>
       </c>
       <c r="D22">
-        <v>69554</v>
+        <v>158302</v>
       </c>
       <c r="E22">
-        <v>64465</v>
+        <v>156210</v>
       </c>
       <c r="F22">
-        <v>64181</v>
+        <v>157891</v>
       </c>
       <c r="G22">
-        <v>59796</v>
+        <v>150571</v>
       </c>
       <c r="H22">
-        <v>54311</v>
+        <v>133157</v>
       </c>
       <c r="I22">
-        <v>46756</v>
+        <v>113376</v>
       </c>
       <c r="J22">
-        <v>41197</v>
+        <v>94032</v>
       </c>
       <c r="K22">
-        <v>32419</v>
+        <v>73795</v>
       </c>
       <c r="L22">
-        <v>22475</v>
+        <v>52004</v>
       </c>
       <c r="M22">
-        <v>14882</v>
+        <v>34177</v>
       </c>
       <c r="N22">
-        <v>9038</v>
+        <v>21311</v>
       </c>
       <c r="O22">
-        <v>5598</v>
+        <v>13300</v>
       </c>
       <c r="P22">
-        <v>5158</v>
+        <v>12205</v>
       </c>
       <c r="Q22">
-        <v>34456</v>
+        <v>34676</v>
       </c>
       <c r="R22">
-        <v>87137</v>
+        <v>78332</v>
       </c>
       <c r="S22">
-        <v>93978</v>
+        <v>77719</v>
       </c>
       <c r="T22">
-        <v>88186</v>
+        <v>79543</v>
       </c>
       <c r="U22">
-        <v>80230</v>
+        <v>76110</v>
       </c>
       <c r="V22">
-        <v>72977</v>
+        <v>70925</v>
       </c>
       <c r="W22">
-        <v>70882</v>
+        <v>69861</v>
       </c>
       <c r="X22">
-        <v>72912</v>
+        <v>71890</v>
       </c>
       <c r="Y22">
-        <v>80709</v>
+        <v>78642</v>
       </c>
       <c r="Z22">
-        <v>76267</v>
+        <v>72635</v>
       </c>
       <c r="AA22">
-        <v>61101</v>
+        <v>57107</v>
       </c>
       <c r="AB22">
-        <v>45523</v>
+        <v>41319</v>
       </c>
       <c r="AC22">
-        <v>28594</v>
+        <v>25656</v>
       </c>
       <c r="AD22">
-        <v>18165</v>
+        <v>16071</v>
       </c>
       <c r="AE22">
-        <v>16320</v>
+        <v>14115</v>
       </c>
       <c r="AF22">
-        <v>30573</v>
+        <v>72902</v>
       </c>
       <c r="AG22">
-        <v>72443</v>
+        <v>174910</v>
       </c>
       <c r="AH22">
-        <v>73786</v>
+        <v>175624</v>
       </c>
       <c r="AI22">
-        <v>77677</v>
+        <v>172973</v>
       </c>
       <c r="AJ22">
-        <v>77400</v>
+        <v>172017</v>
       </c>
       <c r="AK22">
-        <v>70277</v>
+        <v>160617</v>
       </c>
       <c r="AL22">
-        <v>62421</v>
+        <v>140297</v>
       </c>
       <c r="AM22">
-        <v>54302</v>
+        <v>120693</v>
       </c>
       <c r="AN22">
-        <v>45282</v>
+        <v>97852</v>
       </c>
       <c r="AO22">
-        <v>34677</v>
+        <v>73672</v>
       </c>
       <c r="AP22">
-        <v>22486</v>
+        <v>48923</v>
       </c>
       <c r="AQ22">
-        <v>14226</v>
+        <v>30031</v>
       </c>
       <c r="AR22">
-        <v>7641</v>
+        <v>16616</v>
       </c>
       <c r="AS22">
-        <v>4286</v>
+        <v>9395</v>
       </c>
       <c r="AT22">
-        <v>3106</v>
+        <v>7316</v>
       </c>
       <c r="AU22">
-        <v>35484</v>
+        <v>35327</v>
       </c>
       <c r="AV22">
-        <v>88116</v>
+        <v>80903</v>
       </c>
       <c r="AW22">
-        <v>95675</v>
+        <v>79370</v>
       </c>
       <c r="AX22">
-        <v>89019</v>
+        <v>79078</v>
       </c>
       <c r="AY22">
-        <v>78991</v>
+        <v>73751</v>
       </c>
       <c r="AZ22">
-        <v>72011</v>
+        <v>68901</v>
       </c>
       <c r="BA22">
-        <v>69183</v>
+        <v>67410</v>
       </c>
       <c r="BB22">
-        <v>70008</v>
+        <v>67779</v>
       </c>
       <c r="BC22">
-        <v>74856</v>
+        <v>72359</v>
       </c>
       <c r="BD22">
-        <v>67666</v>
+        <v>64933</v>
       </c>
       <c r="BE22">
-        <v>52863</v>
+        <v>49560</v>
       </c>
       <c r="BF22">
-        <v>39842</v>
+        <v>35642</v>
       </c>
       <c r="BG22">
-        <v>23929</v>
+        <v>20654</v>
       </c>
       <c r="BH22">
-        <v>13883</v>
+        <v>11509</v>
       </c>
       <c r="BI22">
-        <v>9978</v>
+        <v>8025</v>
       </c>
       <c r="BJ22">
-        <v>10007</v>
+        <v>14781</v>
       </c>
       <c r="BK22">
-        <v>24027</v>
+        <v>35817</v>
       </c>
       <c r="BL22">
-        <v>24524</v>
+        <v>33952</v>
       </c>
       <c r="BM22">
-        <v>24473</v>
+        <v>31610</v>
       </c>
       <c r="BN22">
-        <v>22603</v>
+        <v>28686</v>
       </c>
       <c r="BO22">
-        <v>21414</v>
+        <v>26082</v>
       </c>
       <c r="BP22">
-        <v>18803</v>
+        <v>23016</v>
       </c>
       <c r="BQ22">
-        <v>16221</v>
+        <v>19720</v>
       </c>
       <c r="BR22">
-        <v>13890</v>
+        <v>16016</v>
       </c>
       <c r="BS22">
-        <v>11091</v>
+        <v>12481</v>
       </c>
       <c r="BT22">
-        <v>8129</v>
+        <v>8922</v>
       </c>
       <c r="BU22">
-        <v>5751</v>
+        <v>6364</v>
       </c>
       <c r="BV22">
-        <v>3590</v>
+        <v>3916</v>
       </c>
       <c r="BW22">
-        <v>2345</v>
+        <v>2520</v>
       </c>
       <c r="BX22">
-        <v>2111</v>
+        <v>2493</v>
       </c>
       <c r="BY22">
-        <v>230522</v>
+        <v>266034</v>
       </c>
       <c r="BZ22">
-        <v>611598</v>
+        <v>715178</v>
       </c>
       <c r="CA22">
-        <v>757642</v>
+        <v>784653</v>
       </c>
       <c r="CB22">
-        <v>869265</v>
+        <v>867540</v>
       </c>
       <c r="CC22">
-        <v>866404</v>
+        <v>863796</v>
       </c>
       <c r="CD22">
-        <v>792292</v>
+        <v>792971</v>
       </c>
       <c r="CE22">
-        <v>764927</v>
+        <v>786368</v>
       </c>
       <c r="CF22">
-        <v>670172</v>
+        <v>701467</v>
       </c>
       <c r="CG22">
-        <v>614213</v>
+        <v>634149</v>
       </c>
       <c r="CH22">
-        <v>562475</v>
+        <v>579540</v>
       </c>
       <c r="CI22">
-        <v>487901</v>
+        <v>494624</v>
       </c>
       <c r="CJ22">
-        <v>385495</v>
+        <v>387534</v>
       </c>
       <c r="CK22">
-        <v>243113</v>
+        <v>243472</v>
       </c>
       <c r="CL22">
-        <v>161968</v>
+        <v>160372</v>
       </c>
       <c r="CM22">
-        <v>174105</v>
+        <v>164367</v>
       </c>
       <c r="CN22">
-        <v>10560</v>
+        <v>15086</v>
       </c>
       <c r="CO22">
-        <v>24683</v>
+        <v>35556</v>
       </c>
       <c r="CP22">
-        <v>23789</v>
+        <v>33430</v>
       </c>
       <c r="CQ22">
-        <v>24469</v>
+        <v>30938</v>
       </c>
       <c r="CR22">
-        <v>23680</v>
+        <v>28229</v>
       </c>
       <c r="CS22">
-        <v>21515</v>
+        <v>24676</v>
       </c>
       <c r="CT22">
-        <v>18598</v>
+        <v>21630</v>
       </c>
       <c r="CU22">
-        <v>15859</v>
+        <v>18172</v>
       </c>
       <c r="CV22">
-        <v>13186</v>
+        <v>14417</v>
       </c>
       <c r="CW22">
-        <v>10258</v>
+        <v>11036</v>
       </c>
       <c r="CX22">
-        <v>6919</v>
+        <v>7374</v>
       </c>
       <c r="CY22">
-        <v>4512</v>
+        <v>4980</v>
       </c>
       <c r="CZ22">
-        <v>2601</v>
+        <v>2756</v>
       </c>
       <c r="DA22">
-        <v>1598</v>
+        <v>1680</v>
       </c>
       <c r="DB22">
-        <v>1145</v>
+        <v>1363</v>
       </c>
       <c r="DC22">
-        <v>232843</v>
+        <v>264820</v>
       </c>
       <c r="DD22">
-        <v>614765</v>
+        <v>723564</v>
       </c>
       <c r="DE22">
-        <v>740859</v>
+        <v>772040</v>
       </c>
       <c r="DF22">
-        <v>816161</v>
+        <v>790855</v>
       </c>
       <c r="DG22">
-        <v>792751</v>
+        <v>759452</v>
       </c>
       <c r="DH22">
-        <v>699843</v>
+        <v>676754</v>
       </c>
       <c r="DI22">
-        <v>684958</v>
+        <v>676445</v>
       </c>
       <c r="DJ22">
-        <v>595738</v>
+        <v>600695</v>
       </c>
       <c r="DK22">
-        <v>537625</v>
+        <v>540498</v>
       </c>
       <c r="DL22">
-        <v>474442</v>
+        <v>475225</v>
       </c>
       <c r="DM22">
-        <v>390977</v>
+        <v>392612</v>
       </c>
       <c r="DN22">
-        <v>304956</v>
+        <v>299958</v>
       </c>
       <c r="DO22">
-        <v>193174</v>
+        <v>190012</v>
       </c>
       <c r="DP22">
-        <v>125190</v>
+        <v>122281</v>
       </c>
       <c r="DQ22">
-        <v>105151</v>
+        <v>96634</v>
       </c>
       <c r="DR22">
-        <v>50744</v>
+        <v>68002</v>
       </c>
       <c r="DS22">
-        <v>118813</v>
+        <v>157773</v>
       </c>
       <c r="DT22">
-        <v>122123</v>
+        <v>156669</v>
       </c>
       <c r="DU22">
-        <v>123626</v>
+        <v>148850</v>
       </c>
       <c r="DV22">
-        <v>117844</v>
+        <v>133900</v>
       </c>
       <c r="DW22">
-        <v>108906</v>
+        <v>117971</v>
       </c>
       <c r="DX22">
-        <v>91543</v>
+        <v>98982</v>
       </c>
       <c r="DY22">
-        <v>78957</v>
+        <v>85579</v>
       </c>
       <c r="DZ22">
-        <v>69032</v>
+        <v>73003</v>
       </c>
       <c r="EA22">
-        <v>55448</v>
+        <v>57013</v>
       </c>
       <c r="EB22">
-        <v>40290</v>
+        <v>42057</v>
       </c>
       <c r="EC22">
-        <v>29176</v>
+        <v>30015</v>
       </c>
       <c r="ED22">
-        <v>18247</v>
+        <v>18993</v>
       </c>
       <c r="EE22">
-        <v>12364</v>
+        <v>12696</v>
       </c>
       <c r="EF22">
-        <v>11382</v>
+        <v>12943</v>
       </c>
       <c r="EG22">
-        <v>584051</v>
+        <v>615391</v>
       </c>
       <c r="EH22">
-        <v>1483711</v>
+        <v>1480146</v>
       </c>
       <c r="EI22">
-        <v>1669626</v>
+        <v>1524177</v>
       </c>
       <c r="EJ22">
-        <v>1603008</v>
+        <v>1526835</v>
       </c>
       <c r="EK22">
-        <v>1463882</v>
+        <v>1437457</v>
       </c>
       <c r="EL22">
-        <v>1385301</v>
+        <v>1356072</v>
       </c>
       <c r="EM22">
-        <v>1351750</v>
+        <v>1317102</v>
       </c>
       <c r="EN22">
-        <v>1353647</v>
+        <v>1339060</v>
       </c>
       <c r="EO22">
-        <v>1409774</v>
+        <v>1406611</v>
       </c>
       <c r="EP22">
-        <v>1307475</v>
+        <v>1320662</v>
       </c>
       <c r="EQ22">
-        <v>1057806</v>
+        <v>1074768</v>
       </c>
       <c r="ER22">
-        <v>784056</v>
+        <v>789015</v>
       </c>
       <c r="ES22">
-        <v>499710</v>
+        <v>501041</v>
       </c>
       <c r="ET22">
-        <v>329047</v>
+        <v>325637</v>
       </c>
       <c r="EU22">
-        <v>328400</v>
+        <v>328210</v>
       </c>
       <c r="EV22">
-        <v>53174</v>
+        <v>70908</v>
       </c>
       <c r="EW22">
-        <v>122643</v>
+        <v>163625</v>
       </c>
       <c r="EX22">
-        <v>125312</v>
+        <v>154275</v>
       </c>
       <c r="EY22">
-        <v>122049</v>
+        <v>141763</v>
       </c>
       <c r="EZ22">
-        <v>110986</v>
+        <v>124878</v>
       </c>
       <c r="FA22">
-        <v>99016</v>
+        <v>107467</v>
       </c>
       <c r="FB22">
-        <v>80460</v>
+        <v>89565</v>
       </c>
       <c r="FC22">
-        <v>71436</v>
+        <v>77886</v>
       </c>
       <c r="FD22">
-        <v>61753</v>
+        <v>64993</v>
       </c>
       <c r="FE22">
-        <v>48352</v>
+        <v>50071</v>
       </c>
       <c r="FF22">
-        <v>34260</v>
+        <v>35714</v>
       </c>
       <c r="FG22">
-        <v>22749</v>
+        <v>23195</v>
       </c>
       <c r="FH22">
-        <v>13332</v>
+        <v>13660</v>
       </c>
       <c r="FI22">
-        <v>8261</v>
+        <v>8216</v>
       </c>
       <c r="FJ22">
-        <v>5892</v>
+        <v>6385</v>
       </c>
       <c r="FK22">
-        <v>589209</v>
+        <v>616339</v>
       </c>
       <c r="FL22">
-        <v>1475003</v>
+        <v>1449070</v>
       </c>
       <c r="FM22">
-        <v>1658001</v>
+        <v>1427833</v>
       </c>
       <c r="FN22">
-        <v>1532950</v>
+        <v>1378537</v>
       </c>
       <c r="FO22">
-        <v>1355903</v>
+        <v>1276313</v>
       </c>
       <c r="FP22">
-        <v>1250407</v>
+        <v>1199222</v>
       </c>
       <c r="FQ22">
-        <v>1209149</v>
+        <v>1166603</v>
       </c>
       <c r="FR22">
-        <v>1215284</v>
+        <v>1181840</v>
       </c>
       <c r="FS22">
-        <v>1241983</v>
+        <v>1220254</v>
       </c>
       <c r="FT22">
-        <v>1114021</v>
+        <v>1111953</v>
       </c>
       <c r="FU22">
-        <v>831542</v>
+        <v>851947</v>
       </c>
       <c r="FV22">
-        <v>578040</v>
+        <v>585417</v>
       </c>
       <c r="FW22">
-        <v>335126</v>
+        <v>337821</v>
       </c>
       <c r="FX22">
-        <v>195293</v>
+        <v>194001</v>
       </c>
       <c r="FY22">
-        <v>143830</v>
+        <v>146026</v>
       </c>
       <c r="FZ22">
-        <v>3576</v>
+        <v>4252</v>
       </c>
       <c r="GA22">
-        <v>8084</v>
+        <v>9883</v>
       </c>
       <c r="GB22">
-        <v>8616</v>
+        <v>9395</v>
       </c>
       <c r="GC22">
-        <v>8579</v>
+        <v>8681</v>
       </c>
       <c r="GD22">
-        <v>8452</v>
+        <v>8208</v>
       </c>
       <c r="GE22">
-        <v>7589</v>
+        <v>7508</v>
       </c>
       <c r="GF22">
-        <v>6324</v>
+        <v>6331</v>
       </c>
       <c r="GG22">
-        <v>5593</v>
+        <v>5496</v>
       </c>
       <c r="GH22">
-        <v>4656</v>
+        <v>4662</v>
       </c>
       <c r="GI22">
-        <v>3422</v>
+        <v>3418</v>
       </c>
       <c r="GJ22">
-        <v>2415</v>
+        <v>2434</v>
       </c>
       <c r="GK22">
-        <v>1569</v>
+        <v>1552</v>
       </c>
       <c r="GL22">
-        <v>954</v>
+        <v>1026</v>
       </c>
       <c r="GM22">
-        <v>709</v>
+        <v>650</v>
       </c>
       <c r="GN22">
-        <v>531</v>
+        <v>609</v>
       </c>
       <c r="GO22">
-        <v>8091</v>
+        <v>10403</v>
       </c>
       <c r="GP22">
-        <v>20251</v>
+        <v>26203</v>
       </c>
       <c r="GQ22">
-        <v>23927</v>
+        <v>26140</v>
       </c>
       <c r="GR22">
-        <v>25804</v>
+        <v>25502</v>
       </c>
       <c r="GS22">
-        <v>24492</v>
+        <v>23891</v>
       </c>
       <c r="GT22">
-        <v>21350</v>
+        <v>21136</v>
       </c>
       <c r="GU22">
-        <v>18630</v>
+        <v>18895</v>
       </c>
       <c r="GV22">
-        <v>18174</v>
+        <v>18166</v>
       </c>
       <c r="GW22">
-        <v>17969</v>
+        <v>17627</v>
       </c>
       <c r="GX22">
-        <v>15426</v>
+        <v>14955</v>
       </c>
       <c r="GY22">
-        <v>12250</v>
+        <v>11656</v>
       </c>
       <c r="GZ22">
-        <v>9164</v>
+        <v>8068</v>
       </c>
       <c r="HA22">
-        <v>5558</v>
+        <v>4984</v>
       </c>
       <c r="HB22">
-        <v>3535</v>
+        <v>3042</v>
       </c>
       <c r="HC22">
-        <v>3387</v>
+        <v>3032</v>
       </c>
       <c r="HD22">
-        <v>3461</v>
+        <v>4312</v>
       </c>
       <c r="HE22">
-        <v>8510</v>
+        <v>10411</v>
       </c>
       <c r="HF22">
-        <v>9190</v>
+        <v>9500</v>
       </c>
       <c r="HG22">
-        <v>10661</v>
+        <v>8783</v>
       </c>
       <c r="HH22">
-        <v>10583</v>
+        <v>8088</v>
       </c>
       <c r="HI22">
-        <v>9175</v>
+        <v>7215</v>
       </c>
       <c r="HJ22">
-        <v>6975</v>
+        <v>5977</v>
       </c>
       <c r="HK22">
-        <v>5926</v>
+        <v>5267</v>
       </c>
       <c r="HL22">
-        <v>4664</v>
+        <v>4288</v>
       </c>
       <c r="HM22">
-        <v>3441</v>
+        <v>3083</v>
       </c>
       <c r="HN22">
-        <v>2074</v>
+        <v>2020</v>
       </c>
       <c r="HO22">
-        <v>1474</v>
+        <v>1322</v>
       </c>
       <c r="HP22">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="HQ22">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="HR22">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="HS22">
-        <v>8275</v>
+        <v>10386</v>
       </c>
       <c r="HT22">
-        <v>20773</v>
+        <v>27019</v>
       </c>
       <c r="HU22">
-        <v>23960</v>
+        <v>26977</v>
       </c>
       <c r="HV22">
-        <v>26933</v>
+        <v>26124</v>
       </c>
       <c r="HW22">
-        <v>25875</v>
+        <v>23963</v>
       </c>
       <c r="HX22">
-        <v>21921</v>
+        <v>21177</v>
       </c>
       <c r="HY22">
-        <v>19542</v>
+        <v>18681</v>
       </c>
       <c r="HZ22">
-        <v>18144</v>
+        <v>17478</v>
       </c>
       <c r="IA22">
-        <v>17513</v>
+        <v>16283</v>
       </c>
       <c r="IB22">
-        <v>15120</v>
+        <v>13832</v>
       </c>
       <c r="IC22">
-        <v>11286</v>
+        <v>10261</v>
       </c>
       <c r="ID22">
-        <v>8615</v>
+        <v>7256</v>
       </c>
       <c r="IE22">
-        <v>5002</v>
+        <v>4142</v>
       </c>
       <c r="IF22">
-        <v>2825</v>
+        <v>2123</v>
       </c>
       <c r="IG22">
-        <v>2267</v>
+        <v>1691</v>
       </c>
       <c r="IH22">
-        <v>36510</v>
+        <v>70104</v>
       </c>
       <c r="II22">
-        <v>83082</v>
+        <v>151326</v>
       </c>
       <c r="IJ22">
-        <v>74966</v>
+        <v>139647</v>
       </c>
       <c r="IK22">
-        <v>65340</v>
+        <v>126200</v>
       </c>
       <c r="IL22">
-        <v>60586</v>
+        <v>113726</v>
       </c>
       <c r="IM22">
-        <v>54761</v>
+        <v>98981</v>
       </c>
       <c r="IN22">
-        <v>42732</v>
+        <v>81725</v>
       </c>
       <c r="IO22">
-        <v>35235</v>
+        <v>68963</v>
       </c>
       <c r="IP22">
-        <v>30814</v>
+        <v>57043</v>
       </c>
       <c r="IQ22">
-        <v>24525</v>
+        <v>44787</v>
       </c>
       <c r="IR22">
-        <v>17261</v>
+        <v>32274</v>
       </c>
       <c r="IS22">
-        <v>11855</v>
+        <v>22293</v>
       </c>
       <c r="IT22">
-        <v>7383</v>
+        <v>13423</v>
       </c>
       <c r="IU22">
-        <v>4669</v>
+        <v>8219</v>
       </c>
       <c r="IV22">
+        <v>7478</v>
+      </c>
+      <c r="IW22">
+        <v>202263</v>
+      </c>
+      <c r="IX22">
+        <v>451226</v>
+      </c>
+      <c r="IY22">
+        <v>411351</v>
+      </c>
+      <c r="IZ22">
+        <v>376869</v>
+      </c>
+      <c r="JA22">
+        <v>336746</v>
+      </c>
+      <c r="JB22">
+        <v>296437</v>
+      </c>
+      <c r="JC22">
+        <v>271219</v>
+      </c>
+      <c r="JD22">
+        <v>255865</v>
+      </c>
+      <c r="JE22">
+        <v>254015</v>
+      </c>
+      <c r="JF22">
+        <v>223176</v>
+      </c>
+      <c r="JG22">
+        <v>168664</v>
+      </c>
+      <c r="JH22">
+        <v>122631</v>
+      </c>
+      <c r="JI22">
+        <v>73803</v>
+      </c>
+      <c r="JJ22">
+        <v>43431</v>
+      </c>
+      <c r="JK22">
+        <v>38936</v>
+      </c>
+      <c r="JL22">
+        <v>72438</v>
+      </c>
+      <c r="JM22">
+        <v>153803</v>
+      </c>
+      <c r="JN22">
+        <v>136477</v>
+      </c>
+      <c r="JO22">
+        <v>119277</v>
+      </c>
+      <c r="JP22">
+        <v>106393</v>
+      </c>
+      <c r="JQ22">
+        <v>91125</v>
+      </c>
+      <c r="JR22">
+        <v>75154</v>
+      </c>
+      <c r="JS22">
+        <v>61954</v>
+      </c>
+      <c r="JT22">
+        <v>50045</v>
+      </c>
+      <c r="JU22">
+        <v>37898</v>
+      </c>
+      <c r="JV22">
+        <v>26137</v>
+      </c>
+      <c r="JW22">
+        <v>16677</v>
+      </c>
+      <c r="JX22">
+        <v>9641</v>
+      </c>
+      <c r="JY22">
+        <v>5308</v>
+      </c>
+      <c r="JZ22">
         <v>4199</v>
       </c>
-      <c r="IW22">
-        <v>148393</v>
-      </c>
-      <c r="IX22">
-        <v>338662</v>
-      </c>
-      <c r="IY22">
-        <v>299878</v>
-      </c>
-      <c r="IZ22">
-        <v>241750</v>
-      </c>
-      <c r="JA22">
-        <v>204339</v>
-      </c>
-      <c r="JB22">
-        <v>173161</v>
-      </c>
-      <c r="JC22">
-        <v>147772</v>
-      </c>
-      <c r="JD22">
-        <v>129926</v>
-      </c>
-      <c r="JE22">
-        <v>125395</v>
-      </c>
-      <c r="JF22">
-        <v>111558</v>
-      </c>
-      <c r="JG22">
-        <v>86865</v>
-      </c>
-      <c r="JH22">
-        <v>65056</v>
-      </c>
-      <c r="JI22">
-        <v>42147</v>
-      </c>
-      <c r="JJ22">
-        <v>26499</v>
-      </c>
-      <c r="JK22">
-        <v>27044</v>
-      </c>
-      <c r="JL22">
-        <v>37962</v>
-      </c>
-      <c r="JM22">
-        <v>85530</v>
-      </c>
-      <c r="JN22">
-        <v>76696</v>
-      </c>
-      <c r="JO22">
-        <v>65663</v>
-      </c>
-      <c r="JP22">
-        <v>60333</v>
-      </c>
-      <c r="JQ22">
-        <v>53992</v>
-      </c>
-      <c r="JR22">
-        <v>40436</v>
-      </c>
-      <c r="JS22">
-        <v>33946</v>
-      </c>
-      <c r="JT22">
-        <v>28223</v>
-      </c>
-      <c r="JU22">
-        <v>21811</v>
-      </c>
-      <c r="JV22">
-        <v>14379</v>
-      </c>
-      <c r="JW22">
-        <v>9358</v>
-      </c>
-      <c r="JX22">
-        <v>5344</v>
-      </c>
-      <c r="JY22">
-        <v>3118</v>
-      </c>
-      <c r="JZ22">
-        <v>2268</v>
-      </c>
       <c r="KA22">
-        <v>150811</v>
+        <v>202360</v>
       </c>
       <c r="KB22">
-        <v>339188</v>
+        <v>433821</v>
       </c>
       <c r="KC22">
-        <v>290215</v>
+        <v>377058</v>
       </c>
       <c r="KD22">
-        <v>220638</v>
+        <v>335833</v>
       </c>
       <c r="KE22">
-        <v>182048</v>
+        <v>295641</v>
       </c>
       <c r="KF22">
-        <v>153277</v>
+        <v>259969</v>
       </c>
       <c r="KG22">
-        <v>131965</v>
+        <v>238516</v>
       </c>
       <c r="KH22">
-        <v>117566</v>
+        <v>222366</v>
       </c>
       <c r="KI22">
-        <v>112747</v>
+        <v>216219</v>
       </c>
       <c r="KJ22">
-        <v>101061</v>
+        <v>188342</v>
       </c>
       <c r="KK22">
-        <v>77188</v>
+        <v>137612</v>
       </c>
       <c r="KL22">
-        <v>56240</v>
+        <v>96720</v>
       </c>
       <c r="KM22">
-        <v>34288</v>
+        <v>55142</v>
       </c>
       <c r="KN22">
-        <v>20377</v>
+        <v>30675</v>
       </c>
       <c r="KO22">
-        <v>16210</v>
+        <v>22004</v>
       </c>
       <c r="KP22">
-        <v>874336</v>
+        <v>851749</v>
       </c>
       <c r="KQ22">
-        <v>2079967</v>
+        <v>1993408</v>
       </c>
       <c r="KR22">
-        <v>2074645</v>
+        <v>1927288</v>
       </c>
       <c r="KS22">
-        <v>1945247</v>
+        <v>1840079</v>
       </c>
       <c r="KT22">
-        <v>1927093</v>
+        <v>1793285</v>
       </c>
       <c r="KU22">
-        <v>1840399</v>
+        <v>1715472</v>
       </c>
       <c r="KV22">
-        <v>1726409</v>
+        <v>1610064</v>
       </c>
       <c r="KW22">
-        <v>1517774</v>
+        <v>1449074</v>
       </c>
       <c r="KX22">
-        <v>1338678</v>
+        <v>1291514</v>
       </c>
       <c r="KY22">
-        <v>1083646</v>
+        <v>1061699</v>
       </c>
       <c r="KZ22">
-        <v>834331</v>
+        <v>824179</v>
       </c>
       <c r="LA22">
-        <v>620085</v>
+        <v>617829</v>
       </c>
       <c r="LB22">
-        <v>416045</v>
+        <v>418655</v>
       </c>
       <c r="LC22">
-        <v>284283</v>
+        <v>285321</v>
       </c>
       <c r="LD22">
-        <v>285043</v>
+        <v>289986</v>
       </c>
       <c r="LE22">
-        <v>2192452</v>
+        <v>2228904</v>
       </c>
       <c r="LF22">
-        <v>5542437</v>
+        <v>5611596</v>
       </c>
       <c r="LG22">
-        <v>5958601</v>
+        <v>5730466</v>
       </c>
       <c r="LH22">
-        <v>6215025</v>
+        <v>6054014</v>
       </c>
       <c r="LI22">
-        <v>6146267</v>
+        <v>6003176</v>
       </c>
       <c r="LJ22">
-        <v>5755181</v>
+        <v>5618544</v>
       </c>
       <c r="LK22">
-        <v>5862998</v>
+        <v>5731469</v>
       </c>
       <c r="LL22">
-        <v>6463650</v>
+        <v>6363398</v>
       </c>
       <c r="LM22">
-        <v>7427521</v>
+        <v>7372598</v>
       </c>
       <c r="LN22">
-        <v>7518148</v>
+        <v>7574872</v>
       </c>
       <c r="LO22">
-        <v>6811801</v>
+        <v>6915265</v>
       </c>
       <c r="LP22">
-        <v>5794050</v>
+        <v>5925507</v>
       </c>
       <c r="LQ22">
-        <v>4027816</v>
+        <v>4177655</v>
       </c>
       <c r="LR22">
-        <v>2681242</v>
+        <v>2795775</v>
       </c>
       <c r="LS22">
-        <v>3029715</v>
+        <v>3157697</v>
       </c>
       <c r="LT22">
-        <v>905146</v>
+        <v>881485</v>
       </c>
       <c r="LU22">
-        <v>2138955</v>
+        <v>2066463</v>
       </c>
       <c r="LV22">
-        <v>2172086</v>
+        <v>1976640</v>
       </c>
       <c r="LW22">
-        <v>2142352</v>
+        <v>1873093</v>
       </c>
       <c r="LX22">
-        <v>2124096</v>
+        <v>1793756</v>
       </c>
       <c r="LY22">
-        <v>1976726</v>
+        <v>1682619</v>
       </c>
       <c r="LZ22">
-        <v>1799481</v>
+        <v>1547461</v>
       </c>
       <c r="MA22">
-        <v>1589541</v>
+        <v>1409287</v>
       </c>
       <c r="MB22">
-        <v>1351188</v>
+        <v>1227861</v>
       </c>
       <c r="MC22">
-        <v>1040830</v>
+        <v>966491</v>
       </c>
       <c r="MD22">
-        <v>743403</v>
+        <v>706970</v>
       </c>
       <c r="ME22">
-        <v>517416</v>
+        <v>498194</v>
       </c>
       <c r="MF22">
-        <v>313880</v>
+        <v>309709</v>
       </c>
       <c r="MG22">
-        <v>197197</v>
+        <v>193217</v>
       </c>
       <c r="MH22">
-        <v>162509</v>
+        <v>162587</v>
       </c>
       <c r="MI22">
-        <v>2281070</v>
+        <v>2273010</v>
       </c>
       <c r="MJ22">
-        <v>5672672</v>
+        <v>5675478</v>
       </c>
       <c r="MK22">
-        <v>6080362</v>
+        <v>5821627</v>
       </c>
       <c r="ML22">
-        <v>6297003</v>
+        <v>6126039</v>
       </c>
       <c r="MM22">
-        <v>6270114</v>
+        <v>6064981</v>
       </c>
       <c r="MN22">
-        <v>5882671</v>
+        <v>5672450</v>
       </c>
       <c r="MO22">
-        <v>6010831</v>
+        <v>5772391</v>
       </c>
       <c r="MP22">
-        <v>6574116</v>
+        <v>6326046</v>
       </c>
       <c r="MQ22">
-        <v>7364297</v>
+        <v>7169397</v>
       </c>
       <c r="MR22">
-        <v>7293154</v>
+        <v>7198665</v>
       </c>
       <c r="MS22">
-        <v>6366514</v>
+        <v>6387286</v>
       </c>
       <c r="MT22">
-        <v>5249922</v>
+        <v>5314808</v>
       </c>
       <c r="MU22">
-        <v>3423610</v>
+        <v>3533152</v>
       </c>
       <c r="MV22">
-        <v>2057410</v>
+        <v>2145401</v>
       </c>
       <c r="MW22">
-        <v>1727787</v>
+        <v>1829193</v>
       </c>
     </row>
     <row r="23" spans="1:361">
@@ -40733,1084 +40733,1084 @@
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>29640</v>
+        <v>67344</v>
       </c>
       <c r="C23">
-        <v>70652</v>
+        <v>158295</v>
       </c>
       <c r="D23">
-        <v>69781</v>
+        <v>157296</v>
       </c>
       <c r="E23">
-        <v>65609</v>
+        <v>157266</v>
       </c>
       <c r="F23">
-        <v>64399</v>
+        <v>157513</v>
       </c>
       <c r="G23">
-        <v>61092</v>
+        <v>153594</v>
       </c>
       <c r="H23">
-        <v>54716</v>
+        <v>135700</v>
       </c>
       <c r="I23">
-        <v>48645</v>
+        <v>117447</v>
       </c>
       <c r="J23">
-        <v>42304</v>
+        <v>97817</v>
       </c>
       <c r="K23">
-        <v>33934</v>
+        <v>77512</v>
       </c>
       <c r="L23">
-        <v>23949</v>
+        <v>55180</v>
       </c>
       <c r="M23">
-        <v>16213</v>
+        <v>37006</v>
       </c>
       <c r="N23">
-        <v>9726</v>
+        <v>22856</v>
       </c>
       <c r="O23">
-        <v>5795</v>
+        <v>13958</v>
       </c>
       <c r="P23">
-        <v>5331</v>
+        <v>12656</v>
       </c>
       <c r="Q23">
-        <v>34021</v>
+        <v>33596</v>
       </c>
       <c r="R23">
-        <v>87374</v>
+        <v>81489</v>
       </c>
       <c r="S23">
-        <v>91662</v>
+        <v>75764</v>
       </c>
       <c r="T23">
-        <v>90761</v>
+        <v>80307</v>
       </c>
       <c r="U23">
-        <v>80867</v>
+        <v>76502</v>
       </c>
       <c r="V23">
-        <v>74788</v>
+        <v>72342</v>
       </c>
       <c r="W23">
-        <v>69306</v>
+        <v>68271</v>
       </c>
       <c r="X23">
-        <v>72464</v>
+        <v>71626</v>
       </c>
       <c r="Y23">
-        <v>78544</v>
+        <v>77189</v>
       </c>
       <c r="Z23">
-        <v>77398</v>
+        <v>74224</v>
       </c>
       <c r="AA23">
-        <v>63791</v>
+        <v>60009</v>
       </c>
       <c r="AB23">
-        <v>48574</v>
+        <v>44495</v>
       </c>
       <c r="AC23">
-        <v>30048</v>
+        <v>27248</v>
       </c>
       <c r="AD23">
-        <v>19244</v>
+        <v>17265</v>
       </c>
       <c r="AE23">
-        <v>17703</v>
+        <v>15611</v>
       </c>
       <c r="AF23">
-        <v>31408</v>
+        <v>73016</v>
       </c>
       <c r="AG23">
-        <v>73608</v>
+        <v>176793</v>
       </c>
       <c r="AH23">
-        <v>72859</v>
+        <v>174884</v>
       </c>
       <c r="AI23">
-        <v>77532</v>
+        <v>173671</v>
       </c>
       <c r="AJ23">
-        <v>77855</v>
+        <v>172255</v>
       </c>
       <c r="AK23">
-        <v>72100</v>
+        <v>163959</v>
       </c>
       <c r="AL23">
-        <v>63294</v>
+        <v>143274</v>
       </c>
       <c r="AM23">
-        <v>55833</v>
+        <v>124359</v>
       </c>
       <c r="AN23">
-        <v>46732</v>
+        <v>101679</v>
       </c>
       <c r="AO23">
-        <v>36103</v>
+        <v>76935</v>
       </c>
       <c r="AP23">
-        <v>24441</v>
+        <v>52601</v>
       </c>
       <c r="AQ23">
-        <v>15240</v>
+        <v>32595</v>
       </c>
       <c r="AR23">
-        <v>8267</v>
+        <v>17844</v>
       </c>
       <c r="AS23">
-        <v>4494</v>
+        <v>9821</v>
       </c>
       <c r="AT23">
-        <v>3202</v>
+        <v>7450</v>
       </c>
       <c r="AU23">
-        <v>35021</v>
+        <v>35047</v>
       </c>
       <c r="AV23">
-        <v>88204</v>
+        <v>83443</v>
       </c>
       <c r="AW23">
-        <v>93314</v>
+        <v>77787</v>
       </c>
       <c r="AX23">
-        <v>92043</v>
+        <v>80429</v>
       </c>
       <c r="AY23">
-        <v>79928</v>
+        <v>74149</v>
       </c>
       <c r="AZ23">
-        <v>73183</v>
+        <v>70057</v>
       </c>
       <c r="BA23">
-        <v>67557</v>
+        <v>65994</v>
       </c>
       <c r="BB23">
-        <v>69948</v>
+        <v>67667</v>
       </c>
       <c r="BC23">
-        <v>73299</v>
+        <v>71386</v>
       </c>
       <c r="BD23">
-        <v>68904</v>
+        <v>66529</v>
       </c>
       <c r="BE23">
-        <v>54553</v>
+        <v>51849</v>
       </c>
       <c r="BF23">
-        <v>42284</v>
+        <v>38293</v>
       </c>
       <c r="BG23">
-        <v>25015</v>
+        <v>21873</v>
       </c>
       <c r="BH23">
-        <v>14866</v>
+        <v>12608</v>
       </c>
       <c r="BI23">
-        <v>11060</v>
+        <v>9040</v>
       </c>
       <c r="BJ23">
-        <v>10416</v>
+        <v>14609</v>
       </c>
       <c r="BK23">
-        <v>24267</v>
+        <v>36401</v>
       </c>
       <c r="BL23">
-        <v>24057</v>
+        <v>34017</v>
       </c>
       <c r="BM23">
-        <v>25235</v>
+        <v>32616</v>
       </c>
       <c r="BN23">
-        <v>22691</v>
+        <v>29142</v>
       </c>
       <c r="BO23">
-        <v>21799</v>
+        <v>26717</v>
       </c>
       <c r="BP23">
-        <v>19298</v>
+        <v>23516</v>
       </c>
       <c r="BQ23">
-        <v>16728</v>
+        <v>20468</v>
       </c>
       <c r="BR23">
-        <v>14297</v>
+        <v>16691</v>
       </c>
       <c r="BS23">
-        <v>11518</v>
+        <v>12983</v>
       </c>
       <c r="BT23">
-        <v>8627</v>
+        <v>9559</v>
       </c>
       <c r="BU23">
-        <v>6207</v>
+        <v>6742</v>
       </c>
       <c r="BV23">
-        <v>3823</v>
+        <v>4230</v>
       </c>
       <c r="BW23">
-        <v>2443</v>
+        <v>2619</v>
       </c>
       <c r="BX23">
-        <v>2180</v>
+        <v>2565</v>
       </c>
       <c r="BY23">
-        <v>229924</v>
+        <v>244272</v>
       </c>
       <c r="BZ23">
-        <v>607386</v>
+        <v>721489</v>
       </c>
       <c r="CA23">
-        <v>736220</v>
+        <v>775527</v>
       </c>
       <c r="CB23">
-        <v>873451</v>
+        <v>872972</v>
       </c>
       <c r="CC23">
-        <v>877254</v>
+        <v>874312</v>
       </c>
       <c r="CD23">
-        <v>808441</v>
+        <v>808927</v>
       </c>
       <c r="CE23">
-        <v>770922</v>
+        <v>786886</v>
       </c>
       <c r="CF23">
-        <v>695114</v>
+        <v>727022</v>
       </c>
       <c r="CG23">
-        <v>624002</v>
+        <v>646861</v>
       </c>
       <c r="CH23">
-        <v>568861</v>
+        <v>584719</v>
       </c>
       <c r="CI23">
-        <v>505004</v>
+        <v>514915</v>
       </c>
       <c r="CJ23">
-        <v>410051</v>
+        <v>411796</v>
       </c>
       <c r="CK23">
-        <v>257285</v>
+        <v>258007</v>
       </c>
       <c r="CL23">
-        <v>170355</v>
+        <v>169100</v>
       </c>
       <c r="CM23">
-        <v>183008</v>
+        <v>173403</v>
       </c>
       <c r="CN23">
-        <v>10830</v>
+        <v>14899</v>
       </c>
       <c r="CO23">
-        <v>25167</v>
+        <v>36302</v>
       </c>
       <c r="CP23">
-        <v>23477</v>
+        <v>33587</v>
       </c>
       <c r="CQ23">
-        <v>24859</v>
+        <v>31745</v>
       </c>
       <c r="CR23">
-        <v>23722</v>
+        <v>28696</v>
       </c>
       <c r="CS23">
-        <v>22147</v>
+        <v>25547</v>
       </c>
       <c r="CT23">
-        <v>18864</v>
+        <v>21836</v>
       </c>
       <c r="CU23">
-        <v>16573</v>
+        <v>19011</v>
       </c>
       <c r="CV23">
-        <v>13508</v>
+        <v>14994</v>
       </c>
       <c r="CW23">
-        <v>10715</v>
+        <v>11466</v>
       </c>
       <c r="CX23">
-        <v>7406</v>
+        <v>7973</v>
       </c>
       <c r="CY23">
-        <v>4880</v>
+        <v>5246</v>
       </c>
       <c r="CZ23">
-        <v>2740</v>
+        <v>2988</v>
       </c>
       <c r="DA23">
-        <v>1652</v>
+        <v>1739</v>
       </c>
       <c r="DB23">
-        <v>1186</v>
+        <v>1375</v>
       </c>
       <c r="DC23">
-        <v>230888</v>
+        <v>244383</v>
       </c>
       <c r="DD23">
-        <v>609922</v>
+        <v>725013</v>
       </c>
       <c r="DE23">
-        <v>723947</v>
+        <v>771227</v>
       </c>
       <c r="DF23">
-        <v>822626</v>
+        <v>803220</v>
       </c>
       <c r="DG23">
-        <v>809362</v>
+        <v>775267</v>
       </c>
       <c r="DH23">
-        <v>715256</v>
+        <v>690479</v>
       </c>
       <c r="DI23">
-        <v>687940</v>
+        <v>676274</v>
       </c>
       <c r="DJ23">
-        <v>617960</v>
+        <v>620928</v>
       </c>
       <c r="DK23">
-        <v>548199</v>
+        <v>552820</v>
       </c>
       <c r="DL23">
-        <v>480860</v>
+        <v>480701</v>
       </c>
       <c r="DM23">
-        <v>407399</v>
+        <v>408935</v>
       </c>
       <c r="DN23">
-        <v>320210</v>
+        <v>316063</v>
       </c>
       <c r="DO23">
-        <v>202980</v>
+        <v>199700</v>
       </c>
       <c r="DP23">
-        <v>131223</v>
+        <v>128364</v>
       </c>
       <c r="DQ23">
-        <v>112350</v>
+        <v>103534</v>
       </c>
       <c r="DR23">
-        <v>51562</v>
+        <v>66160</v>
       </c>
       <c r="DS23">
-        <v>121477</v>
+        <v>162478</v>
       </c>
       <c r="DT23">
-        <v>119446</v>
+        <v>155193</v>
       </c>
       <c r="DU23">
-        <v>126144</v>
+        <v>152994</v>
       </c>
       <c r="DV23">
-        <v>118601</v>
+        <v>136221</v>
       </c>
       <c r="DW23">
-        <v>112075</v>
+        <v>122781</v>
       </c>
       <c r="DX23">
-        <v>94262</v>
+        <v>101235</v>
       </c>
       <c r="DY23">
-        <v>81648</v>
+        <v>88582</v>
       </c>
       <c r="DZ23">
-        <v>71246</v>
+        <v>75835</v>
       </c>
       <c r="EA23">
-        <v>57536</v>
+        <v>59397</v>
       </c>
       <c r="EB23">
-        <v>42798</v>
+        <v>44615</v>
       </c>
       <c r="EC23">
-        <v>30851</v>
+        <v>31722</v>
       </c>
       <c r="ED23">
-        <v>19646</v>
+        <v>20492</v>
       </c>
       <c r="EE23">
-        <v>12782</v>
+        <v>13219</v>
       </c>
       <c r="EF23">
-        <v>11706</v>
+        <v>13068</v>
       </c>
       <c r="EG23">
-        <v>572126</v>
+        <v>574194</v>
       </c>
       <c r="EH23">
-        <v>1482775</v>
+        <v>1520065</v>
       </c>
       <c r="EI23">
-        <v>1617971</v>
+        <v>1485530</v>
       </c>
       <c r="EJ23">
-        <v>1653734</v>
+        <v>1552330</v>
       </c>
       <c r="EK23">
-        <v>1472399</v>
+        <v>1444899</v>
       </c>
       <c r="EL23">
-        <v>1414155</v>
+        <v>1385576</v>
       </c>
       <c r="EM23">
-        <v>1316881</v>
+        <v>1283632</v>
       </c>
       <c r="EN23">
-        <v>1358438</v>
+        <v>1337751</v>
       </c>
       <c r="EO23">
-        <v>1394644</v>
+        <v>1390746</v>
       </c>
       <c r="EP23">
-        <v>1322336</v>
+        <v>1332447</v>
       </c>
       <c r="EQ23">
-        <v>1087201</v>
+        <v>1104011</v>
       </c>
       <c r="ER23">
-        <v>835693</v>
+        <v>843401</v>
       </c>
       <c r="ES23">
-        <v>512175</v>
+        <v>514283</v>
       </c>
       <c r="ET23">
-        <v>335725</v>
+        <v>334187</v>
       </c>
       <c r="EU23">
-        <v>330359</v>
+        <v>328657</v>
       </c>
       <c r="EV23">
-        <v>54103</v>
+        <v>68577</v>
       </c>
       <c r="EW23">
-        <v>125490</v>
+        <v>168992</v>
       </c>
       <c r="EX23">
-        <v>122958</v>
+        <v>154338</v>
       </c>
       <c r="EY23">
-        <v>125251</v>
+        <v>146176</v>
       </c>
       <c r="EZ23">
-        <v>113051</v>
+        <v>127851</v>
       </c>
       <c r="FA23">
-        <v>102360</v>
+        <v>111972</v>
       </c>
       <c r="FB23">
-        <v>82822</v>
+        <v>91418</v>
       </c>
       <c r="FC23">
-        <v>72909</v>
+        <v>80043</v>
       </c>
       <c r="FD23">
-        <v>63885</v>
+        <v>67653</v>
       </c>
       <c r="FE23">
-        <v>50183</v>
+        <v>52206</v>
       </c>
       <c r="FF23">
-        <v>36229</v>
+        <v>37603</v>
       </c>
       <c r="FG23">
-        <v>24264</v>
+        <v>24875</v>
       </c>
       <c r="FH23">
-        <v>14156</v>
+        <v>14526</v>
       </c>
       <c r="FI23">
-        <v>8469</v>
+        <v>8574</v>
       </c>
       <c r="FJ23">
-        <v>6175</v>
+        <v>6522</v>
       </c>
       <c r="FK23">
-        <v>576692</v>
+        <v>584067</v>
       </c>
       <c r="FL23">
-        <v>1474103</v>
+        <v>1490887</v>
       </c>
       <c r="FM23">
-        <v>1606680</v>
+        <v>1403980</v>
       </c>
       <c r="FN23">
-        <v>1590674</v>
+        <v>1405558</v>
       </c>
       <c r="FO23">
-        <v>1368507</v>
+        <v>1282143</v>
       </c>
       <c r="FP23">
-        <v>1279854</v>
+        <v>1223957</v>
       </c>
       <c r="FQ23">
-        <v>1174704</v>
+        <v>1133102</v>
       </c>
       <c r="FR23">
-        <v>1216091</v>
+        <v>1178023</v>
       </c>
       <c r="FS23">
-        <v>1225497</v>
+        <v>1201986</v>
       </c>
       <c r="FT23">
-        <v>1126590</v>
+        <v>1119253</v>
       </c>
       <c r="FU23">
-        <v>858035</v>
+        <v>876603</v>
       </c>
       <c r="FV23">
-        <v>611454</v>
+        <v>621608</v>
       </c>
       <c r="FW23">
-        <v>342811</v>
+        <v>346921</v>
       </c>
       <c r="FX23">
-        <v>198322</v>
+        <v>198275</v>
       </c>
       <c r="FY23">
-        <v>147453</v>
+        <v>148683</v>
       </c>
       <c r="FZ23">
-        <v>3551</v>
+        <v>4097</v>
       </c>
       <c r="GA23">
-        <v>8271</v>
+        <v>10323</v>
       </c>
       <c r="GB23">
-        <v>8498</v>
+        <v>9341</v>
       </c>
       <c r="GC23">
-        <v>8710</v>
+        <v>8915</v>
       </c>
       <c r="GD23">
-        <v>8453</v>
+        <v>8258</v>
       </c>
       <c r="GE23">
-        <v>7832</v>
+        <v>7695</v>
       </c>
       <c r="GF23">
-        <v>6490</v>
+        <v>6534</v>
       </c>
       <c r="GG23">
-        <v>5821</v>
+        <v>5613</v>
       </c>
       <c r="GH23">
-        <v>4816</v>
+        <v>4861</v>
       </c>
       <c r="GI23">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="GJ23">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="GK23">
-        <v>1695</v>
+        <v>1682</v>
       </c>
       <c r="GL23">
-        <v>1007</v>
+        <v>1101</v>
       </c>
       <c r="GM23">
-        <v>728</v>
+        <v>681</v>
       </c>
       <c r="GN23">
-        <v>557</v>
+        <v>612</v>
       </c>
       <c r="GO23">
-        <v>8322</v>
+        <v>9625</v>
       </c>
       <c r="GP23">
-        <v>20204</v>
+        <v>26728</v>
       </c>
       <c r="GQ23">
-        <v>23115</v>
+        <v>26000</v>
       </c>
       <c r="GR23">
-        <v>25941</v>
+        <v>25985</v>
       </c>
       <c r="GS23">
-        <v>25179</v>
+        <v>24409</v>
       </c>
       <c r="GT23">
-        <v>22062</v>
+        <v>21813</v>
       </c>
       <c r="GU23">
-        <v>18786</v>
+        <v>19019</v>
       </c>
       <c r="GV23">
-        <v>18376</v>
+        <v>18437</v>
       </c>
       <c r="GW23">
-        <v>18091</v>
+        <v>17811</v>
       </c>
       <c r="GX23">
-        <v>15931</v>
+        <v>15561</v>
       </c>
       <c r="GY23">
-        <v>12942</v>
+        <v>12263</v>
       </c>
       <c r="GZ23">
-        <v>9712</v>
+        <v>8708</v>
       </c>
       <c r="HA23">
-        <v>6076</v>
+        <v>5432</v>
       </c>
       <c r="HB23">
-        <v>3705</v>
+        <v>3232</v>
       </c>
       <c r="HC23">
-        <v>3598</v>
+        <v>3181</v>
       </c>
       <c r="HD23">
-        <v>3638</v>
+        <v>4311</v>
       </c>
       <c r="HE23">
-        <v>8462</v>
+        <v>10575</v>
       </c>
       <c r="HF23">
-        <v>8873</v>
+        <v>9618</v>
       </c>
       <c r="HG23">
-        <v>10515</v>
+        <v>9019</v>
       </c>
       <c r="HH23">
-        <v>10701</v>
+        <v>8109</v>
       </c>
       <c r="HI23">
-        <v>9661</v>
+        <v>7558</v>
       </c>
       <c r="HJ23">
-        <v>7154</v>
+        <v>5988</v>
       </c>
       <c r="HK23">
-        <v>6163</v>
+        <v>5455</v>
       </c>
       <c r="HL23">
-        <v>4855</v>
+        <v>4452</v>
       </c>
       <c r="HM23">
-        <v>3646</v>
+        <v>3293</v>
       </c>
       <c r="HN23">
-        <v>2284</v>
+        <v>2207</v>
       </c>
       <c r="HO23">
-        <v>1526</v>
+        <v>1369</v>
       </c>
       <c r="HP23">
-        <v>807</v>
+        <v>772</v>
       </c>
       <c r="HQ23">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="HR23">
-        <v>334</v>
+        <v>385</v>
       </c>
       <c r="HS23">
-        <v>8469</v>
+        <v>9847</v>
       </c>
       <c r="HT23">
-        <v>20689</v>
+        <v>27413</v>
       </c>
       <c r="HU23">
-        <v>23029</v>
+        <v>26714</v>
       </c>
       <c r="HV23">
-        <v>27011</v>
+        <v>26585</v>
       </c>
       <c r="HW23">
-        <v>26240</v>
+        <v>24613</v>
       </c>
       <c r="HX23">
-        <v>23010</v>
+        <v>21862</v>
       </c>
       <c r="HY23">
-        <v>19662</v>
+        <v>18781</v>
       </c>
       <c r="HZ23">
-        <v>18459</v>
+        <v>17850</v>
       </c>
       <c r="IA23">
-        <v>17603</v>
+        <v>16491</v>
       </c>
       <c r="IB23">
-        <v>15725</v>
+        <v>14435</v>
       </c>
       <c r="IC23">
-        <v>11839</v>
+        <v>10810</v>
       </c>
       <c r="ID23">
-        <v>8982</v>
+        <v>7736</v>
       </c>
       <c r="IE23">
-        <v>5455</v>
+        <v>4467</v>
       </c>
       <c r="IF23">
-        <v>3048</v>
+        <v>2400</v>
       </c>
       <c r="IG23">
-        <v>2441</v>
+        <v>1764</v>
       </c>
       <c r="IH23">
-        <v>37692</v>
+        <v>72779</v>
       </c>
       <c r="II23">
-        <v>85648</v>
+        <v>157570</v>
       </c>
       <c r="IJ23">
-        <v>76344</v>
+        <v>140771</v>
       </c>
       <c r="IK23">
-        <v>68069</v>
+        <v>130364</v>
       </c>
       <c r="IL23">
-        <v>61113</v>
+        <v>115673</v>
       </c>
       <c r="IM23">
-        <v>56855</v>
+        <v>103073</v>
       </c>
       <c r="IN23">
-        <v>44407</v>
+        <v>83841</v>
       </c>
       <c r="IO23">
-        <v>36698</v>
+        <v>71672</v>
       </c>
       <c r="IP23">
-        <v>31660</v>
+        <v>58950</v>
       </c>
       <c r="IQ23">
-        <v>25522</v>
+        <v>47242</v>
       </c>
       <c r="IR23">
-        <v>18604</v>
+        <v>34152</v>
       </c>
       <c r="IS23">
-        <v>12626</v>
+        <v>24025</v>
       </c>
       <c r="IT23">
-        <v>7938</v>
+        <v>14338</v>
       </c>
       <c r="IU23">
-        <v>4883</v>
+        <v>8780</v>
       </c>
       <c r="IV23">
-        <v>4390</v>
+        <v>7776</v>
       </c>
       <c r="IW23">
-        <v>151994</v>
+        <v>207658</v>
       </c>
       <c r="IX23">
-        <v>348547</v>
+        <v>467201</v>
       </c>
       <c r="IY23">
-        <v>306880</v>
+        <v>414677</v>
       </c>
       <c r="IZ23">
-        <v>255068</v>
+        <v>386981</v>
       </c>
       <c r="JA23">
-        <v>208776</v>
+        <v>342491</v>
       </c>
       <c r="JB23">
-        <v>180973</v>
+        <v>306686</v>
       </c>
       <c r="JC23">
-        <v>148345</v>
+        <v>268201</v>
       </c>
       <c r="JD23">
-        <v>135268</v>
+        <v>262962</v>
       </c>
       <c r="JE23">
-        <v>124683</v>
+        <v>253118</v>
       </c>
       <c r="JF23">
-        <v>114590</v>
+        <v>230769</v>
       </c>
       <c r="JG23">
-        <v>91381</v>
+        <v>178870</v>
       </c>
       <c r="JH23">
-        <v>69452</v>
+        <v>132682</v>
       </c>
       <c r="JI23">
-        <v>44296</v>
+        <v>78817</v>
       </c>
       <c r="JJ23">
-        <v>28187</v>
+        <v>47313</v>
       </c>
       <c r="JK23">
-        <v>28709</v>
+        <v>42872</v>
       </c>
       <c r="JL23">
-        <v>38635</v>
+        <v>74795</v>
       </c>
       <c r="JM23">
-        <v>88162</v>
+        <v>161000</v>
       </c>
       <c r="JN23">
-        <v>78501</v>
+        <v>138725</v>
       </c>
       <c r="JO23">
-        <v>68245</v>
+        <v>123313</v>
       </c>
       <c r="JP23">
-        <v>61122</v>
+        <v>108338</v>
       </c>
       <c r="JQ23">
-        <v>55693</v>
+        <v>94597</v>
       </c>
       <c r="JR23">
-        <v>42547</v>
+        <v>77340</v>
       </c>
       <c r="JS23">
-        <v>35276</v>
+        <v>64598</v>
       </c>
       <c r="JT23">
-        <v>28988</v>
+        <v>51766</v>
       </c>
       <c r="JU23">
-        <v>22785</v>
+        <v>39767</v>
       </c>
       <c r="JV23">
-        <v>15536</v>
+        <v>27755</v>
       </c>
       <c r="JW23">
-        <v>10042</v>
+        <v>18037</v>
       </c>
       <c r="JX23">
-        <v>5660</v>
+        <v>10187</v>
       </c>
       <c r="JY23">
-        <v>3286</v>
+        <v>5684</v>
       </c>
       <c r="JZ23">
-        <v>2356</v>
+        <v>4318</v>
       </c>
       <c r="KA23">
-        <v>154131</v>
+        <v>209580</v>
       </c>
       <c r="KB23">
-        <v>349680</v>
+        <v>453109</v>
       </c>
       <c r="KC23">
-        <v>301053</v>
+        <v>384070</v>
       </c>
       <c r="KD23">
-        <v>234047</v>
+        <v>344734</v>
       </c>
       <c r="KE23">
-        <v>186440</v>
+        <v>301998</v>
       </c>
       <c r="KF23">
-        <v>160281</v>
+        <v>268281</v>
       </c>
       <c r="KG23">
-        <v>132162</v>
+        <v>236017</v>
       </c>
       <c r="KH23">
-        <v>122054</v>
+        <v>229281</v>
       </c>
       <c r="KI23">
-        <v>111545</v>
+        <v>215407</v>
       </c>
       <c r="KJ23">
-        <v>103799</v>
+        <v>194942</v>
       </c>
       <c r="KK23">
-        <v>81070</v>
+        <v>146486</v>
       </c>
       <c r="KL23">
-        <v>60068</v>
+        <v>104799</v>
       </c>
       <c r="KM23">
-        <v>36330</v>
+        <v>59484</v>
       </c>
       <c r="KN23">
-        <v>21653</v>
+        <v>33254</v>
       </c>
       <c r="KO23">
-        <v>17729</v>
+        <v>24849</v>
       </c>
       <c r="KP23">
-        <v>885937</v>
+        <v>839069</v>
       </c>
       <c r="KQ23">
-        <v>2113532</v>
+        <v>2048702</v>
       </c>
       <c r="KR23">
-        <v>2080321</v>
+        <v>1931809</v>
       </c>
       <c r="KS23">
-        <v>1977319</v>
+        <v>1869369</v>
       </c>
       <c r="KT23">
-        <v>1929256</v>
+        <v>1799700</v>
       </c>
       <c r="KU23">
-        <v>1867189</v>
+        <v>1740904</v>
       </c>
       <c r="KV23">
-        <v>1743442</v>
+        <v>1622555</v>
       </c>
       <c r="KW23">
-        <v>1564531</v>
+        <v>1486581</v>
       </c>
       <c r="KX23">
-        <v>1373835</v>
+        <v>1323977</v>
       </c>
       <c r="KY23">
-        <v>1124291</v>
+        <v>1098922</v>
       </c>
       <c r="KZ23">
-        <v>873937</v>
+        <v>861368</v>
       </c>
       <c r="LA23">
-        <v>653482</v>
+        <v>651368</v>
       </c>
       <c r="LB23">
-        <v>436977</v>
+        <v>439739</v>
       </c>
       <c r="LC23">
-        <v>293360</v>
+        <v>296131</v>
       </c>
       <c r="LD23">
-        <v>290548</v>
+        <v>296336</v>
       </c>
       <c r="LE23">
-        <v>2165657</v>
+        <v>2107730</v>
       </c>
       <c r="LF23">
-        <v>5531435</v>
+        <v>5684290</v>
       </c>
       <c r="LG23">
-        <v>5820379</v>
+        <v>5607262</v>
       </c>
       <c r="LH23">
-        <v>6235094</v>
+        <v>6047843</v>
       </c>
       <c r="LI23">
-        <v>6151689</v>
+        <v>6014631</v>
       </c>
       <c r="LJ23">
-        <v>5878199</v>
+        <v>5737453</v>
       </c>
       <c r="LK23">
-        <v>5619667</v>
+        <v>5495087</v>
       </c>
       <c r="LL23">
-        <v>6436408</v>
+        <v>6324518</v>
       </c>
       <c r="LM23">
-        <v>7160233</v>
+        <v>7088838</v>
       </c>
       <c r="LN23">
-        <v>7541666</v>
+        <v>7576689</v>
       </c>
       <c r="LO23">
-        <v>6906871</v>
+        <v>7004377</v>
       </c>
       <c r="LP23">
-        <v>6052563</v>
+        <v>6180684</v>
       </c>
       <c r="LQ23">
-        <v>4105015</v>
+        <v>4258594</v>
       </c>
       <c r="LR23">
-        <v>2736517</v>
+        <v>2858137</v>
       </c>
       <c r="LS23">
-        <v>2987362</v>
+        <v>3133084</v>
       </c>
       <c r="LT23">
-        <v>914261</v>
+        <v>871761</v>
       </c>
       <c r="LU23">
-        <v>2170046</v>
+        <v>2115005</v>
       </c>
       <c r="LV23">
-        <v>2160924</v>
+        <v>1985007</v>
       </c>
       <c r="LW23">
-        <v>2152707</v>
+        <v>1901264</v>
       </c>
       <c r="LX23">
-        <v>2133569</v>
+        <v>1807249</v>
       </c>
       <c r="LY23">
-        <v>2015763</v>
+        <v>1712710</v>
       </c>
       <c r="LZ23">
-        <v>1816496</v>
+        <v>1557072</v>
       </c>
       <c r="MA23">
-        <v>1632709</v>
+        <v>1436380</v>
       </c>
       <c r="MB23">
-        <v>1392053</v>
+        <v>1260207</v>
       </c>
       <c r="MC23">
-        <v>1085590</v>
+        <v>1002957</v>
       </c>
       <c r="MD23">
-        <v>780448</v>
+        <v>738795</v>
       </c>
       <c r="ME23">
-        <v>547243</v>
+        <v>526195</v>
       </c>
       <c r="MF23">
-        <v>329966</v>
+        <v>325374</v>
       </c>
       <c r="MG23">
-        <v>201762</v>
+        <v>199360</v>
       </c>
       <c r="MH23">
-        <v>165394</v>
+        <v>164550</v>
       </c>
       <c r="MI23">
-        <v>2258799</v>
+        <v>2184948</v>
       </c>
       <c r="MJ23">
-        <v>5661839</v>
+        <v>5729063</v>
       </c>
       <c r="MK23">
-        <v>5956953</v>
+        <v>5702040</v>
       </c>
       <c r="ML23">
-        <v>6305338</v>
+        <v>6119599</v>
       </c>
       <c r="MM23">
-        <v>6263030</v>
+        <v>6070930</v>
       </c>
       <c r="MN23">
-        <v>6006431</v>
+        <v>5788841</v>
       </c>
       <c r="MO23">
-        <v>5742088</v>
+        <v>5531149</v>
       </c>
       <c r="MP23">
-        <v>6563250</v>
+        <v>6295797</v>
       </c>
       <c r="MQ23">
-        <v>7102246</v>
+        <v>6895573</v>
       </c>
       <c r="MR23">
-        <v>7318784</v>
+        <v>7194812</v>
       </c>
       <c r="MS23">
-        <v>6456907</v>
+        <v>6457408</v>
       </c>
       <c r="MT23">
-        <v>5457688</v>
+        <v>5519754</v>
       </c>
       <c r="MU23">
-        <v>3487602</v>
+        <v>3603276</v>
       </c>
       <c r="MV23">
-        <v>2099621</v>
+        <v>2191498</v>
       </c>
       <c r="MW23">
-        <v>1733919</v>
+        <v>1844433</v>
       </c>
     </row>
     <row r="24" spans="1:361">
@@ -41818,1084 +41818,1084 @@
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>31633</v>
+        <v>69393</v>
       </c>
       <c r="C24">
-        <v>74531</v>
+        <v>164659</v>
       </c>
       <c r="D24">
-        <v>72295</v>
+        <v>159204</v>
       </c>
       <c r="E24">
-        <v>69373</v>
+        <v>160801</v>
       </c>
       <c r="F24">
-        <v>65517</v>
+        <v>158138</v>
       </c>
       <c r="G24">
-        <v>63187</v>
+        <v>156984</v>
       </c>
       <c r="H24">
-        <v>55774</v>
+        <v>139275</v>
       </c>
       <c r="I24">
-        <v>50460</v>
+        <v>121826</v>
       </c>
       <c r="J24">
-        <v>42963</v>
+        <v>101066</v>
       </c>
       <c r="K24">
-        <v>35747</v>
+        <v>81053</v>
       </c>
       <c r="L24">
-        <v>25828</v>
+        <v>59381</v>
       </c>
       <c r="M24">
-        <v>17219</v>
+        <v>39347</v>
       </c>
       <c r="N24">
-        <v>10604</v>
+        <v>24817</v>
       </c>
       <c r="O24">
-        <v>6202</v>
+        <v>14910</v>
       </c>
       <c r="P24">
-        <v>5577</v>
+        <v>13333</v>
       </c>
       <c r="Q24">
-        <v>34335</v>
+        <v>33836</v>
       </c>
       <c r="R24">
-        <v>87142</v>
+        <v>83703</v>
       </c>
       <c r="S24">
-        <v>89276</v>
+        <v>74374</v>
       </c>
       <c r="T24">
-        <v>93387</v>
+        <v>81072</v>
       </c>
       <c r="U24">
-        <v>81957</v>
+        <v>76806</v>
       </c>
       <c r="V24">
-        <v>75579</v>
+        <v>72960</v>
       </c>
       <c r="W24">
-        <v>69275</v>
+        <v>68203</v>
       </c>
       <c r="X24">
-        <v>71805</v>
+        <v>71181</v>
       </c>
       <c r="Y24">
-        <v>76273</v>
+        <v>75331</v>
       </c>
       <c r="Z24">
-        <v>77915</v>
+        <v>75240</v>
       </c>
       <c r="AA24">
-        <v>66115</v>
+        <v>62691</v>
       </c>
       <c r="AB24">
-        <v>50073</v>
+        <v>46397</v>
       </c>
       <c r="AC24">
-        <v>33361</v>
+        <v>30380</v>
       </c>
       <c r="AD24">
-        <v>20459</v>
+        <v>18592</v>
       </c>
       <c r="AE24">
-        <v>19170</v>
+        <v>17242</v>
       </c>
       <c r="AF24">
-        <v>33667</v>
+        <v>74968</v>
       </c>
       <c r="AG24">
-        <v>78636</v>
+        <v>183096</v>
       </c>
       <c r="AH24">
-        <v>75397</v>
+        <v>178066</v>
       </c>
       <c r="AI24">
-        <v>80435</v>
+        <v>178074</v>
       </c>
       <c r="AJ24">
-        <v>78966</v>
+        <v>173356</v>
       </c>
       <c r="AK24">
-        <v>74877</v>
+        <v>167758</v>
       </c>
       <c r="AL24">
-        <v>64648</v>
+        <v>147081</v>
       </c>
       <c r="AM24">
-        <v>57663</v>
+        <v>128309</v>
       </c>
       <c r="AN24">
-        <v>47733</v>
+        <v>105060</v>
       </c>
       <c r="AO24">
-        <v>37525</v>
+        <v>80270</v>
       </c>
       <c r="AP24">
-        <v>26567</v>
+        <v>56858</v>
       </c>
       <c r="AQ24">
-        <v>16004</v>
+        <v>34600</v>
       </c>
       <c r="AR24">
-        <v>9369</v>
+        <v>19907</v>
       </c>
       <c r="AS24">
-        <v>4741</v>
+        <v>10424</v>
       </c>
       <c r="AT24">
-        <v>3396</v>
+        <v>7836</v>
       </c>
       <c r="AU24">
-        <v>35269</v>
+        <v>35669</v>
       </c>
       <c r="AV24">
-        <v>88299</v>
+        <v>85478</v>
       </c>
       <c r="AW24">
-        <v>90610</v>
+        <v>76812</v>
       </c>
       <c r="AX24">
-        <v>94763</v>
+        <v>81252</v>
       </c>
       <c r="AY24">
-        <v>80995</v>
+        <v>74630</v>
       </c>
       <c r="AZ24">
-        <v>74307</v>
+        <v>70858</v>
       </c>
       <c r="BA24">
-        <v>67285</v>
+        <v>65599</v>
       </c>
       <c r="BB24">
-        <v>69587</v>
+        <v>67634</v>
       </c>
       <c r="BC24">
-        <v>71056</v>
+        <v>69762</v>
       </c>
       <c r="BD24">
-        <v>69532</v>
+        <v>67343</v>
       </c>
       <c r="BE24">
-        <v>56805</v>
+        <v>54578</v>
       </c>
       <c r="BF24">
-        <v>42765</v>
+        <v>39517</v>
       </c>
       <c r="BG24">
-        <v>28022</v>
+        <v>24722</v>
       </c>
       <c r="BH24">
-        <v>16072</v>
+        <v>13826</v>
       </c>
       <c r="BI24">
-        <v>12279</v>
+        <v>10217</v>
       </c>
       <c r="BJ24">
-        <v>10862</v>
+        <v>14711</v>
       </c>
       <c r="BK24">
-        <v>24940</v>
+        <v>37201</v>
       </c>
       <c r="BL24">
-        <v>24379</v>
+        <v>34775</v>
       </c>
       <c r="BM24">
-        <v>25933</v>
+        <v>33538</v>
       </c>
       <c r="BN24">
-        <v>23028</v>
+        <v>30001</v>
       </c>
       <c r="BO24">
-        <v>22395</v>
+        <v>27502</v>
       </c>
       <c r="BP24">
-        <v>19942</v>
+        <v>24119</v>
       </c>
       <c r="BQ24">
-        <v>17373</v>
+        <v>21336</v>
       </c>
       <c r="BR24">
-        <v>14560</v>
+        <v>17281</v>
       </c>
       <c r="BS24">
-        <v>12101</v>
+        <v>13662</v>
       </c>
       <c r="BT24">
-        <v>9122</v>
+        <v>10163</v>
       </c>
       <c r="BU24">
-        <v>6497</v>
+        <v>7084</v>
       </c>
       <c r="BV24">
-        <v>4228</v>
+        <v>4627</v>
       </c>
       <c r="BW24">
-        <v>2547</v>
+        <v>2787</v>
       </c>
       <c r="BX24">
-        <v>2347</v>
+        <v>2700</v>
       </c>
       <c r="BY24">
-        <v>242663</v>
+        <v>247806</v>
       </c>
       <c r="BZ24">
-        <v>632738</v>
+        <v>739289</v>
       </c>
       <c r="CA24">
-        <v>756290</v>
+        <v>807782</v>
       </c>
       <c r="CB24">
-        <v>899717</v>
+        <v>900824</v>
       </c>
       <c r="CC24">
-        <v>900425</v>
+        <v>894752</v>
       </c>
       <c r="CD24">
-        <v>841580</v>
+        <v>839749</v>
       </c>
       <c r="CE24">
-        <v>783523</v>
+        <v>791830</v>
       </c>
       <c r="CF24">
-        <v>730979</v>
+        <v>762485</v>
       </c>
       <c r="CG24">
-        <v>636501</v>
+        <v>661043</v>
       </c>
       <c r="CH24">
-        <v>581647</v>
+        <v>594954</v>
       </c>
       <c r="CI24">
-        <v>523887</v>
+        <v>537328</v>
       </c>
       <c r="CJ24">
-        <v>429440</v>
+        <v>431362</v>
       </c>
       <c r="CK24">
-        <v>281798</v>
+        <v>281785</v>
       </c>
       <c r="CL24">
-        <v>181821</v>
+        <v>180682</v>
       </c>
       <c r="CM24">
-        <v>193944</v>
+        <v>184336</v>
       </c>
       <c r="CN24">
-        <v>11352</v>
+        <v>15339</v>
       </c>
       <c r="CO24">
-        <v>26006</v>
+        <v>37294</v>
       </c>
       <c r="CP24">
-        <v>24136</v>
+        <v>34445</v>
       </c>
       <c r="CQ24">
-        <v>25252</v>
+        <v>32758</v>
       </c>
       <c r="CR24">
-        <v>24125</v>
+        <v>29490</v>
       </c>
       <c r="CS24">
-        <v>22638</v>
+        <v>26330</v>
       </c>
       <c r="CT24">
-        <v>19509</v>
+        <v>22474</v>
       </c>
       <c r="CU24">
-        <v>17132</v>
+        <v>19685</v>
       </c>
       <c r="CV24">
-        <v>13967</v>
+        <v>15609</v>
       </c>
       <c r="CW24">
-        <v>11147</v>
+        <v>11990</v>
       </c>
       <c r="CX24">
-        <v>7912</v>
+        <v>8538</v>
       </c>
       <c r="CY24">
-        <v>5211</v>
+        <v>5592</v>
       </c>
       <c r="CZ24">
-        <v>3024</v>
+        <v>3298</v>
       </c>
       <c r="DA24">
-        <v>1712</v>
+        <v>1800</v>
       </c>
       <c r="DB24">
-        <v>1270</v>
+        <v>1445</v>
       </c>
       <c r="DC24">
-        <v>243252</v>
+        <v>249371</v>
       </c>
       <c r="DD24">
-        <v>635516</v>
+        <v>740987</v>
       </c>
       <c r="DE24">
-        <v>735913</v>
+        <v>798051</v>
       </c>
       <c r="DF24">
-        <v>848498</v>
+        <v>838095</v>
       </c>
       <c r="DG24">
-        <v>835343</v>
+        <v>801270</v>
       </c>
       <c r="DH24">
-        <v>751671</v>
+        <v>721869</v>
       </c>
       <c r="DI24">
-        <v>695656</v>
+        <v>679721</v>
       </c>
       <c r="DJ24">
-        <v>648958</v>
+        <v>649541</v>
       </c>
       <c r="DK24">
-        <v>557553</v>
+        <v>562753</v>
       </c>
       <c r="DL24">
-        <v>494465</v>
+        <v>492498</v>
       </c>
       <c r="DM24">
-        <v>424667</v>
+        <v>426673</v>
       </c>
       <c r="DN24">
-        <v>332802</v>
+        <v>330408</v>
       </c>
       <c r="DO24">
-        <v>221544</v>
+        <v>216119</v>
       </c>
       <c r="DP24">
-        <v>139104</v>
+        <v>136039</v>
       </c>
       <c r="DQ24">
-        <v>121420</v>
+        <v>112495</v>
       </c>
       <c r="DR24">
-        <v>53609</v>
+        <v>66388</v>
       </c>
       <c r="DS24">
-        <v>126380</v>
+        <v>168834</v>
       </c>
       <c r="DT24">
-        <v>119822</v>
+        <v>156437</v>
       </c>
       <c r="DU24">
-        <v>129671</v>
+        <v>158838</v>
       </c>
       <c r="DV24">
-        <v>120348</v>
+        <v>139889</v>
       </c>
       <c r="DW24">
-        <v>115562</v>
+        <v>127816</v>
       </c>
       <c r="DX24">
-        <v>98503</v>
+        <v>105833</v>
       </c>
       <c r="DY24">
-        <v>84627</v>
+        <v>91876</v>
       </c>
       <c r="DZ24">
-        <v>73734</v>
+        <v>79061</v>
       </c>
       <c r="EA24">
-        <v>59737</v>
+        <v>62071</v>
       </c>
       <c r="EB24">
-        <v>45632</v>
+        <v>47522</v>
       </c>
       <c r="EC24">
-        <v>32620</v>
+        <v>33605</v>
       </c>
       <c r="ED24">
-        <v>21476</v>
+        <v>22332</v>
       </c>
       <c r="EE24">
-        <v>13248</v>
+        <v>13745</v>
       </c>
       <c r="EF24">
-        <v>12284</v>
+        <v>13581</v>
       </c>
       <c r="EG24">
-        <v>573878</v>
+        <v>560534</v>
       </c>
       <c r="EH24">
-        <v>1484106</v>
+        <v>1540612</v>
       </c>
       <c r="EI24">
-        <v>1582268</v>
+        <v>1467977</v>
       </c>
       <c r="EJ24">
-        <v>1705376</v>
+        <v>1577752</v>
       </c>
       <c r="EK24">
-        <v>1490659</v>
+        <v>1458347</v>
       </c>
       <c r="EL24">
-        <v>1438021</v>
+        <v>1408493</v>
       </c>
       <c r="EM24">
-        <v>1310285</v>
+        <v>1278062</v>
       </c>
       <c r="EN24">
-        <v>1361819</v>
+        <v>1336198</v>
       </c>
       <c r="EO24">
-        <v>1371079</v>
+        <v>1365940</v>
       </c>
       <c r="EP24">
-        <v>1330176</v>
+        <v>1334180</v>
       </c>
       <c r="EQ24">
-        <v>1124974</v>
+        <v>1142856</v>
       </c>
       <c r="ER24">
-        <v>860497</v>
+        <v>871539</v>
       </c>
       <c r="ES24">
-        <v>551916</v>
+        <v>552508</v>
       </c>
       <c r="ET24">
-        <v>346892</v>
+        <v>346202</v>
       </c>
       <c r="EU24">
-        <v>335044</v>
+        <v>332515</v>
       </c>
       <c r="EV24">
-        <v>56182</v>
+        <v>69467</v>
       </c>
       <c r="EW24">
-        <v>130941</v>
+        <v>175088</v>
       </c>
       <c r="EX24">
-        <v>124080</v>
+        <v>158400</v>
       </c>
       <c r="EY24">
-        <v>129679</v>
+        <v>152480</v>
       </c>
       <c r="EZ24">
-        <v>115722</v>
+        <v>131851</v>
       </c>
       <c r="FA24">
-        <v>106909</v>
+        <v>117778</v>
       </c>
       <c r="FB24">
-        <v>86667</v>
+        <v>95144</v>
       </c>
       <c r="FC24">
-        <v>75076</v>
+        <v>82898</v>
       </c>
       <c r="FD24">
-        <v>65422</v>
+        <v>69800</v>
       </c>
       <c r="FE24">
-        <v>52474</v>
+        <v>54716</v>
       </c>
       <c r="FF24">
-        <v>38680</v>
+        <v>40057</v>
       </c>
       <c r="FG24">
-        <v>25683</v>
+        <v>26552</v>
       </c>
       <c r="FH24">
-        <v>15441</v>
+        <v>15779</v>
       </c>
       <c r="FI24">
-        <v>8853</v>
+        <v>9087</v>
       </c>
       <c r="FJ24">
-        <v>6639</v>
+        <v>6890</v>
       </c>
       <c r="FK24">
-        <v>580103</v>
+        <v>577497</v>
       </c>
       <c r="FL24">
-        <v>1476785</v>
+        <v>1515280</v>
       </c>
       <c r="FM24">
-        <v>1568416</v>
+        <v>1400165</v>
       </c>
       <c r="FN24">
-        <v>1652003</v>
+        <v>1435945</v>
       </c>
       <c r="FO24">
-        <v>1394073</v>
+        <v>1298166</v>
       </c>
       <c r="FP24">
-        <v>1307090</v>
+        <v>1243489</v>
       </c>
       <c r="FQ24">
-        <v>1165881</v>
+        <v>1124329</v>
       </c>
       <c r="FR24">
-        <v>1216097</v>
+        <v>1173721</v>
       </c>
       <c r="FS24">
-        <v>1200723</v>
+        <v>1176286</v>
       </c>
       <c r="FT24">
-        <v>1132652</v>
+        <v>1118210</v>
       </c>
       <c r="FU24">
-        <v>891883</v>
+        <v>907584</v>
       </c>
       <c r="FV24">
-        <v>624680</v>
+        <v>640225</v>
       </c>
       <c r="FW24">
-        <v>372078</v>
+        <v>373963</v>
       </c>
       <c r="FX24">
-        <v>205213</v>
+        <v>206204</v>
       </c>
       <c r="FY24">
-        <v>152165</v>
+        <v>153001</v>
       </c>
       <c r="FZ24">
-        <v>3657</v>
+        <v>4181</v>
       </c>
       <c r="GA24">
-        <v>8600</v>
+        <v>10640</v>
       </c>
       <c r="GB24">
-        <v>8441</v>
+        <v>9554</v>
       </c>
       <c r="GC24">
-        <v>8787</v>
+        <v>9075</v>
       </c>
       <c r="GD24">
-        <v>8500</v>
+        <v>8354</v>
       </c>
       <c r="GE24">
-        <v>8093</v>
+        <v>7929</v>
       </c>
       <c r="GF24">
-        <v>6762</v>
+        <v>6763</v>
       </c>
       <c r="GG24">
-        <v>5982</v>
+        <v>5819</v>
       </c>
       <c r="GH24">
+        <v>4993</v>
+      </c>
+      <c r="GI24">
+        <v>3861</v>
+      </c>
+      <c r="GJ24">
+        <v>2796</v>
+      </c>
+      <c r="GK24">
+        <v>1836</v>
+      </c>
+      <c r="GL24">
+        <v>1156</v>
+      </c>
+      <c r="GM24">
+        <v>725</v>
+      </c>
+      <c r="GN24">
+        <v>656</v>
+      </c>
+      <c r="GO24">
+        <v>9558</v>
+      </c>
+      <c r="GP24">
+        <v>27016</v>
+      </c>
+      <c r="GQ24">
+        <v>26324</v>
+      </c>
+      <c r="GR24">
+        <v>26471</v>
+      </c>
+      <c r="GS24">
+        <v>24852</v>
+      </c>
+      <c r="GT24">
+        <v>22572</v>
+      </c>
+      <c r="GU24">
+        <v>19526</v>
+      </c>
+      <c r="GV24">
+        <v>18687</v>
+      </c>
+      <c r="GW24">
+        <v>17812</v>
+      </c>
+      <c r="GX24">
+        <v>16239</v>
+      </c>
+      <c r="GY24">
+        <v>12956</v>
+      </c>
+      <c r="GZ24">
+        <v>9382</v>
+      </c>
+      <c r="HA24">
+        <v>5884</v>
+      </c>
+      <c r="HB24">
+        <v>3489</v>
+      </c>
+      <c r="HC24">
+        <v>3400</v>
+      </c>
+      <c r="HD24">
+        <v>4443</v>
+      </c>
+      <c r="HE24">
+        <v>10766</v>
+      </c>
+      <c r="HF24">
+        <v>9822</v>
+      </c>
+      <c r="HG24">
+        <v>9245</v>
+      </c>
+      <c r="HH24">
+        <v>8289</v>
+      </c>
+      <c r="HI24">
+        <v>7745</v>
+      </c>
+      <c r="HJ24">
+        <v>6228</v>
+      </c>
+      <c r="HK24">
+        <v>5536</v>
+      </c>
+      <c r="HL24">
+        <v>4642</v>
+      </c>
+      <c r="HM24">
+        <v>3520</v>
+      </c>
+      <c r="HN24">
+        <v>2364</v>
+      </c>
+      <c r="HO24">
+        <v>1454</v>
+      </c>
+      <c r="HP24">
+        <v>846</v>
+      </c>
+      <c r="HQ24">
+        <v>515</v>
+      </c>
+      <c r="HR24">
+        <v>386</v>
+      </c>
+      <c r="HS24">
+        <v>9965</v>
+      </c>
+      <c r="HT24">
+        <v>27509</v>
+      </c>
+      <c r="HU24">
+        <v>26927</v>
+      </c>
+      <c r="HV24">
+        <v>26957</v>
+      </c>
+      <c r="HW24">
+        <v>25233</v>
+      </c>
+      <c r="HX24">
+        <v>22615</v>
+      </c>
+      <c r="HY24">
+        <v>19254</v>
+      </c>
+      <c r="HZ24">
+        <v>18029</v>
+      </c>
+      <c r="IA24">
+        <v>16603</v>
+      </c>
+      <c r="IB24">
+        <v>14951</v>
+      </c>
+      <c r="IC24">
+        <v>11540</v>
+      </c>
+      <c r="ID24">
+        <v>8185</v>
+      </c>
+      <c r="IE24">
         <v>4985</v>
       </c>
-      <c r="GI24">
-        <v>3892</v>
-      </c>
-      <c r="GJ24">
-        <v>2758</v>
-      </c>
-      <c r="GK24">
-        <v>1841</v>
-      </c>
-      <c r="GL24">
-        <v>1074</v>
-      </c>
-      <c r="GM24">
-        <v>767</v>
-      </c>
-      <c r="GN24">
-        <v>603</v>
-      </c>
-      <c r="GO24">
-        <v>8752</v>
-      </c>
-      <c r="GP24">
-        <v>20850</v>
-      </c>
-      <c r="GQ24">
-        <v>22947</v>
-      </c>
-      <c r="GR24">
-        <v>26176</v>
-      </c>
-      <c r="GS24">
-        <v>25584</v>
-      </c>
-      <c r="GT24">
-        <v>23057</v>
-      </c>
-      <c r="GU24">
-        <v>19396</v>
-      </c>
-      <c r="GV24">
-        <v>18543</v>
-      </c>
-      <c r="GW24">
-        <v>18125</v>
-      </c>
-      <c r="GX24">
-        <v>16590</v>
-      </c>
-      <c r="GY24">
-        <v>13585</v>
-      </c>
-      <c r="GZ24">
-        <v>10309</v>
-      </c>
-      <c r="HA24">
-        <v>6710</v>
-      </c>
-      <c r="HB24">
-        <v>3950</v>
-      </c>
-      <c r="HC24">
-        <v>3870</v>
-      </c>
-      <c r="HD24">
-        <v>3788</v>
-      </c>
-      <c r="HE24">
-        <v>8610</v>
-      </c>
-      <c r="HF24">
-        <v>8673</v>
-      </c>
-      <c r="HG24">
-        <v>10402</v>
-      </c>
-      <c r="HH24">
-        <v>10767</v>
-      </c>
-      <c r="HI24">
-        <v>10032</v>
-      </c>
-      <c r="HJ24">
-        <v>7562</v>
-      </c>
-      <c r="HK24">
-        <v>6296</v>
-      </c>
-      <c r="HL24">
-        <v>5101</v>
-      </c>
-      <c r="HM24">
-        <v>3834</v>
-      </c>
-      <c r="HN24">
-        <v>2505</v>
-      </c>
-      <c r="HO24">
-        <v>1591</v>
-      </c>
-      <c r="HP24">
-        <v>904</v>
-      </c>
-      <c r="HQ24">
-        <v>491</v>
-      </c>
-      <c r="HR24">
-        <v>365</v>
-      </c>
-      <c r="HS24">
-        <v>8866</v>
-      </c>
-      <c r="HT24">
-        <v>21157</v>
-      </c>
-      <c r="HU24">
-        <v>22796</v>
-      </c>
-      <c r="HV24">
-        <v>26989</v>
-      </c>
-      <c r="HW24">
-        <v>26511</v>
-      </c>
-      <c r="HX24">
-        <v>24164</v>
-      </c>
-      <c r="HY24">
-        <v>20082</v>
-      </c>
-      <c r="HZ24">
-        <v>18785</v>
-      </c>
-      <c r="IA24">
-        <v>17627</v>
-      </c>
-      <c r="IB24">
-        <v>16266</v>
-      </c>
-      <c r="IC24">
-        <v>12596</v>
-      </c>
-      <c r="ID24">
-        <v>9371</v>
-      </c>
-      <c r="IE24">
-        <v>6076</v>
-      </c>
       <c r="IF24">
-        <v>3239</v>
+        <v>2598</v>
       </c>
       <c r="IG24">
-        <v>2674</v>
+        <v>1939</v>
       </c>
       <c r="IH24">
-        <v>39981</v>
+        <v>76717</v>
       </c>
       <c r="II24">
-        <v>89291</v>
+        <v>165616</v>
       </c>
       <c r="IJ24">
-        <v>79542</v>
+        <v>144256</v>
       </c>
       <c r="IK24">
-        <v>71503</v>
+        <v>134954</v>
       </c>
       <c r="IL24">
-        <v>63140</v>
+        <v>119176</v>
       </c>
       <c r="IM24">
-        <v>58760</v>
+        <v>106866</v>
       </c>
       <c r="IN24">
-        <v>47177</v>
+        <v>87496</v>
       </c>
       <c r="IO24">
-        <v>38436</v>
+        <v>74830</v>
       </c>
       <c r="IP24">
-        <v>32436</v>
+        <v>61142</v>
       </c>
       <c r="IQ24">
-        <v>26806</v>
+        <v>49306</v>
       </c>
       <c r="IR24">
-        <v>19980</v>
+        <v>36455</v>
       </c>
       <c r="IS24">
-        <v>13361</v>
+        <v>25312</v>
       </c>
       <c r="IT24">
-        <v>8781</v>
+        <v>15898</v>
       </c>
       <c r="IU24">
-        <v>5152</v>
+        <v>9384</v>
       </c>
       <c r="IV24">
-        <v>4627</v>
+        <v>8243</v>
       </c>
       <c r="IW24">
-        <v>158599</v>
+        <v>215627</v>
       </c>
       <c r="IX24">
-        <v>359024</v>
+        <v>483826</v>
       </c>
       <c r="IY24">
-        <v>315682</v>
+        <v>420879</v>
       </c>
       <c r="IZ24">
-        <v>269729</v>
+        <v>397437</v>
       </c>
       <c r="JA24">
-        <v>215452</v>
+        <v>349053</v>
       </c>
       <c r="JB24">
-        <v>188306</v>
+        <v>316238</v>
       </c>
       <c r="JC24">
-        <v>152602</v>
+        <v>271300</v>
       </c>
       <c r="JD24">
-        <v>139708</v>
+        <v>267808</v>
       </c>
       <c r="JE24">
-        <v>123747</v>
+        <v>251267</v>
       </c>
       <c r="JF24">
-        <v>117329</v>
+        <v>236984</v>
       </c>
       <c r="JG24">
-        <v>95993</v>
+        <v>189543</v>
       </c>
       <c r="JH24">
-        <v>71388</v>
+        <v>137521</v>
       </c>
       <c r="JI24">
-        <v>49267</v>
+        <v>89645</v>
       </c>
       <c r="JJ24">
-        <v>30089</v>
+        <v>51575</v>
       </c>
       <c r="JK24">
-        <v>30744</v>
+        <v>47414</v>
       </c>
       <c r="JL24">
-        <v>41079</v>
+        <v>78857</v>
       </c>
       <c r="JM24">
-        <v>91954</v>
+        <v>169929</v>
       </c>
       <c r="JN24">
-        <v>82183</v>
+        <v>143393</v>
       </c>
       <c r="JO24">
-        <v>72259</v>
+        <v>128973</v>
       </c>
       <c r="JP24">
-        <v>62584</v>
+        <v>111274</v>
       </c>
       <c r="JQ24">
-        <v>57893</v>
+        <v>98533</v>
       </c>
       <c r="JR24">
-        <v>45340</v>
+        <v>80502</v>
       </c>
       <c r="JS24">
-        <v>36598</v>
+        <v>66820</v>
       </c>
       <c r="JT24">
-        <v>29733</v>
+        <v>53780</v>
       </c>
       <c r="JU24">
-        <v>23941</v>
+        <v>41704</v>
       </c>
       <c r="JV24">
-        <v>16733</v>
+        <v>29710</v>
       </c>
       <c r="JW24">
-        <v>10530</v>
+        <v>19044</v>
       </c>
       <c r="JX24">
-        <v>6306</v>
+        <v>11236</v>
       </c>
       <c r="JY24">
-        <v>3461</v>
+        <v>6092</v>
       </c>
       <c r="JZ24">
-        <v>2528</v>
+        <v>4573</v>
       </c>
       <c r="KA24">
-        <v>162027</v>
+        <v>220065</v>
       </c>
       <c r="KB24">
-        <v>360657</v>
+        <v>473379</v>
       </c>
       <c r="KC24">
-        <v>312024</v>
+        <v>393134</v>
       </c>
       <c r="KD24">
-        <v>251618</v>
+        <v>357306</v>
       </c>
       <c r="KE24">
-        <v>192837</v>
+        <v>309016</v>
       </c>
       <c r="KF24">
-        <v>167235</v>
+        <v>275981</v>
       </c>
       <c r="KG24">
-        <v>134997</v>
+        <v>237828</v>
       </c>
       <c r="KH24">
-        <v>125558</v>
+        <v>234648</v>
       </c>
       <c r="KI24">
-        <v>110516</v>
+        <v>213641</v>
       </c>
       <c r="KJ24">
-        <v>105655</v>
+        <v>199773</v>
       </c>
       <c r="KK24">
-        <v>85303</v>
+        <v>155904</v>
       </c>
       <c r="KL24">
-        <v>61884</v>
+        <v>109288</v>
       </c>
       <c r="KM24">
-        <v>40694</v>
+        <v>68083</v>
       </c>
       <c r="KN24">
-        <v>23383</v>
+        <v>36528</v>
       </c>
       <c r="KO24">
-        <v>19498</v>
+        <v>28142</v>
       </c>
       <c r="KP24">
-        <v>913033</v>
+        <v>854496</v>
       </c>
       <c r="KQ24">
-        <v>2171923</v>
+        <v>2118464</v>
       </c>
       <c r="KR24">
-        <v>2106268</v>
+        <v>1972059</v>
       </c>
       <c r="KS24">
-        <v>2043459</v>
+        <v>1929507</v>
       </c>
       <c r="KT24">
-        <v>1941903</v>
+        <v>1823877</v>
       </c>
       <c r="KU24">
-        <v>1906172</v>
+        <v>1778556</v>
       </c>
       <c r="KV24">
-        <v>1774057</v>
+        <v>1653320</v>
       </c>
       <c r="KW24">
-        <v>1615301</v>
+        <v>1530285</v>
       </c>
       <c r="KX24">
-        <v>1405769</v>
+        <v>1354172</v>
       </c>
       <c r="KY24">
-        <v>1171746</v>
+        <v>1140149</v>
       </c>
       <c r="KZ24">
-        <v>919163</v>
+        <v>906857</v>
       </c>
       <c r="LA24">
-        <v>679269</v>
+        <v>678334</v>
       </c>
       <c r="LB24">
-        <v>472252</v>
+        <v>473836</v>
       </c>
       <c r="LC24">
-        <v>306076</v>
+        <v>309857</v>
       </c>
       <c r="LD24">
-        <v>301261</v>
+        <v>308283</v>
       </c>
       <c r="LE24">
-        <v>2175775</v>
+        <v>2085463</v>
       </c>
       <c r="LF24">
-        <v>5517287</v>
+        <v>5676257</v>
       </c>
       <c r="LG24">
-        <v>5728810</v>
+        <v>5536716</v>
       </c>
       <c r="LH24">
-        <v>6243758</v>
+        <v>6032124</v>
       </c>
       <c r="LI24">
-        <v>6145741</v>
+        <v>6010614</v>
       </c>
       <c r="LJ24">
-        <v>5975333</v>
+        <v>5829172</v>
       </c>
       <c r="LK24">
-        <v>5533809</v>
+        <v>5409113</v>
       </c>
       <c r="LL24">
-        <v>6331044</v>
+        <v>6212184</v>
       </c>
       <c r="LM24">
-        <v>6889913</v>
+        <v>6812820</v>
       </c>
       <c r="LN24">
-        <v>7487847</v>
+        <v>7487886</v>
       </c>
       <c r="LO24">
-        <v>6998083</v>
+        <v>7096285</v>
       </c>
       <c r="LP24">
-        <v>5986733</v>
+        <v>6115329</v>
       </c>
       <c r="LQ24">
-        <v>4493119</v>
+        <v>4634121</v>
       </c>
       <c r="LR24">
-        <v>2835820</v>
+        <v>2963529</v>
       </c>
       <c r="LS24">
-        <v>2957496</v>
+        <v>3120763</v>
       </c>
       <c r="LT24">
-        <v>944649</v>
+        <v>892612</v>
       </c>
       <c r="LU24">
-        <v>2232758</v>
+        <v>2187527</v>
       </c>
       <c r="LV24">
-        <v>2177013</v>
+        <v>2032780</v>
       </c>
       <c r="LW24">
-        <v>2199188</v>
+        <v>1966745</v>
       </c>
       <c r="LX24">
-        <v>2150422</v>
+        <v>1839688</v>
       </c>
       <c r="LY24">
-        <v>2066763</v>
+        <v>1755413</v>
       </c>
       <c r="LZ24">
-        <v>1850987</v>
+        <v>1586588</v>
       </c>
       <c r="MA24">
-        <v>1677655</v>
+        <v>1467518</v>
       </c>
       <c r="MB24">
-        <v>1427031</v>
+        <v>1288651</v>
       </c>
       <c r="MC24">
-        <v>1137336</v>
+        <v>1043527</v>
       </c>
       <c r="MD24">
-        <v>826007</v>
+        <v>779686</v>
       </c>
       <c r="ME24">
-        <v>569087</v>
+        <v>548279</v>
       </c>
       <c r="MF24">
-        <v>361467</v>
+        <v>352522</v>
       </c>
       <c r="MG24">
-        <v>210760</v>
+        <v>209458</v>
       </c>
       <c r="MH24">
-        <v>173205</v>
+        <v>172177</v>
       </c>
       <c r="MI24">
-        <v>2276512</v>
+        <v>2188537</v>
       </c>
       <c r="MJ24">
-        <v>5665956</v>
+        <v>5729531</v>
       </c>
       <c r="MK24">
-        <v>5870639</v>
+        <v>5634818</v>
       </c>
       <c r="ML24">
-        <v>6314130</v>
+        <v>6106227</v>
       </c>
       <c r="MM24">
-        <v>6248560</v>
+        <v>6068703</v>
       </c>
       <c r="MN24">
-        <v>6102566</v>
+        <v>5876191</v>
       </c>
       <c r="MO24">
-        <v>5644034</v>
+        <v>5444584</v>
       </c>
       <c r="MP24">
-        <v>6459806</v>
+        <v>6187403</v>
       </c>
       <c r="MQ24">
-        <v>6839201</v>
+        <v>6626355</v>
       </c>
       <c r="MR24">
-        <v>7259443</v>
+        <v>7103958</v>
       </c>
       <c r="MS24">
-        <v>6544672</v>
+        <v>6529406</v>
       </c>
       <c r="MT24">
-        <v>5366405</v>
+        <v>5441881</v>
       </c>
       <c r="MU24">
-        <v>3846181</v>
+        <v>3932836</v>
       </c>
       <c r="MV24">
-        <v>2180336</v>
+        <v>2275600</v>
       </c>
       <c r="MW24">
-        <v>1741841</v>
+        <v>1861096</v>
       </c>
     </row>
     <row r="25" spans="1:361">
@@ -42903,1084 +42903,1084 @@
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>34697</v>
+        <v>73268</v>
       </c>
       <c r="C25">
-        <v>81614</v>
+        <v>174948</v>
       </c>
       <c r="D25">
-        <v>77794</v>
+        <v>165114</v>
       </c>
       <c r="E25">
-        <v>75579</v>
+        <v>167937</v>
       </c>
       <c r="F25">
-        <v>68875</v>
+        <v>161629</v>
       </c>
       <c r="G25">
-        <v>66096</v>
+        <v>161064</v>
       </c>
       <c r="H25">
-        <v>57699</v>
+        <v>143860</v>
       </c>
       <c r="I25">
-        <v>52610</v>
+        <v>126801</v>
       </c>
       <c r="J25">
-        <v>43949</v>
+        <v>104749</v>
       </c>
       <c r="K25">
-        <v>37712</v>
+        <v>85117</v>
       </c>
       <c r="L25">
-        <v>27632</v>
+        <v>63540</v>
       </c>
       <c r="M25">
-        <v>18423</v>
+        <v>42145</v>
       </c>
       <c r="N25">
-        <v>11514</v>
+        <v>26835</v>
       </c>
       <c r="O25">
-        <v>6783</v>
+        <v>16157</v>
       </c>
       <c r="P25">
-        <v>5987</v>
+        <v>14356</v>
       </c>
       <c r="Q25">
-        <v>34906</v>
+        <v>34605</v>
       </c>
       <c r="R25">
-        <v>86575</v>
+        <v>84778</v>
       </c>
       <c r="S25">
-        <v>87918</v>
+        <v>74627</v>
       </c>
       <c r="T25">
-        <v>94930</v>
+        <v>80777</v>
       </c>
       <c r="U25">
-        <v>83032</v>
+        <v>76992</v>
       </c>
       <c r="V25">
-        <v>77227</v>
+        <v>74218</v>
       </c>
       <c r="W25">
-        <v>69564</v>
+        <v>68320</v>
       </c>
       <c r="X25">
-        <v>71248</v>
+        <v>70839</v>
       </c>
       <c r="Y25">
-        <v>74078</v>
+        <v>73313</v>
       </c>
       <c r="Z25">
-        <v>77969</v>
+        <v>76012</v>
       </c>
       <c r="AA25">
-        <v>68420</v>
+        <v>65286</v>
       </c>
       <c r="AB25">
-        <v>52273</v>
+        <v>48992</v>
       </c>
       <c r="AC25">
-        <v>36054</v>
+        <v>33050</v>
       </c>
       <c r="AD25">
-        <v>21940</v>
+        <v>20066</v>
       </c>
       <c r="AE25">
-        <v>21059</v>
+        <v>19287</v>
       </c>
       <c r="AF25">
-        <v>38028</v>
+        <v>78971</v>
       </c>
       <c r="AG25">
-        <v>88406</v>
+        <v>195436</v>
       </c>
       <c r="AH25">
-        <v>82142</v>
+        <v>185862</v>
       </c>
       <c r="AI25">
-        <v>85944</v>
+        <v>186739</v>
       </c>
       <c r="AJ25">
-        <v>82878</v>
+        <v>178203</v>
       </c>
       <c r="AK25">
-        <v>79558</v>
+        <v>173817</v>
       </c>
       <c r="AL25">
-        <v>67129</v>
+        <v>152002</v>
       </c>
       <c r="AM25">
-        <v>59260</v>
+        <v>132201</v>
       </c>
       <c r="AN25">
-        <v>49218</v>
+        <v>109044</v>
       </c>
       <c r="AO25">
-        <v>39503</v>
+        <v>84938</v>
       </c>
       <c r="AP25">
-        <v>28230</v>
+        <v>60395</v>
       </c>
       <c r="AQ25">
-        <v>17331</v>
+        <v>37603</v>
       </c>
       <c r="AR25">
-        <v>10394</v>
+        <v>21895</v>
       </c>
       <c r="AS25">
-        <v>5112</v>
+        <v>11403</v>
       </c>
       <c r="AT25">
-        <v>3628</v>
+        <v>8307</v>
       </c>
       <c r="AU25">
-        <v>35630</v>
+        <v>35914</v>
       </c>
       <c r="AV25">
-        <v>88091</v>
+        <v>86968</v>
       </c>
       <c r="AW25">
-        <v>88801</v>
+        <v>77089</v>
       </c>
       <c r="AX25">
-        <v>96286</v>
+        <v>81305</v>
       </c>
       <c r="AY25">
-        <v>82486</v>
+        <v>75375</v>
       </c>
       <c r="AZ25">
-        <v>75988</v>
+        <v>72248</v>
       </c>
       <c r="BA25">
-        <v>67598</v>
+        <v>65536</v>
       </c>
       <c r="BB25">
-        <v>68893</v>
+        <v>67306</v>
       </c>
       <c r="BC25">
-        <v>68959</v>
+        <v>67880</v>
       </c>
       <c r="BD25">
-        <v>70139</v>
+        <v>68402</v>
       </c>
       <c r="BE25">
-        <v>58814</v>
+        <v>56959</v>
       </c>
       <c r="BF25">
-        <v>44345</v>
+        <v>41512</v>
       </c>
       <c r="BG25">
-        <v>30325</v>
+        <v>27199</v>
       </c>
       <c r="BH25">
-        <v>17495</v>
+        <v>15225</v>
       </c>
       <c r="BI25">
-        <v>13815</v>
+        <v>11718</v>
       </c>
       <c r="BJ25">
-        <v>11265</v>
+        <v>15009</v>
       </c>
       <c r="BK25">
-        <v>26108</v>
+        <v>38168</v>
       </c>
       <c r="BL25">
-        <v>25488</v>
+        <v>36401</v>
       </c>
       <c r="BM25">
-        <v>26789</v>
+        <v>35130</v>
       </c>
       <c r="BN25">
-        <v>23954</v>
+        <v>31187</v>
       </c>
       <c r="BO25">
-        <v>23059</v>
+        <v>28543</v>
       </c>
       <c r="BP25">
-        <v>20641</v>
+        <v>24953</v>
       </c>
       <c r="BQ25">
-        <v>18084</v>
+        <v>22049</v>
       </c>
       <c r="BR25">
-        <v>14874</v>
+        <v>17896</v>
       </c>
       <c r="BS25">
-        <v>12868</v>
+        <v>14557</v>
       </c>
       <c r="BT25">
-        <v>9679</v>
+        <v>10951</v>
       </c>
       <c r="BU25">
-        <v>6826</v>
+        <v>7468</v>
       </c>
       <c r="BV25">
-        <v>4649</v>
+        <v>5086</v>
       </c>
       <c r="BW25">
-        <v>2731</v>
+        <v>3013</v>
       </c>
       <c r="BX25">
-        <v>2528</v>
+        <v>2882</v>
       </c>
       <c r="BY25">
-        <v>250756</v>
+        <v>255281</v>
       </c>
       <c r="BZ25">
-        <v>668634</v>
+        <v>756074</v>
       </c>
       <c r="CA25">
-        <v>787417</v>
+        <v>851913</v>
       </c>
       <c r="CB25">
-        <v>928999</v>
+        <v>932902</v>
       </c>
       <c r="CC25">
-        <v>934084</v>
+        <v>925030</v>
       </c>
       <c r="CD25">
-        <v>881397</v>
+        <v>876957</v>
       </c>
       <c r="CE25">
-        <v>799416</v>
+        <v>799657</v>
       </c>
       <c r="CF25">
-        <v>759274</v>
+        <v>788253</v>
       </c>
       <c r="CG25">
-        <v>651719</v>
+        <v>676966</v>
       </c>
       <c r="CH25">
-        <v>602719</v>
+        <v>616385</v>
       </c>
       <c r="CI25">
-        <v>544726</v>
+        <v>559747</v>
       </c>
       <c r="CJ25">
-        <v>450061</v>
+        <v>452265</v>
       </c>
       <c r="CK25">
-        <v>309784</v>
+        <v>310202</v>
       </c>
       <c r="CL25">
-        <v>192981</v>
+        <v>191837</v>
       </c>
       <c r="CM25">
-        <v>207063</v>
+        <v>197484</v>
       </c>
       <c r="CN25">
-        <v>11936</v>
+        <v>16106</v>
       </c>
       <c r="CO25">
-        <v>27175</v>
+        <v>38375</v>
       </c>
       <c r="CP25">
-        <v>25159</v>
+        <v>35741</v>
       </c>
       <c r="CQ25">
-        <v>25841</v>
+        <v>34095</v>
       </c>
       <c r="CR25">
-        <v>24836</v>
+        <v>30912</v>
       </c>
       <c r="CS25">
-        <v>23501</v>
+        <v>27346</v>
       </c>
       <c r="CT25">
-        <v>20258</v>
+        <v>23207</v>
       </c>
       <c r="CU25">
-        <v>17651</v>
+        <v>20341</v>
       </c>
       <c r="CV25">
-        <v>14445</v>
+        <v>16355</v>
       </c>
       <c r="CW25">
-        <v>11748</v>
+        <v>12712</v>
       </c>
       <c r="CX25">
-        <v>8386</v>
+        <v>9073</v>
       </c>
       <c r="CY25">
-        <v>5588</v>
+        <v>5968</v>
       </c>
       <c r="CZ25">
-        <v>3304</v>
+        <v>3576</v>
       </c>
       <c r="DA25">
-        <v>1842</v>
+        <v>1963</v>
       </c>
       <c r="DB25">
-        <v>1376</v>
+        <v>1548</v>
       </c>
       <c r="DC25">
-        <v>252458</v>
+        <v>257746</v>
       </c>
       <c r="DD25">
-        <v>674982</v>
+        <v>762273</v>
       </c>
       <c r="DE25">
-        <v>757485</v>
+        <v>833544</v>
       </c>
       <c r="DF25">
-        <v>875984</v>
+        <v>877232</v>
       </c>
       <c r="DG25">
-        <v>871798</v>
+        <v>837931</v>
       </c>
       <c r="DH25">
-        <v>795586</v>
+        <v>761849</v>
       </c>
       <c r="DI25">
-        <v>707688</v>
+        <v>686560</v>
       </c>
       <c r="DJ25">
-        <v>675062</v>
+        <v>672168</v>
       </c>
       <c r="DK25">
-        <v>568459</v>
+        <v>572103</v>
       </c>
       <c r="DL25">
-        <v>514711</v>
+        <v>513000</v>
       </c>
       <c r="DM25">
-        <v>443460</v>
+        <v>445551</v>
       </c>
       <c r="DN25">
-        <v>348199</v>
+        <v>346693</v>
       </c>
       <c r="DO25">
-        <v>241192</v>
+        <v>235107</v>
       </c>
       <c r="DP25">
-        <v>147636</v>
+        <v>144274</v>
       </c>
       <c r="DQ25">
-        <v>132195</v>
+        <v>122830</v>
       </c>
       <c r="DR25">
-        <v>57124</v>
+        <v>69471</v>
       </c>
       <c r="DS25">
-        <v>132648</v>
+        <v>175509</v>
       </c>
       <c r="DT25">
-        <v>123799</v>
+        <v>161266</v>
       </c>
       <c r="DU25">
-        <v>132875</v>
+        <v>165239</v>
       </c>
       <c r="DV25">
-        <v>123607</v>
+        <v>145715</v>
       </c>
       <c r="DW25">
-        <v>119777</v>
+        <v>133482</v>
       </c>
       <c r="DX25">
-        <v>103519</v>
+        <v>111480</v>
       </c>
       <c r="DY25">
-        <v>87980</v>
+        <v>95861</v>
       </c>
       <c r="DZ25">
-        <v>76243</v>
+        <v>82159</v>
       </c>
       <c r="EA25">
-        <v>62681</v>
+        <v>65761</v>
       </c>
       <c r="EB25">
-        <v>48534</v>
+        <v>50314</v>
       </c>
       <c r="EC25">
-        <v>34635</v>
+        <v>35883</v>
       </c>
       <c r="ED25">
-        <v>22951</v>
+        <v>23903</v>
       </c>
       <c r="EE25">
-        <v>14216</v>
+        <v>14881</v>
       </c>
       <c r="EF25">
-        <v>13152</v>
+        <v>14405</v>
       </c>
       <c r="EG25">
-        <v>579264</v>
+        <v>563350</v>
       </c>
       <c r="EH25">
-        <v>1483995</v>
+        <v>1534565</v>
       </c>
       <c r="EI25">
-        <v>1557953</v>
+        <v>1467591</v>
       </c>
       <c r="EJ25">
-        <v>1744314</v>
+        <v>1596683</v>
       </c>
       <c r="EK25">
-        <v>1523802</v>
+        <v>1480308</v>
       </c>
       <c r="EL25">
-        <v>1462633</v>
+        <v>1433778</v>
       </c>
       <c r="EM25">
-        <v>1319815</v>
+        <v>1285165</v>
       </c>
       <c r="EN25">
-        <v>1359150</v>
+        <v>1329741</v>
       </c>
       <c r="EO25">
-        <v>1350544</v>
+        <v>1342003</v>
       </c>
       <c r="EP25">
-        <v>1340128</v>
+        <v>1340121</v>
       </c>
       <c r="EQ25">
-        <v>1159620</v>
+        <v>1176831</v>
       </c>
       <c r="ER25">
-        <v>889340</v>
+        <v>903508</v>
       </c>
       <c r="ES25">
-        <v>588266</v>
+        <v>589632</v>
       </c>
       <c r="ET25">
-        <v>364887</v>
+        <v>365335</v>
       </c>
       <c r="EU25">
-        <v>345966</v>
+        <v>343864</v>
       </c>
       <c r="EV25">
-        <v>59444</v>
+        <v>72831</v>
       </c>
       <c r="EW25">
-        <v>138418</v>
+        <v>182217</v>
       </c>
       <c r="EX25">
-        <v>127756</v>
+        <v>165207</v>
       </c>
       <c r="EY25">
-        <v>134810</v>
+        <v>160266</v>
       </c>
       <c r="EZ25">
-        <v>120621</v>
+        <v>138534</v>
       </c>
       <c r="FA25">
-        <v>111604</v>
+        <v>124095</v>
       </c>
       <c r="FB25">
-        <v>91966</v>
+        <v>100345</v>
       </c>
       <c r="FC25">
-        <v>77306</v>
+        <v>86037</v>
       </c>
       <c r="FD25">
-        <v>67789</v>
+        <v>72671</v>
       </c>
       <c r="FE25">
-        <v>55092</v>
+        <v>57794</v>
       </c>
       <c r="FF25">
-        <v>41343</v>
+        <v>42876</v>
       </c>
       <c r="FG25">
-        <v>27401</v>
+        <v>28595</v>
       </c>
       <c r="FH25">
-        <v>16842</v>
+        <v>17197</v>
       </c>
       <c r="FI25">
-        <v>9496</v>
+        <v>9798</v>
       </c>
       <c r="FJ25">
-        <v>7160</v>
+        <v>7416</v>
       </c>
       <c r="FK25">
-        <v>588661</v>
+        <v>581019</v>
       </c>
       <c r="FL25">
-        <v>1475455</v>
+        <v>1518262</v>
       </c>
       <c r="FM25">
-        <v>1538490</v>
+        <v>1410681</v>
       </c>
       <c r="FN25">
-        <v>1702701</v>
+        <v>1462456</v>
       </c>
       <c r="FO25">
-        <v>1433788</v>
+        <v>1320977</v>
       </c>
       <c r="FP25">
-        <v>1335114</v>
+        <v>1265031</v>
       </c>
       <c r="FQ25">
-        <v>1175482</v>
+        <v>1129049</v>
       </c>
       <c r="FR25">
-        <v>1208919</v>
+        <v>1165492</v>
       </c>
       <c r="FS25">
-        <v>1180266</v>
+        <v>1152541</v>
       </c>
       <c r="FT25">
-        <v>1138757</v>
+        <v>1120026</v>
       </c>
       <c r="FU25">
-        <v>925613</v>
+        <v>936202</v>
       </c>
       <c r="FV25">
-        <v>645352</v>
+        <v>663805</v>
       </c>
       <c r="FW25">
-        <v>397829</v>
+        <v>400595</v>
       </c>
       <c r="FX25">
-        <v>216821</v>
+        <v>218759</v>
       </c>
       <c r="FY25">
-        <v>159553</v>
+        <v>160389</v>
       </c>
       <c r="FZ25">
-        <v>3820</v>
+        <v>4301</v>
       </c>
       <c r="GA25">
-        <v>8957</v>
+        <v>10881</v>
       </c>
       <c r="GB25">
-        <v>8577</v>
+        <v>9884</v>
       </c>
       <c r="GC25">
-        <v>8952</v>
+        <v>9493</v>
       </c>
       <c r="GD25">
-        <v>8614</v>
+        <v>8575</v>
       </c>
       <c r="GE25">
-        <v>8415</v>
+        <v>8200</v>
       </c>
       <c r="GF25">
-        <v>7073</v>
+        <v>7067</v>
       </c>
       <c r="GG25">
-        <v>6122</v>
+        <v>6023</v>
       </c>
       <c r="GH25">
-        <v>5216</v>
+        <v>5202</v>
       </c>
       <c r="GI25">
-        <v>4113</v>
+        <v>4094</v>
       </c>
       <c r="GJ25">
-        <v>2960</v>
+        <v>2998</v>
       </c>
       <c r="GK25">
-        <v>1990</v>
+        <v>1983</v>
       </c>
       <c r="GL25">
-        <v>1196</v>
+        <v>1261</v>
       </c>
       <c r="GM25">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="GN25">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="GO25">
-        <v>9222</v>
+        <v>9780</v>
       </c>
       <c r="GP25">
-        <v>21896</v>
+        <v>27012</v>
       </c>
       <c r="GQ25">
-        <v>22898</v>
+        <v>26780</v>
       </c>
       <c r="GR25">
-        <v>26307</v>
+        <v>26906</v>
       </c>
       <c r="GS25">
-        <v>25949</v>
+        <v>25265</v>
       </c>
       <c r="GT25">
-        <v>24202</v>
+        <v>23459</v>
       </c>
       <c r="GU25">
-        <v>20088</v>
+        <v>20038</v>
       </c>
       <c r="GV25">
-        <v>18740</v>
+        <v>18884</v>
       </c>
       <c r="GW25">
-        <v>18274</v>
+        <v>17973</v>
       </c>
       <c r="GX25">
-        <v>17116</v>
+        <v>16866</v>
       </c>
       <c r="GY25">
-        <v>14263</v>
+        <v>13568</v>
       </c>
       <c r="GZ25">
-        <v>10789</v>
+        <v>9954</v>
       </c>
       <c r="HA25">
-        <v>7431</v>
+        <v>6497</v>
       </c>
       <c r="HB25">
-        <v>4280</v>
+        <v>3799</v>
       </c>
       <c r="HC25">
-        <v>4163</v>
+        <v>3619</v>
       </c>
       <c r="HD25">
-        <v>4114</v>
+        <v>4664</v>
       </c>
       <c r="HE25">
-        <v>9025</v>
+        <v>11142</v>
       </c>
       <c r="HF25">
-        <v>8683</v>
+        <v>10168</v>
       </c>
       <c r="HG25">
-        <v>10189</v>
+        <v>9529</v>
       </c>
       <c r="HH25">
-        <v>10938</v>
+        <v>8587</v>
       </c>
       <c r="HI25">
-        <v>10415</v>
+        <v>8044</v>
       </c>
       <c r="HJ25">
-        <v>7970</v>
+        <v>6426</v>
       </c>
       <c r="HK25">
-        <v>6468</v>
+        <v>5736</v>
       </c>
       <c r="HL25">
-        <v>5360</v>
+        <v>4821</v>
       </c>
       <c r="HM25">
-        <v>4050</v>
+        <v>3709</v>
       </c>
       <c r="HN25">
-        <v>2724</v>
+        <v>2526</v>
       </c>
       <c r="HO25">
-        <v>1684</v>
+        <v>1567</v>
       </c>
       <c r="HP25">
-        <v>1029</v>
+        <v>950</v>
       </c>
       <c r="HQ25">
-        <v>496</v>
+        <v>531</v>
       </c>
       <c r="HR25">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="HS25">
-        <v>9232</v>
+        <v>10068</v>
       </c>
       <c r="HT25">
-        <v>22068</v>
+        <v>27460</v>
       </c>
       <c r="HU25">
-        <v>22913</v>
+        <v>27391</v>
       </c>
       <c r="HV25">
-        <v>26932</v>
+        <v>27678</v>
       </c>
       <c r="HW25">
-        <v>27076</v>
+        <v>25842</v>
       </c>
       <c r="HX25">
-        <v>25242</v>
+        <v>23339</v>
       </c>
       <c r="HY25">
-        <v>20798</v>
+        <v>19831</v>
       </c>
       <c r="HZ25">
-        <v>19274</v>
+        <v>18359</v>
       </c>
       <c r="IA25">
-        <v>17816</v>
+        <v>16878</v>
       </c>
       <c r="IB25">
-        <v>16628</v>
+        <v>15375</v>
       </c>
       <c r="IC25">
-        <v>13228</v>
+        <v>12168</v>
       </c>
       <c r="ID25">
-        <v>9849</v>
+        <v>8660</v>
       </c>
       <c r="IE25">
-        <v>6609</v>
+        <v>5465</v>
       </c>
       <c r="IF25">
-        <v>3541</v>
+        <v>2835</v>
       </c>
       <c r="IG25">
-        <v>2924</v>
+        <v>2145</v>
       </c>
       <c r="IH25">
-        <v>42296</v>
+        <v>80165</v>
       </c>
       <c r="II25">
-        <v>94675</v>
+        <v>176445</v>
       </c>
       <c r="IJ25">
-        <v>83872</v>
+        <v>149023</v>
       </c>
       <c r="IK25">
-        <v>75827</v>
+        <v>140671</v>
       </c>
       <c r="IL25">
-        <v>65521</v>
+        <v>123141</v>
       </c>
       <c r="IM25">
-        <v>61075</v>
+        <v>111503</v>
       </c>
       <c r="IN25">
-        <v>50614</v>
+        <v>91942</v>
       </c>
       <c r="IO25">
-        <v>40252</v>
+        <v>77798</v>
       </c>
       <c r="IP25">
-        <v>33358</v>
+        <v>63580</v>
       </c>
       <c r="IQ25">
-        <v>28331</v>
+        <v>51815</v>
       </c>
       <c r="IR25">
-        <v>21409</v>
+        <v>38708</v>
       </c>
       <c r="IS25">
-        <v>14254</v>
+        <v>27137</v>
       </c>
       <c r="IT25">
-        <v>9535</v>
+        <v>17405</v>
       </c>
       <c r="IU25">
-        <v>5592</v>
+        <v>10283</v>
       </c>
       <c r="IV25">
-        <v>5017</v>
+        <v>8861</v>
       </c>
       <c r="IW25">
-        <v>165469</v>
+        <v>222279</v>
       </c>
       <c r="IX25">
-        <v>370051</v>
+        <v>500722</v>
       </c>
       <c r="IY25">
-        <v>326573</v>
+        <v>431141</v>
       </c>
       <c r="IZ25">
-        <v>284111</v>
+        <v>406815</v>
       </c>
       <c r="JA25">
-        <v>224010</v>
+        <v>357693</v>
       </c>
       <c r="JB25">
-        <v>195798</v>
+        <v>325459</v>
       </c>
       <c r="JC25">
-        <v>158518</v>
+        <v>277243</v>
       </c>
       <c r="JD25">
-        <v>143456</v>
+        <v>271331</v>
       </c>
       <c r="JE25">
-        <v>123846</v>
+        <v>249313</v>
       </c>
       <c r="JF25">
-        <v>119742</v>
+        <v>242475</v>
       </c>
       <c r="JG25">
-        <v>99950</v>
+        <v>199500</v>
       </c>
       <c r="JH25">
-        <v>75101</v>
+        <v>145303</v>
       </c>
       <c r="JI25">
-        <v>53031</v>
+        <v>98289</v>
       </c>
       <c r="JJ25">
-        <v>32838</v>
+        <v>57228</v>
       </c>
       <c r="JK25">
-        <v>33105</v>
+        <v>52811</v>
       </c>
       <c r="JL25">
-        <v>44761</v>
+        <v>83777</v>
       </c>
       <c r="JM25">
-        <v>97611</v>
+        <v>181425</v>
       </c>
       <c r="JN25">
-        <v>87207</v>
+        <v>150386</v>
       </c>
       <c r="JO25">
-        <v>76612</v>
+        <v>135358</v>
       </c>
       <c r="JP25">
-        <v>65596</v>
+        <v>115754</v>
       </c>
       <c r="JQ25">
-        <v>60141</v>
+        <v>102820</v>
       </c>
       <c r="JR25">
-        <v>48692</v>
+        <v>84061</v>
       </c>
       <c r="JS25">
-        <v>38094</v>
+        <v>69833</v>
       </c>
       <c r="JT25">
-        <v>31026</v>
+        <v>56123</v>
       </c>
       <c r="JU25">
-        <v>25058</v>
+        <v>43879</v>
       </c>
       <c r="JV25">
-        <v>18090</v>
+        <v>31814</v>
       </c>
       <c r="JW25">
-        <v>11211</v>
+        <v>20260</v>
       </c>
       <c r="JX25">
-        <v>6960</v>
+        <v>12463</v>
       </c>
       <c r="JY25">
-        <v>3716</v>
+        <v>6639</v>
       </c>
       <c r="JZ25">
-        <v>2790</v>
+        <v>4966</v>
       </c>
       <c r="KA25">
-        <v>169005</v>
+        <v>226828</v>
       </c>
       <c r="KB25">
-        <v>372831</v>
+        <v>495594</v>
       </c>
       <c r="KC25">
-        <v>324590</v>
+        <v>406664</v>
       </c>
       <c r="KD25">
-        <v>269241</v>
+        <v>368184</v>
       </c>
       <c r="KE25">
-        <v>201934</v>
+        <v>317638</v>
       </c>
       <c r="KF25">
-        <v>174897</v>
+        <v>285469</v>
       </c>
       <c r="KG25">
-        <v>140022</v>
+        <v>243307</v>
       </c>
       <c r="KH25">
-        <v>128661</v>
+        <v>237451</v>
       </c>
       <c r="KI25">
-        <v>110148</v>
+        <v>212328</v>
       </c>
       <c r="KJ25">
-        <v>107292</v>
+        <v>204496</v>
       </c>
       <c r="KK25">
-        <v>89422</v>
+        <v>165082</v>
       </c>
       <c r="KL25">
-        <v>65111</v>
+        <v>116034</v>
       </c>
       <c r="KM25">
-        <v>44157</v>
+        <v>74898</v>
       </c>
       <c r="KN25">
-        <v>25574</v>
+        <v>40844</v>
       </c>
       <c r="KO25">
-        <v>21700</v>
+        <v>32133</v>
       </c>
       <c r="KP25">
-        <v>939385</v>
+        <v>877984</v>
       </c>
       <c r="KQ25">
-        <v>2245801</v>
+        <v>2188830</v>
       </c>
       <c r="KR25">
-        <v>2151398</v>
+        <v>2037463</v>
       </c>
       <c r="KS25">
-        <v>2115951</v>
+        <v>1997102</v>
       </c>
       <c r="KT25">
-        <v>1971825</v>
+        <v>1864346</v>
       </c>
       <c r="KU25">
-        <v>1952237</v>
+        <v>1827156</v>
       </c>
       <c r="KV25">
-        <v>1810222</v>
+        <v>1689629</v>
       </c>
       <c r="KW25">
-        <v>1664032</v>
+        <v>1572508</v>
       </c>
       <c r="KX25">
-        <v>1443407</v>
+        <v>1388617</v>
       </c>
       <c r="KY25">
-        <v>1224589</v>
+        <v>1189663</v>
       </c>
       <c r="KZ25">
-        <v>964212</v>
+        <v>950479</v>
       </c>
       <c r="LA25">
-        <v>713962</v>
+        <v>712966</v>
       </c>
       <c r="LB25">
-        <v>504128</v>
+        <v>505907</v>
       </c>
       <c r="LC25">
-        <v>323979</v>
+        <v>329363</v>
       </c>
       <c r="LD25">
-        <v>317252</v>
+        <v>325901</v>
       </c>
       <c r="LE25">
-        <v>2167371</v>
+        <v>2077202</v>
       </c>
       <c r="LF25">
-        <v>5515503</v>
+        <v>5613911</v>
       </c>
       <c r="LG25">
-        <v>5673721</v>
+        <v>5534683</v>
       </c>
       <c r="LH25">
-        <v>6214430</v>
+        <v>5982329</v>
       </c>
       <c r="LI25">
-        <v>6156875</v>
+        <v>6015298</v>
       </c>
       <c r="LJ25">
-        <v>6065475</v>
+        <v>5915693</v>
       </c>
       <c r="LK25">
-        <v>5553639</v>
+        <v>5419963</v>
       </c>
       <c r="LL25">
-        <v>6184962</v>
+        <v>6061213</v>
       </c>
       <c r="LM25">
-        <v>6630899</v>
+        <v>6544154</v>
       </c>
       <c r="LN25">
-        <v>7404173</v>
+        <v>7384168</v>
       </c>
       <c r="LO25">
-        <v>7081380</v>
+        <v>7164723</v>
       </c>
       <c r="LP25">
-        <v>6063494</v>
+        <v>6183300</v>
       </c>
       <c r="LQ25">
-        <v>4672643</v>
+        <v>4812619</v>
       </c>
       <c r="LR25">
-        <v>3012829</v>
+        <v>3149774</v>
       </c>
       <c r="LS25">
-        <v>2978309</v>
+        <v>3156928</v>
       </c>
       <c r="LT25">
-        <v>978815</v>
+        <v>921087</v>
       </c>
       <c r="LU25">
-        <v>2313622</v>
+        <v>2267519</v>
       </c>
       <c r="LV25">
-        <v>2219248</v>
+        <v>2109875</v>
       </c>
       <c r="LW25">
-        <v>2255919</v>
+        <v>2044925</v>
       </c>
       <c r="LX25">
-        <v>2184008</v>
+        <v>1893200</v>
       </c>
       <c r="LY25">
-        <v>2122726</v>
+        <v>1806916</v>
       </c>
       <c r="LZ25">
-        <v>1900356</v>
+        <v>1629086</v>
       </c>
       <c r="MA25">
-        <v>1719002</v>
+        <v>1498805</v>
       </c>
       <c r="MB25">
-        <v>1471478</v>
+        <v>1321745</v>
       </c>
       <c r="MC25">
-        <v>1193256</v>
+        <v>1091686</v>
       </c>
       <c r="MD25">
-        <v>873757</v>
+        <v>820872</v>
       </c>
       <c r="ME25">
-        <v>599458</v>
+        <v>577141</v>
       </c>
       <c r="MF25">
-        <v>391057</v>
+        <v>380358</v>
       </c>
       <c r="MG25">
-        <v>223863</v>
+        <v>223504</v>
       </c>
       <c r="MH25">
-        <v>184762</v>
+        <v>184131</v>
       </c>
       <c r="MI25">
-        <v>2263928</v>
+        <v>2178702</v>
       </c>
       <c r="MJ25">
-        <v>5679162</v>
+        <v>5692067</v>
       </c>
       <c r="MK25">
-        <v>5817556</v>
+        <v>5633301</v>
       </c>
       <c r="ML25">
-        <v>6303806</v>
+        <v>6065690</v>
       </c>
       <c r="MM25">
-        <v>6243709</v>
+        <v>6069291</v>
       </c>
       <c r="MN25">
-        <v>6191018</v>
+        <v>5964780</v>
       </c>
       <c r="MO25">
-        <v>5661225</v>
+        <v>5454875</v>
       </c>
       <c r="MP25">
-        <v>6304090</v>
+        <v>6038062</v>
       </c>
       <c r="MQ25">
-        <v>6601067</v>
+        <v>6375003</v>
       </c>
       <c r="MR25">
-        <v>7177060</v>
+        <v>7006689</v>
       </c>
       <c r="MS25">
-        <v>6635274</v>
+        <v>6590294</v>
       </c>
       <c r="MT25">
-        <v>5428953</v>
+        <v>5491834</v>
       </c>
       <c r="MU25">
-        <v>4009224</v>
+        <v>4094439</v>
       </c>
       <c r="MV25">
-        <v>2335874</v>
+        <v>2436125</v>
       </c>
       <c r="MW25">
-        <v>1789951</v>
+        <v>1917778</v>
       </c>
     </row>
     <row r="26" spans="1:361">
@@ -43988,1084 +43988,2169 @@
         <v>2024</v>
       </c>
       <c r="B26">
-        <v>37832</v>
+        <v>77277</v>
       </c>
       <c r="C26">
-        <v>89993</v>
+        <v>187788</v>
       </c>
       <c r="D26">
-        <v>84834</v>
+        <v>175389</v>
       </c>
       <c r="E26">
-        <v>82999</v>
+        <v>176697</v>
       </c>
       <c r="F26">
-        <v>73529</v>
+        <v>168000</v>
       </c>
       <c r="G26">
-        <v>69440</v>
+        <v>165437</v>
       </c>
       <c r="H26">
-        <v>60176</v>
+        <v>149743</v>
       </c>
       <c r="I26">
-        <v>54466</v>
+        <v>131077</v>
       </c>
       <c r="J26">
-        <v>45371</v>
+        <v>108971</v>
       </c>
       <c r="K26">
-        <v>39580</v>
+        <v>89209</v>
       </c>
       <c r="L26">
-        <v>29599</v>
+        <v>67791</v>
       </c>
       <c r="M26">
-        <v>19869</v>
+        <v>45512</v>
       </c>
       <c r="N26">
-        <v>12562</v>
+        <v>29054</v>
       </c>
       <c r="O26">
-        <v>7457</v>
+        <v>17660</v>
       </c>
       <c r="P26">
-        <v>6425</v>
+        <v>15480</v>
       </c>
       <c r="Q26">
+        <v>34907</v>
+      </c>
+      <c r="R26">
+        <v>85685</v>
+      </c>
+      <c r="S26">
+        <v>76037</v>
+      </c>
+      <c r="T26">
+        <v>79429</v>
+      </c>
+      <c r="U26">
+        <v>78162</v>
+      </c>
+      <c r="V26">
+        <v>75231</v>
+      </c>
+      <c r="W26">
+        <v>68748</v>
+      </c>
+      <c r="X26">
+        <v>69871</v>
+      </c>
+      <c r="Y26">
+        <v>71554</v>
+      </c>
+      <c r="Z26">
+        <v>76487</v>
+      </c>
+      <c r="AA26">
+        <v>67622</v>
+      </c>
+      <c r="AB26">
+        <v>51750</v>
+      </c>
+      <c r="AC26">
+        <v>35874</v>
+      </c>
+      <c r="AD26">
+        <v>21641</v>
+      </c>
+      <c r="AE26">
+        <v>21546</v>
+      </c>
+      <c r="AF26">
+        <v>84523</v>
+      </c>
+      <c r="AG26">
+        <v>211698</v>
+      </c>
+      <c r="AH26">
+        <v>199812</v>
+      </c>
+      <c r="AI26">
+        <v>198613</v>
+      </c>
+      <c r="AJ26">
+        <v>186646</v>
+      </c>
+      <c r="AK26">
+        <v>180417</v>
+      </c>
+      <c r="AL26">
+        <v>158483</v>
+      </c>
+      <c r="AM26">
+        <v>136736</v>
+      </c>
+      <c r="AN26">
+        <v>112743</v>
+      </c>
+      <c r="AO26">
+        <v>89515</v>
+      </c>
+      <c r="AP26">
+        <v>64730</v>
+      </c>
+      <c r="AQ26">
+        <v>40848</v>
+      </c>
+      <c r="AR26">
+        <v>24205</v>
+      </c>
+      <c r="AS26">
+        <v>12388</v>
+      </c>
+      <c r="AT26">
+        <v>9116</v>
+      </c>
+      <c r="AU26">
+        <v>35877</v>
+      </c>
+      <c r="AV26">
+        <v>87997</v>
+      </c>
+      <c r="AW26">
+        <v>78569</v>
+      </c>
+      <c r="AX26">
+        <v>80716</v>
+      </c>
+      <c r="AY26">
+        <v>76680</v>
+      </c>
+      <c r="AZ26">
+        <v>72844</v>
+      </c>
+      <c r="BA26">
+        <v>66378</v>
+      </c>
+      <c r="BB26">
+        <v>66410</v>
+      </c>
+      <c r="BC26">
+        <v>66407</v>
+      </c>
+      <c r="BD26">
+        <v>69171</v>
+      </c>
+      <c r="BE26">
+        <v>59059</v>
+      </c>
+      <c r="BF26">
+        <v>43623</v>
+      </c>
+      <c r="BG26">
+        <v>29746</v>
+      </c>
+      <c r="BH26">
+        <v>16793</v>
+      </c>
+      <c r="BI26">
+        <v>13266</v>
+      </c>
+      <c r="BJ26">
+        <v>15752</v>
+      </c>
+      <c r="BK26">
+        <v>38852</v>
+      </c>
+      <c r="BL26">
+        <v>38304</v>
+      </c>
+      <c r="BM26">
+        <v>36980</v>
+      </c>
+      <c r="BN26">
+        <v>32702</v>
+      </c>
+      <c r="BO26">
+        <v>29610</v>
+      </c>
+      <c r="BP26">
+        <v>26068</v>
+      </c>
+      <c r="BQ26">
+        <v>22833</v>
+      </c>
+      <c r="BR26">
+        <v>18752</v>
+      </c>
+      <c r="BS26">
+        <v>15190</v>
+      </c>
+      <c r="BT26">
+        <v>11660</v>
+      </c>
+      <c r="BU26">
+        <v>8048</v>
+      </c>
+      <c r="BV26">
+        <v>5518</v>
+      </c>
+      <c r="BW26">
+        <v>3248</v>
+      </c>
+      <c r="BX26">
+        <v>3115</v>
+      </c>
+      <c r="BY26">
+        <v>257723</v>
+      </c>
+      <c r="BZ26">
+        <v>773801</v>
+      </c>
+      <c r="CA26">
+        <v>903005</v>
+      </c>
+      <c r="CB26">
+        <v>965438</v>
+      </c>
+      <c r="CC26">
+        <v>966766</v>
+      </c>
+      <c r="CD26">
+        <v>911169</v>
+      </c>
+      <c r="CE26">
+        <v>817934</v>
+      </c>
+      <c r="CF26">
+        <v>805038</v>
+      </c>
+      <c r="CG26">
+        <v>698403</v>
+      </c>
+      <c r="CH26">
+        <v>641120</v>
+      </c>
+      <c r="CI26">
+        <v>578376</v>
+      </c>
+      <c r="CJ26">
+        <v>473775</v>
+      </c>
+      <c r="CK26">
+        <v>340247</v>
+      </c>
+      <c r="CL26">
+        <v>205856</v>
+      </c>
+      <c r="CM26">
+        <v>212339</v>
+      </c>
+      <c r="CN26">
+        <v>16969</v>
+      </c>
+      <c r="CO26">
+        <v>39688</v>
+      </c>
+      <c r="CP26">
+        <v>37877</v>
+      </c>
+      <c r="CQ26">
+        <v>35942</v>
+      </c>
+      <c r="CR26">
+        <v>32371</v>
+      </c>
+      <c r="CS26">
+        <v>28771</v>
+      </c>
+      <c r="CT26">
+        <v>24217</v>
+      </c>
+      <c r="CU26">
+        <v>21029</v>
+      </c>
+      <c r="CV26">
+        <v>17109</v>
+      </c>
+      <c r="CW26">
+        <v>13387</v>
+      </c>
+      <c r="CX26">
+        <v>9707</v>
+      </c>
+      <c r="CY26">
+        <v>6324</v>
+      </c>
+      <c r="CZ26">
+        <v>4014</v>
+      </c>
+      <c r="DA26">
+        <v>2075</v>
+      </c>
+      <c r="DB26">
+        <v>1656</v>
+      </c>
+      <c r="DC26">
+        <v>263437</v>
+      </c>
+      <c r="DD26">
+        <v>787984</v>
+      </c>
+      <c r="DE26">
+        <v>879682</v>
+      </c>
+      <c r="DF26">
+        <v>913243</v>
+      </c>
+      <c r="DG26">
+        <v>886066</v>
+      </c>
+      <c r="DH26">
+        <v>805783</v>
+      </c>
+      <c r="DI26">
+        <v>702028</v>
+      </c>
+      <c r="DJ26">
+        <v>688338</v>
+      </c>
+      <c r="DK26">
+        <v>589050</v>
+      </c>
+      <c r="DL26">
+        <v>534446</v>
+      </c>
+      <c r="DM26">
+        <v>460557</v>
+      </c>
+      <c r="DN26">
+        <v>364377</v>
+      </c>
+      <c r="DO26">
+        <v>255401</v>
+      </c>
+      <c r="DP26">
+        <v>153657</v>
+      </c>
+      <c r="DQ26">
+        <v>134517</v>
+      </c>
+      <c r="DR26">
+        <v>73310</v>
+      </c>
+      <c r="DS26">
+        <v>182165</v>
+      </c>
+      <c r="DT26">
+        <v>170002</v>
+      </c>
+      <c r="DU26">
+        <v>171865</v>
+      </c>
+      <c r="DV26">
+        <v>154465</v>
+      </c>
+      <c r="DW26">
+        <v>138074</v>
+      </c>
+      <c r="DX26">
+        <v>118196</v>
+      </c>
+      <c r="DY26">
+        <v>99776</v>
+      </c>
+      <c r="DZ26">
+        <v>84870</v>
+      </c>
+      <c r="EA26">
+        <v>70232</v>
+      </c>
+      <c r="EB26">
+        <v>53483</v>
+      </c>
+      <c r="EC26">
+        <v>38444</v>
+      </c>
+      <c r="ED26">
+        <v>25941</v>
+      </c>
+      <c r="EE26">
+        <v>15783</v>
+      </c>
+      <c r="EF26">
+        <v>15338</v>
+      </c>
+      <c r="EG26">
+        <v>571138</v>
+      </c>
+      <c r="EH26">
+        <v>1519251</v>
+      </c>
+      <c r="EI26">
+        <v>1487650</v>
+      </c>
+      <c r="EJ26">
+        <v>1598964</v>
+      </c>
+      <c r="EK26">
+        <v>1519234</v>
+      </c>
+      <c r="EL26">
+        <v>1446375</v>
+      </c>
+      <c r="EM26">
+        <v>1314147</v>
+      </c>
+      <c r="EN26">
+        <v>1317349</v>
+      </c>
+      <c r="EO26">
+        <v>1314930</v>
+      </c>
+      <c r="EP26">
+        <v>1342954</v>
+      </c>
+      <c r="EQ26">
+        <v>1205435</v>
+      </c>
+      <c r="ER26">
+        <v>938369</v>
+      </c>
+      <c r="ES26">
+        <v>634551</v>
+      </c>
+      <c r="ET26">
+        <v>383027</v>
+      </c>
+      <c r="EU26">
+        <v>356362</v>
+      </c>
+      <c r="EV26">
+        <v>76970</v>
+      </c>
+      <c r="EW26">
+        <v>189708</v>
+      </c>
+      <c r="EX26">
+        <v>175344</v>
+      </c>
+      <c r="EY26">
+        <v>168493</v>
+      </c>
+      <c r="EZ26">
+        <v>147148</v>
+      </c>
+      <c r="FA26">
+        <v>130636</v>
+      </c>
+      <c r="FB26">
+        <v>107204</v>
+      </c>
+      <c r="FC26">
+        <v>89688</v>
+      </c>
+      <c r="FD26">
+        <v>75599</v>
+      </c>
+      <c r="FE26">
+        <v>61373</v>
+      </c>
+      <c r="FF26">
+        <v>45479</v>
+      </c>
+      <c r="FG26">
+        <v>31014</v>
+      </c>
+      <c r="FH26">
+        <v>18728</v>
+      </c>
+      <c r="FI26">
+        <v>10458</v>
+      </c>
+      <c r="FJ26">
+        <v>8123</v>
+      </c>
+      <c r="FK26">
+        <v>585458</v>
+      </c>
+      <c r="FL26">
+        <v>1512720</v>
+      </c>
+      <c r="FM26">
+        <v>1439088</v>
+      </c>
+      <c r="FN26">
+        <v>1475032</v>
+      </c>
+      <c r="FO26">
+        <v>1362072</v>
+      </c>
+      <c r="FP26">
+        <v>1274625</v>
+      </c>
+      <c r="FQ26">
+        <v>1153371</v>
+      </c>
+      <c r="FR26">
+        <v>1151528</v>
+      </c>
+      <c r="FS26">
+        <v>1127892</v>
+      </c>
+      <c r="FT26">
+        <v>1120940</v>
+      </c>
+      <c r="FU26">
+        <v>959409</v>
+      </c>
+      <c r="FV26">
+        <v>690381</v>
+      </c>
+      <c r="FW26">
+        <v>431777</v>
+      </c>
+      <c r="FX26">
+        <v>230449</v>
+      </c>
+      <c r="FY26">
+        <v>168705</v>
+      </c>
+      <c r="FZ26">
+        <v>4472</v>
+      </c>
+      <c r="GA26">
+        <v>11200</v>
+      </c>
+      <c r="GB26">
+        <v>10425</v>
+      </c>
+      <c r="GC26">
+        <v>9844</v>
+      </c>
+      <c r="GD26">
+        <v>8935</v>
+      </c>
+      <c r="GE26">
+        <v>8488</v>
+      </c>
+      <c r="GF26">
+        <v>7410</v>
+      </c>
+      <c r="GG26">
+        <v>6286</v>
+      </c>
+      <c r="GH26">
+        <v>5350</v>
+      </c>
+      <c r="GI26">
+        <v>4414</v>
+      </c>
+      <c r="GJ26">
+        <v>3118</v>
+      </c>
+      <c r="GK26">
+        <v>2167</v>
+      </c>
+      <c r="GL26">
+        <v>1357</v>
+      </c>
+      <c r="GM26">
+        <v>842</v>
+      </c>
+      <c r="GN26">
+        <v>768</v>
+      </c>
+      <c r="GO26">
+        <v>9854</v>
+      </c>
+      <c r="GP26">
+        <v>26745</v>
+      </c>
+      <c r="GQ26">
+        <v>27410</v>
+      </c>
+      <c r="GR26">
+        <v>27257</v>
+      </c>
+      <c r="GS26">
+        <v>25777</v>
+      </c>
+      <c r="GT26">
+        <v>24187</v>
+      </c>
+      <c r="GU26">
+        <v>20716</v>
+      </c>
+      <c r="GV26">
+        <v>19013</v>
+      </c>
+      <c r="GW26">
+        <v>18263</v>
+      </c>
+      <c r="GX26">
+        <v>17236</v>
+      </c>
+      <c r="GY26">
+        <v>14196</v>
+      </c>
+      <c r="GZ26">
+        <v>10571</v>
+      </c>
+      <c r="HA26">
+        <v>7132</v>
+      </c>
+      <c r="HB26">
+        <v>4129</v>
+      </c>
+      <c r="HC26">
+        <v>3919</v>
+      </c>
+      <c r="HD26">
+        <v>4867</v>
+      </c>
+      <c r="HE26">
+        <v>11555</v>
+      </c>
+      <c r="HF26">
+        <v>10658</v>
+      </c>
+      <c r="HG26">
+        <v>9928</v>
+      </c>
+      <c r="HH26">
+        <v>9061</v>
+      </c>
+      <c r="HI26">
+        <v>8381</v>
+      </c>
+      <c r="HJ26">
+        <v>6914</v>
+      </c>
+      <c r="HK26">
+        <v>5911</v>
+      </c>
+      <c r="HL26">
+        <v>4990</v>
+      </c>
+      <c r="HM26">
+        <v>3865</v>
+      </c>
+      <c r="HN26">
+        <v>2723</v>
+      </c>
+      <c r="HO26">
+        <v>1680</v>
+      </c>
+      <c r="HP26">
+        <v>1079</v>
+      </c>
+      <c r="HQ26">
+        <v>555</v>
+      </c>
+      <c r="HR26">
+        <v>447</v>
+      </c>
+      <c r="HS26">
+        <v>10112</v>
+      </c>
+      <c r="HT26">
+        <v>27291</v>
+      </c>
+      <c r="HU26">
+        <v>28150</v>
+      </c>
+      <c r="HV26">
+        <v>27996</v>
+      </c>
+      <c r="HW26">
+        <v>26455</v>
+      </c>
+      <c r="HX26">
+        <v>23991</v>
+      </c>
+      <c r="HY26">
+        <v>20695</v>
+      </c>
+      <c r="HZ26">
+        <v>18601</v>
+      </c>
+      <c r="IA26">
+        <v>17115</v>
+      </c>
+      <c r="IB26">
+        <v>15733</v>
+      </c>
+      <c r="IC26">
+        <v>12814</v>
+      </c>
+      <c r="ID26">
+        <v>9153</v>
+      </c>
+      <c r="IE26">
+        <v>6004</v>
+      </c>
+      <c r="IF26">
+        <v>3152</v>
+      </c>
+      <c r="IG26">
+        <v>2324</v>
+      </c>
+      <c r="IH26">
+        <v>83974</v>
+      </c>
+      <c r="II26">
+        <v>187687</v>
+      </c>
+      <c r="IJ26">
+        <v>156390</v>
+      </c>
+      <c r="IK26">
+        <v>147350</v>
+      </c>
+      <c r="IL26">
+        <v>128506</v>
+      </c>
+      <c r="IM26">
+        <v>115465</v>
+      </c>
+      <c r="IN26">
+        <v>97151</v>
+      </c>
+      <c r="IO26">
+        <v>80781</v>
+      </c>
+      <c r="IP26">
+        <v>66558</v>
+      </c>
+      <c r="IQ26">
+        <v>54468</v>
+      </c>
+      <c r="IR26">
+        <v>41326</v>
+      </c>
+      <c r="IS26">
+        <v>29061</v>
+      </c>
+      <c r="IT26">
+        <v>19108</v>
+      </c>
+      <c r="IU26">
+        <v>11124</v>
+      </c>
+      <c r="IV26">
+        <v>9564</v>
+      </c>
+      <c r="IW26">
+        <v>228475</v>
+      </c>
+      <c r="IX26">
+        <v>518348</v>
+      </c>
+      <c r="IY26">
+        <v>443613</v>
+      </c>
+      <c r="IZ26">
+        <v>415204</v>
+      </c>
+      <c r="JA26">
+        <v>369588</v>
+      </c>
+      <c r="JB26">
+        <v>332752</v>
+      </c>
+      <c r="JC26">
+        <v>285936</v>
+      </c>
+      <c r="JD26">
+        <v>271719</v>
+      </c>
+      <c r="JE26">
+        <v>249606</v>
+      </c>
+      <c r="JF26">
+        <v>247327</v>
+      </c>
+      <c r="JG26">
+        <v>208894</v>
+      </c>
+      <c r="JH26">
+        <v>153846</v>
+      </c>
+      <c r="JI26">
+        <v>107509</v>
+      </c>
+      <c r="JJ26">
+        <v>62831</v>
+      </c>
+      <c r="JK26">
+        <v>58863</v>
+      </c>
+      <c r="JL26">
+        <v>88502</v>
+      </c>
+      <c r="JM26">
+        <v>194047</v>
+      </c>
+      <c r="JN26">
+        <v>159671</v>
+      </c>
+      <c r="JO26">
+        <v>143117</v>
+      </c>
+      <c r="JP26">
+        <v>122099</v>
+      </c>
+      <c r="JQ26">
+        <v>107317</v>
+      </c>
+      <c r="JR26">
+        <v>88773</v>
+      </c>
+      <c r="JS26">
+        <v>72308</v>
+      </c>
+      <c r="JT26">
+        <v>58544</v>
+      </c>
+      <c r="JU26">
+        <v>46437</v>
+      </c>
+      <c r="JV26">
+        <v>33994</v>
+      </c>
+      <c r="JW26">
+        <v>21924</v>
+      </c>
+      <c r="JX26">
+        <v>13488</v>
+      </c>
+      <c r="JY26">
+        <v>7252</v>
+      </c>
+      <c r="JZ26">
+        <v>5375</v>
+      </c>
+      <c r="KA26">
+        <v>233495</v>
+      </c>
+      <c r="KB26">
+        <v>517426</v>
+      </c>
+      <c r="KC26">
+        <v>423829</v>
+      </c>
+      <c r="KD26">
+        <v>379126</v>
+      </c>
+      <c r="KE26">
+        <v>329863</v>
+      </c>
+      <c r="KF26">
+        <v>292666</v>
+      </c>
+      <c r="KG26">
+        <v>250763</v>
+      </c>
+      <c r="KH26">
+        <v>237554</v>
+      </c>
+      <c r="KI26">
+        <v>213517</v>
+      </c>
+      <c r="KJ26">
+        <v>208611</v>
+      </c>
+      <c r="KK26">
+        <v>173803</v>
+      </c>
+      <c r="KL26">
+        <v>122978</v>
+      </c>
+      <c r="KM26">
+        <v>82645</v>
+      </c>
+      <c r="KN26">
+        <v>45177</v>
+      </c>
+      <c r="KO26">
+        <v>36399</v>
+      </c>
+      <c r="KP26">
+        <v>905378</v>
+      </c>
+      <c r="KQ26">
+        <v>2265311</v>
+      </c>
+      <c r="KR26">
+        <v>2137460</v>
+      </c>
+      <c r="KS26">
+        <v>2078969</v>
+      </c>
+      <c r="KT26">
+        <v>1927558</v>
+      </c>
+      <c r="KU26">
+        <v>1875940</v>
+      </c>
+      <c r="KV26">
+        <v>1735187</v>
+      </c>
+      <c r="KW26">
+        <v>1613501</v>
+      </c>
+      <c r="KX26">
+        <v>1423464</v>
+      </c>
+      <c r="KY26">
+        <v>1242159</v>
+      </c>
+      <c r="KZ26">
+        <v>994828</v>
+      </c>
+      <c r="LA26">
+        <v>752570</v>
+      </c>
+      <c r="LB26">
+        <v>539992</v>
+      </c>
+      <c r="LC26">
+        <v>349260</v>
+      </c>
+      <c r="LD26">
+        <v>346883</v>
+      </c>
+      <c r="LE26">
+        <v>2060104</v>
+      </c>
+      <c r="LF26">
+        <v>5518469</v>
+      </c>
+      <c r="LG26">
+        <v>5589359</v>
+      </c>
+      <c r="LH26">
+        <v>5907200</v>
+      </c>
+      <c r="LI26">
+        <v>6049919</v>
+      </c>
+      <c r="LJ26">
+        <v>5962309</v>
+      </c>
+      <c r="LK26">
+        <v>5484595</v>
+      </c>
+      <c r="LL26">
+        <v>5858378</v>
+      </c>
+      <c r="LM26">
+        <v>6331970</v>
+      </c>
+      <c r="LN26">
+        <v>7277154</v>
+      </c>
+      <c r="LO26">
+        <v>7187019</v>
+      </c>
+      <c r="LP26">
+        <v>6288244</v>
+      </c>
+      <c r="LQ26">
+        <v>5029874</v>
+      </c>
+      <c r="LR26">
+        <v>3279283</v>
+      </c>
+      <c r="LS26">
+        <v>3206155</v>
+      </c>
+      <c r="LT26">
+        <v>951503</v>
+      </c>
+      <c r="LU26">
+        <v>2357974</v>
+      </c>
+      <c r="LV26">
+        <v>2222246</v>
+      </c>
+      <c r="LW26">
+        <v>2144781</v>
+      </c>
+      <c r="LX26">
+        <v>1970070</v>
+      </c>
+      <c r="LY26">
+        <v>1863852</v>
+      </c>
+      <c r="LZ26">
+        <v>1682073</v>
+      </c>
+      <c r="MA26">
+        <v>1532108</v>
+      </c>
+      <c r="MB26">
+        <v>1355364</v>
+      </c>
+      <c r="MC26">
+        <v>1140508</v>
+      </c>
+      <c r="MD26">
+        <v>865016</v>
+      </c>
+      <c r="ME26">
+        <v>610869</v>
+      </c>
+      <c r="MF26">
+        <v>409163</v>
+      </c>
+      <c r="MG26">
+        <v>238188</v>
+      </c>
+      <c r="MH26">
+        <v>198021</v>
+      </c>
+      <c r="MI26">
+        <v>2157332</v>
+      </c>
+      <c r="MJ26">
+        <v>5625839</v>
+      </c>
+      <c r="MK26">
+        <v>5682908</v>
+      </c>
+      <c r="ML26">
+        <v>5994996</v>
+      </c>
+      <c r="MM26">
+        <v>6105241</v>
+      </c>
+      <c r="MN26">
+        <v>6013308</v>
+      </c>
+      <c r="MO26">
+        <v>5516367</v>
+      </c>
+      <c r="MP26">
+        <v>5842746</v>
+      </c>
+      <c r="MQ26">
+        <v>6179519</v>
+      </c>
+      <c r="MR26">
+        <v>6908018</v>
+      </c>
+      <c r="MS26">
+        <v>6611242</v>
+      </c>
+      <c r="MT26">
+        <v>5581297</v>
+      </c>
+      <c r="MU26">
+        <v>4279526</v>
+      </c>
+      <c r="MV26">
+        <v>2547777</v>
+      </c>
+      <c r="MW26">
+        <v>1980656</v>
+      </c>
+    </row>
+    <row r="27" spans="1:361">
+      <c r="A27">
+        <v>2025</v>
+      </c>
+      <c r="B27">
+        <v>78303</v>
+      </c>
+      <c r="C27">
+        <v>193735</v>
+      </c>
+      <c r="D27">
+        <v>181565</v>
+      </c>
+      <c r="E27">
+        <v>179185</v>
+      </c>
+      <c r="F27">
+        <v>171281</v>
+      </c>
+      <c r="G27">
+        <v>166383</v>
+      </c>
+      <c r="H27">
+        <v>153505</v>
+      </c>
+      <c r="I27">
+        <v>134172</v>
+      </c>
+      <c r="J27">
+        <v>112884</v>
+      </c>
+      <c r="K27">
+        <v>92019</v>
+      </c>
+      <c r="L27">
+        <v>71310</v>
+      </c>
+      <c r="M27">
+        <v>49305</v>
+      </c>
+      <c r="N27">
+        <v>31429</v>
+      </c>
+      <c r="O27">
+        <v>18836</v>
+      </c>
+      <c r="P27">
+        <v>16696</v>
+      </c>
+      <c r="Q27">
         <v>35299</v>
       </c>
-      <c r="R26">
-        <v>86542</v>
-      </c>
-      <c r="S26">
-        <v>87232</v>
-      </c>
-      <c r="T26">
-        <v>95114</v>
-      </c>
-      <c r="U26">
-        <v>84978</v>
-      </c>
-      <c r="V26">
-        <v>78609</v>
-      </c>
-      <c r="W26">
-        <v>70262</v>
-      </c>
-      <c r="X26">
-        <v>70405</v>
-      </c>
-      <c r="Y26">
-        <v>71966</v>
-      </c>
-      <c r="Z26">
-        <v>77941</v>
-      </c>
-      <c r="AA26">
-        <v>70187</v>
-      </c>
-      <c r="AB26">
-        <v>54711</v>
-      </c>
-      <c r="AC26">
-        <v>38916</v>
-      </c>
-      <c r="AD26">
-        <v>23575</v>
-      </c>
-      <c r="AE26">
-        <v>23022</v>
-      </c>
-      <c r="AF26">
-        <v>43030</v>
-      </c>
-      <c r="AG26">
-        <v>100193</v>
-      </c>
-      <c r="AH26">
-        <v>91287</v>
-      </c>
-      <c r="AI26">
-        <v>92562</v>
-      </c>
-      <c r="AJ26">
-        <v>88458</v>
-      </c>
-      <c r="AK26">
-        <v>84391</v>
-      </c>
-      <c r="AL26">
-        <v>70181</v>
-      </c>
-      <c r="AM26">
-        <v>61462</v>
-      </c>
-      <c r="AN26">
-        <v>50655</v>
-      </c>
-      <c r="AO26">
-        <v>41452</v>
-      </c>
-      <c r="AP26">
-        <v>30063</v>
-      </c>
-      <c r="AQ26">
-        <v>18731</v>
-      </c>
-      <c r="AR26">
-        <v>11519</v>
-      </c>
-      <c r="AS26">
-        <v>5578</v>
-      </c>
-      <c r="AT26">
-        <v>3953</v>
-      </c>
-      <c r="AU26">
-        <v>35916</v>
-      </c>
-      <c r="AV26">
-        <v>87995</v>
-      </c>
-      <c r="AW26">
-        <v>88001</v>
-      </c>
-      <c r="AX26">
-        <v>96524</v>
-      </c>
-      <c r="AY26">
-        <v>84805</v>
-      </c>
-      <c r="AZ26">
-        <v>76954</v>
-      </c>
-      <c r="BA26">
-        <v>68632</v>
-      </c>
-      <c r="BB26">
-        <v>67685</v>
-      </c>
-      <c r="BC26">
-        <v>67474</v>
-      </c>
-      <c r="BD26">
-        <v>70528</v>
-      </c>
-      <c r="BE26">
-        <v>60437</v>
-      </c>
-      <c r="BF26">
-        <v>46136</v>
-      </c>
-      <c r="BG26">
-        <v>32846</v>
-      </c>
-      <c r="BH26">
-        <v>18974</v>
-      </c>
-      <c r="BI26">
-        <v>15387</v>
-      </c>
-      <c r="BJ26">
-        <v>11804</v>
-      </c>
-      <c r="BK26">
-        <v>27318</v>
-      </c>
-      <c r="BL26">
-        <v>26828</v>
-      </c>
-      <c r="BM26">
-        <v>27587</v>
-      </c>
-      <c r="BN26">
-        <v>25463</v>
-      </c>
-      <c r="BO26">
-        <v>23808</v>
-      </c>
-      <c r="BP26">
-        <v>21404</v>
-      </c>
-      <c r="BQ26">
-        <v>18530</v>
-      </c>
-      <c r="BR26">
-        <v>15521</v>
-      </c>
-      <c r="BS26">
-        <v>13367</v>
-      </c>
-      <c r="BT26">
-        <v>10318</v>
-      </c>
-      <c r="BU26">
-        <v>7339</v>
-      </c>
-      <c r="BV26">
-        <v>5009</v>
-      </c>
-      <c r="BW26">
-        <v>2963</v>
-      </c>
-      <c r="BX26">
-        <v>2759</v>
-      </c>
-      <c r="BY26">
-        <v>255728</v>
-      </c>
-      <c r="BZ26">
-        <v>714791</v>
-      </c>
-      <c r="CA26">
-        <v>831131</v>
-      </c>
-      <c r="CB26">
-        <v>962124</v>
-      </c>
-      <c r="CC26">
-        <v>982063</v>
-      </c>
-      <c r="CD26">
-        <v>922535</v>
-      </c>
-      <c r="CE26">
-        <v>824582</v>
-      </c>
-      <c r="CF26">
-        <v>784543</v>
-      </c>
-      <c r="CG26">
-        <v>674644</v>
-      </c>
-      <c r="CH26">
-        <v>626807</v>
-      </c>
-      <c r="CI26">
-        <v>563440</v>
-      </c>
-      <c r="CJ26">
-        <v>471322</v>
-      </c>
-      <c r="CK26">
-        <v>339988</v>
-      </c>
-      <c r="CL26">
-        <v>207448</v>
-      </c>
-      <c r="CM26">
-        <v>221798</v>
-      </c>
-      <c r="CN26">
-        <v>12654</v>
-      </c>
-      <c r="CO26">
-        <v>28545</v>
-      </c>
-      <c r="CP26">
-        <v>26436</v>
-      </c>
-      <c r="CQ26">
-        <v>26508</v>
-      </c>
-      <c r="CR26">
-        <v>25767</v>
-      </c>
-      <c r="CS26">
-        <v>24498</v>
-      </c>
-      <c r="CT26">
-        <v>21177</v>
-      </c>
-      <c r="CU26">
-        <v>18095</v>
-      </c>
-      <c r="CV26">
-        <v>15023</v>
-      </c>
-      <c r="CW26">
-        <v>12324</v>
-      </c>
-      <c r="CX26">
-        <v>9006</v>
-      </c>
-      <c r="CY26">
-        <v>5883</v>
-      </c>
-      <c r="CZ26">
-        <v>3693</v>
-      </c>
-      <c r="DA26">
-        <v>1927</v>
-      </c>
-      <c r="DB26">
-        <v>1484</v>
-      </c>
-      <c r="DC26">
-        <v>261113</v>
-      </c>
-      <c r="DD26">
-        <v>723814</v>
-      </c>
-      <c r="DE26">
-        <v>791158</v>
-      </c>
-      <c r="DF26">
-        <v>905554</v>
-      </c>
-      <c r="DG26">
-        <v>919656</v>
-      </c>
-      <c r="DH26">
-        <v>842515</v>
-      </c>
-      <c r="DI26">
-        <v>728833</v>
-      </c>
-      <c r="DJ26">
-        <v>698166</v>
-      </c>
-      <c r="DK26">
-        <v>588369</v>
-      </c>
-      <c r="DL26">
-        <v>536472</v>
-      </c>
-      <c r="DM26">
-        <v>459908</v>
-      </c>
-      <c r="DN26">
-        <v>365633</v>
-      </c>
-      <c r="DO26">
-        <v>261844</v>
-      </c>
-      <c r="DP26">
-        <v>157619</v>
-      </c>
-      <c r="DQ26">
-        <v>144176</v>
-      </c>
-      <c r="DR26">
-        <v>61212</v>
-      </c>
-      <c r="DS26">
-        <v>139947</v>
-      </c>
-      <c r="DT26">
-        <v>129334</v>
-      </c>
-      <c r="DU26">
-        <v>136407</v>
-      </c>
-      <c r="DV26">
-        <v>129204</v>
-      </c>
-      <c r="DW26">
-        <v>122481</v>
-      </c>
-      <c r="DX26">
-        <v>109551</v>
-      </c>
-      <c r="DY26">
-        <v>91708</v>
-      </c>
-      <c r="DZ26">
-        <v>78401</v>
-      </c>
-      <c r="EA26">
-        <v>66203</v>
-      </c>
-      <c r="EB26">
-        <v>51574</v>
-      </c>
-      <c r="EC26">
-        <v>36807</v>
-      </c>
-      <c r="ED26">
-        <v>24947</v>
-      </c>
-      <c r="EE26">
-        <v>14992</v>
-      </c>
-      <c r="EF26">
-        <v>14075</v>
-      </c>
-      <c r="EG26">
-        <v>591201</v>
-      </c>
-      <c r="EH26">
-        <v>1489699</v>
-      </c>
-      <c r="EI26">
-        <v>1544109</v>
-      </c>
-      <c r="EJ26">
-        <v>1759596</v>
-      </c>
-      <c r="EK26">
-        <v>1582826</v>
-      </c>
-      <c r="EL26">
-        <v>1476208</v>
-      </c>
-      <c r="EM26">
-        <v>1349304</v>
-      </c>
-      <c r="EN26">
-        <v>1352530</v>
-      </c>
-      <c r="EO26">
-        <v>1327777</v>
-      </c>
-      <c r="EP26">
-        <v>1346229</v>
-      </c>
-      <c r="EQ26">
-        <v>1190245</v>
-      </c>
-      <c r="ER26">
-        <v>923532</v>
-      </c>
-      <c r="ES26">
-        <v>631481</v>
-      </c>
-      <c r="ET26">
-        <v>382013</v>
-      </c>
-      <c r="EU26">
-        <v>358104</v>
-      </c>
-      <c r="EV26">
-        <v>63554</v>
-      </c>
-      <c r="EW26">
-        <v>146597</v>
-      </c>
-      <c r="EX26">
-        <v>133604</v>
-      </c>
-      <c r="EY26">
-        <v>139403</v>
-      </c>
-      <c r="EZ26">
-        <v>127196</v>
-      </c>
-      <c r="FA26">
-        <v>116164</v>
-      </c>
-      <c r="FB26">
-        <v>97969</v>
-      </c>
-      <c r="FC26">
-        <v>80228</v>
-      </c>
-      <c r="FD26">
-        <v>69559</v>
-      </c>
-      <c r="FE26">
-        <v>58281</v>
-      </c>
-      <c r="FF26">
-        <v>43862</v>
-      </c>
-      <c r="FG26">
-        <v>29649</v>
-      </c>
-      <c r="FH26">
-        <v>18270</v>
-      </c>
-      <c r="FI26">
-        <v>10140</v>
-      </c>
-      <c r="FJ26">
-        <v>7839</v>
-      </c>
-      <c r="FK26">
-        <v>601052</v>
-      </c>
-      <c r="FL26">
-        <v>1481781</v>
-      </c>
-      <c r="FM26">
-        <v>1521124</v>
-      </c>
-      <c r="FN26">
-        <v>1727128</v>
-      </c>
-      <c r="FO26">
-        <v>1500069</v>
-      </c>
-      <c r="FP26">
-        <v>1353524</v>
-      </c>
-      <c r="FQ26">
-        <v>1204554</v>
-      </c>
-      <c r="FR26">
-        <v>1197596</v>
-      </c>
-      <c r="FS26">
-        <v>1159111</v>
-      </c>
-      <c r="FT26">
-        <v>1142475</v>
-      </c>
-      <c r="FU26">
-        <v>955474</v>
-      </c>
-      <c r="FV26">
-        <v>671493</v>
-      </c>
-      <c r="FW26">
-        <v>426817</v>
-      </c>
-      <c r="FX26">
-        <v>228100</v>
-      </c>
-      <c r="FY26">
-        <v>167755</v>
-      </c>
-      <c r="FZ26">
-        <v>4115</v>
-      </c>
-      <c r="GA26">
-        <v>9375</v>
-      </c>
-      <c r="GB26">
-        <v>8831</v>
-      </c>
-      <c r="GC26">
-        <v>9107</v>
-      </c>
-      <c r="GD26">
-        <v>8791</v>
-      </c>
-      <c r="GE26">
-        <v>8599</v>
-      </c>
-      <c r="GF26">
-        <v>7481</v>
-      </c>
-      <c r="GG26">
-        <v>6305</v>
-      </c>
-      <c r="GH26">
-        <v>5419</v>
-      </c>
-      <c r="GI26">
-        <v>4420</v>
-      </c>
-      <c r="GJ26">
-        <v>3093</v>
-      </c>
-      <c r="GK26">
-        <v>2186</v>
-      </c>
-      <c r="GL26">
-        <v>1338</v>
-      </c>
-      <c r="GM26">
-        <v>805</v>
-      </c>
-      <c r="GN26">
-        <v>755</v>
-      </c>
-      <c r="GO26">
-        <v>9573</v>
-      </c>
-      <c r="GP26">
-        <v>23227</v>
-      </c>
-      <c r="GQ26">
-        <v>22967</v>
-      </c>
-      <c r="GR26">
-        <v>26454</v>
-      </c>
-      <c r="GS26">
-        <v>26605</v>
-      </c>
-      <c r="GT26">
-        <v>25066</v>
-      </c>
-      <c r="GU26">
-        <v>21003</v>
-      </c>
-      <c r="GV26">
-        <v>18940</v>
-      </c>
-      <c r="GW26">
-        <v>18498</v>
-      </c>
-      <c r="GX26">
-        <v>17657</v>
-      </c>
-      <c r="GY26">
-        <v>14870</v>
-      </c>
-      <c r="GZ26">
-        <v>11289</v>
-      </c>
-      <c r="HA26">
-        <v>8211</v>
-      </c>
-      <c r="HB26">
-        <v>4632</v>
-      </c>
-      <c r="HC26">
-        <v>4538</v>
-      </c>
-      <c r="HD26">
-        <v>4453</v>
-      </c>
-      <c r="HE26">
-        <v>9479</v>
-      </c>
-      <c r="HF26">
-        <v>8910</v>
-      </c>
-      <c r="HG26">
-        <v>10025</v>
-      </c>
-      <c r="HH26">
-        <v>11033</v>
-      </c>
-      <c r="HI26">
-        <v>10711</v>
-      </c>
-      <c r="HJ26">
-        <v>8485</v>
-      </c>
-      <c r="HK26">
-        <v>6693</v>
-      </c>
-      <c r="HL26">
-        <v>5550</v>
-      </c>
-      <c r="HM26">
-        <v>4281</v>
-      </c>
-      <c r="HN26">
-        <v>2973</v>
-      </c>
-      <c r="HO26">
-        <v>1773</v>
-      </c>
-      <c r="HP26">
-        <v>1153</v>
-      </c>
-      <c r="HQ26">
-        <v>534</v>
-      </c>
-      <c r="HR26">
-        <v>433</v>
-      </c>
-      <c r="HS26">
-        <v>9488</v>
-      </c>
-      <c r="HT26">
-        <v>23239</v>
-      </c>
-      <c r="HU26">
-        <v>23285</v>
-      </c>
-      <c r="HV26">
-        <v>26679</v>
-      </c>
-      <c r="HW26">
-        <v>27983</v>
-      </c>
-      <c r="HX26">
-        <v>26168</v>
-      </c>
-      <c r="HY26">
-        <v>21731</v>
-      </c>
-      <c r="HZ26">
-        <v>19621</v>
-      </c>
-      <c r="IA26">
-        <v>18067</v>
-      </c>
-      <c r="IB26">
-        <v>16989</v>
-      </c>
-      <c r="IC26">
-        <v>13969</v>
-      </c>
-      <c r="ID26">
-        <v>10218</v>
-      </c>
-      <c r="IE26">
-        <v>7214</v>
-      </c>
-      <c r="IF26">
-        <v>3919</v>
-      </c>
-      <c r="IG26">
-        <v>3212</v>
-      </c>
-      <c r="IH26">
-        <v>45288</v>
-      </c>
-      <c r="II26">
-        <v>100586</v>
-      </c>
-      <c r="IJ26">
-        <v>89046</v>
-      </c>
-      <c r="IK26">
-        <v>81023</v>
-      </c>
-      <c r="IL26">
-        <v>68629</v>
-      </c>
-      <c r="IM26">
-        <v>63160</v>
-      </c>
-      <c r="IN26">
-        <v>54360</v>
-      </c>
-      <c r="IO26">
-        <v>42240</v>
-      </c>
-      <c r="IP26">
-        <v>34689</v>
-      </c>
-      <c r="IQ26">
-        <v>29867</v>
-      </c>
-      <c r="IR26">
-        <v>22693</v>
-      </c>
-      <c r="IS26">
-        <v>15503</v>
-      </c>
-      <c r="IT26">
-        <v>10331</v>
-      </c>
-      <c r="IU26">
-        <v>6053</v>
-      </c>
-      <c r="IV26">
-        <v>5403</v>
-      </c>
-      <c r="IW26">
-        <v>171485</v>
-      </c>
-      <c r="IX26">
-        <v>383594</v>
-      </c>
-      <c r="IY26">
-        <v>337512</v>
-      </c>
-      <c r="IZ26">
-        <v>298554</v>
-      </c>
-      <c r="JA26">
-        <v>236207</v>
-      </c>
-      <c r="JB26">
-        <v>202278</v>
-      </c>
-      <c r="JC26">
-        <v>165751</v>
-      </c>
-      <c r="JD26">
-        <v>146403</v>
-      </c>
-      <c r="JE26">
-        <v>125181</v>
-      </c>
-      <c r="JF26">
-        <v>121823</v>
-      </c>
-      <c r="JG26">
-        <v>103804</v>
-      </c>
-      <c r="JH26">
-        <v>79080</v>
-      </c>
-      <c r="JI26">
-        <v>57006</v>
-      </c>
-      <c r="JJ26">
-        <v>35500</v>
-      </c>
-      <c r="JK26">
-        <v>35884</v>
-      </c>
-      <c r="JL26">
-        <v>48495</v>
-      </c>
-      <c r="JM26">
-        <v>104601</v>
-      </c>
-      <c r="JN26">
-        <v>92691</v>
-      </c>
-      <c r="JO26">
-        <v>82172</v>
-      </c>
-      <c r="JP26">
-        <v>69373</v>
-      </c>
-      <c r="JQ26">
-        <v>62601</v>
-      </c>
-      <c r="JR26">
-        <v>52471</v>
-      </c>
-      <c r="JS26">
-        <v>39403</v>
-      </c>
-      <c r="JT26">
-        <v>32370</v>
-      </c>
-      <c r="JU26">
-        <v>26486</v>
-      </c>
-      <c r="JV26">
-        <v>19544</v>
-      </c>
-      <c r="JW26">
-        <v>12039</v>
-      </c>
-      <c r="JX26">
-        <v>7609</v>
-      </c>
-      <c r="JY26">
-        <v>3995</v>
-      </c>
-      <c r="JZ26">
-        <v>3102</v>
-      </c>
-      <c r="KA26">
-        <v>176727</v>
-      </c>
-      <c r="KB26">
-        <v>386727</v>
-      </c>
-      <c r="KC26">
-        <v>337818</v>
-      </c>
-      <c r="KD26">
-        <v>287274</v>
-      </c>
-      <c r="KE26">
-        <v>214979</v>
-      </c>
-      <c r="KF26">
-        <v>181166</v>
-      </c>
-      <c r="KG26">
-        <v>146860</v>
-      </c>
-      <c r="KH26">
-        <v>130514</v>
-      </c>
-      <c r="KI26">
-        <v>111564</v>
-      </c>
-      <c r="KJ26">
-        <v>108503</v>
-      </c>
-      <c r="KK26">
-        <v>92985</v>
-      </c>
-      <c r="KL26">
-        <v>68837</v>
-      </c>
-      <c r="KM26">
-        <v>47937</v>
-      </c>
-      <c r="KN26">
-        <v>27792</v>
-      </c>
-      <c r="KO26">
-        <v>24006</v>
-      </c>
-      <c r="KP26">
-        <v>973169</v>
-      </c>
-      <c r="KQ26">
-        <v>2327485</v>
-      </c>
-      <c r="KR26">
-        <v>2213571</v>
-      </c>
-      <c r="KS26">
-        <v>2195179</v>
-      </c>
-      <c r="KT26">
-        <v>2020065</v>
-      </c>
-      <c r="KU26">
-        <v>1996932</v>
-      </c>
-      <c r="KV26">
-        <v>1849324</v>
-      </c>
-      <c r="KW26">
-        <v>1713861</v>
-      </c>
-      <c r="KX26">
-        <v>1480175</v>
-      </c>
-      <c r="KY26">
-        <v>1280244</v>
-      </c>
-      <c r="KZ26">
-        <v>1010657</v>
-      </c>
-      <c r="LA26">
-        <v>755127</v>
-      </c>
-      <c r="LB26">
-        <v>538377</v>
-      </c>
-      <c r="LC26">
-        <v>343040</v>
-      </c>
-      <c r="LD26">
-        <v>335907</v>
-      </c>
-      <c r="LE26">
-        <v>2153632</v>
-      </c>
-      <c r="LF26">
-        <v>5522553</v>
-      </c>
-      <c r="LG26">
-        <v>5647567</v>
-      </c>
-      <c r="LH26">
-        <v>6159843</v>
-      </c>
-      <c r="LI26">
-        <v>6207006</v>
-      </c>
-      <c r="LJ26">
-        <v>6114976</v>
-      </c>
-      <c r="LK26">
-        <v>5627193</v>
-      </c>
-      <c r="LL26">
-        <v>5992285</v>
-      </c>
-      <c r="LM26">
-        <v>6429854</v>
-      </c>
-      <c r="LN26">
-        <v>7314551</v>
-      </c>
-      <c r="LO26">
-        <v>7121406</v>
-      </c>
-      <c r="LP26">
-        <v>6176642</v>
-      </c>
-      <c r="LQ26">
-        <v>4889292</v>
-      </c>
-      <c r="LR26">
-        <v>3136946</v>
-      </c>
-      <c r="LS26">
-        <v>3012460</v>
-      </c>
-      <c r="LT26">
-        <v>1018857</v>
-      </c>
-      <c r="LU26">
-        <v>2407145</v>
-      </c>
-      <c r="LV26">
-        <v>2281696</v>
-      </c>
-      <c r="LW26">
-        <v>2324577</v>
-      </c>
-      <c r="LX26">
-        <v>2232640</v>
-      </c>
-      <c r="LY26">
-        <v>2177654</v>
-      </c>
-      <c r="LZ26">
-        <v>1952280</v>
-      </c>
-      <c r="MA26">
-        <v>1762611</v>
-      </c>
-      <c r="MB26">
-        <v>1514284</v>
-      </c>
-      <c r="MC26">
-        <v>1250650</v>
-      </c>
-      <c r="MD26">
-        <v>924788</v>
-      </c>
-      <c r="ME26">
-        <v>636980</v>
-      </c>
-      <c r="MF26">
-        <v>421657</v>
-      </c>
-      <c r="MG26">
-        <v>238428</v>
-      </c>
-      <c r="MH26">
-        <v>197936</v>
-      </c>
-      <c r="MI26">
-        <v>2248007</v>
-      </c>
-      <c r="MJ26">
-        <v>5695991</v>
-      </c>
-      <c r="MK26">
-        <v>5792276</v>
-      </c>
-      <c r="ML26">
-        <v>6265501</v>
-      </c>
-      <c r="MM26">
-        <v>6285698</v>
-      </c>
-      <c r="MN26">
-        <v>6236582</v>
-      </c>
-      <c r="MO26">
-        <v>5733608</v>
-      </c>
-      <c r="MP26">
-        <v>6102249</v>
-      </c>
-      <c r="MQ26">
-        <v>6417895</v>
-      </c>
-      <c r="MR26">
-        <v>7094241</v>
-      </c>
-      <c r="MS26">
-        <v>6684576</v>
-      </c>
-      <c r="MT26">
-        <v>5534712</v>
-      </c>
-      <c r="MU26">
-        <v>4195309</v>
-      </c>
-      <c r="MV26">
-        <v>2444057</v>
-      </c>
-      <c r="MW26">
-        <v>1844730</v>
+      <c r="R27">
+        <v>85845</v>
+      </c>
+      <c r="S27">
+        <v>78453</v>
+      </c>
+      <c r="T27">
+        <v>77622</v>
+      </c>
+      <c r="U27">
+        <v>79111</v>
+      </c>
+      <c r="V27">
+        <v>75521</v>
+      </c>
+      <c r="W27">
+        <v>70153</v>
+      </c>
+      <c r="X27">
+        <v>68754</v>
+      </c>
+      <c r="Y27">
+        <v>70347</v>
+      </c>
+      <c r="Z27">
+        <v>76357</v>
+      </c>
+      <c r="AA27">
+        <v>69840</v>
+      </c>
+      <c r="AB27">
+        <v>54479</v>
+      </c>
+      <c r="AC27">
+        <v>38863</v>
+      </c>
+      <c r="AD27">
+        <v>23386</v>
+      </c>
+      <c r="AE27">
+        <v>23957</v>
+      </c>
+      <c r="AF27">
+        <v>86628</v>
+      </c>
+      <c r="AG27">
+        <v>217688</v>
+      </c>
+      <c r="AH27">
+        <v>206278</v>
+      </c>
+      <c r="AI27">
+        <v>202457</v>
+      </c>
+      <c r="AJ27">
+        <v>190720</v>
+      </c>
+      <c r="AK27">
+        <v>182056</v>
+      </c>
+      <c r="AL27">
+        <v>163633</v>
+      </c>
+      <c r="AM27">
+        <v>138676</v>
+      </c>
+      <c r="AN27">
+        <v>116394</v>
+      </c>
+      <c r="AO27">
+        <v>92981</v>
+      </c>
+      <c r="AP27">
+        <v>68407</v>
+      </c>
+      <c r="AQ27">
+        <v>44433</v>
+      </c>
+      <c r="AR27">
+        <v>26581</v>
+      </c>
+      <c r="AS27">
+        <v>13384</v>
+      </c>
+      <c r="AT27">
+        <v>9967</v>
+      </c>
+      <c r="AU27">
+        <v>36139</v>
+      </c>
+      <c r="AV27">
+        <v>87959</v>
+      </c>
+      <c r="AW27">
+        <v>81070</v>
+      </c>
+      <c r="AX27">
+        <v>79251</v>
+      </c>
+      <c r="AY27">
+        <v>78459</v>
+      </c>
+      <c r="AZ27">
+        <v>72837</v>
+      </c>
+      <c r="BA27">
+        <v>67715</v>
+      </c>
+      <c r="BB27">
+        <v>65656</v>
+      </c>
+      <c r="BC27">
+        <v>65412</v>
+      </c>
+      <c r="BD27">
+        <v>69016</v>
+      </c>
+      <c r="BE27">
+        <v>60999</v>
+      </c>
+      <c r="BF27">
+        <v>46121</v>
+      </c>
+      <c r="BG27">
+        <v>32537</v>
+      </c>
+      <c r="BH27">
+        <v>18098</v>
+      </c>
+      <c r="BI27">
+        <v>15149</v>
+      </c>
+      <c r="BJ27">
+        <v>16399</v>
+      </c>
+      <c r="BK27">
+        <v>39055</v>
+      </c>
+      <c r="BL27">
+        <v>39317</v>
+      </c>
+      <c r="BM27">
+        <v>37963</v>
+      </c>
+      <c r="BN27">
+        <v>33772</v>
+      </c>
+      <c r="BO27">
+        <v>30318</v>
+      </c>
+      <c r="BP27">
+        <v>26945</v>
+      </c>
+      <c r="BQ27">
+        <v>23361</v>
+      </c>
+      <c r="BR27">
+        <v>19555</v>
+      </c>
+      <c r="BS27">
+        <v>15810</v>
+      </c>
+      <c r="BT27">
+        <v>12354</v>
+      </c>
+      <c r="BU27">
+        <v>8565</v>
+      </c>
+      <c r="BV27">
+        <v>5994</v>
+      </c>
+      <c r="BW27">
+        <v>3469</v>
+      </c>
+      <c r="BX27">
+        <v>3363</v>
+      </c>
+      <c r="BY27">
+        <v>254605</v>
+      </c>
+      <c r="BZ27">
+        <v>756346</v>
+      </c>
+      <c r="CA27">
+        <v>933131</v>
+      </c>
+      <c r="CB27">
+        <v>979472</v>
+      </c>
+      <c r="CC27">
+        <v>996096</v>
+      </c>
+      <c r="CD27">
+        <v>936736</v>
+      </c>
+      <c r="CE27">
+        <v>836600</v>
+      </c>
+      <c r="CF27">
+        <v>814349</v>
+      </c>
+      <c r="CG27">
+        <v>724902</v>
+      </c>
+      <c r="CH27">
+        <v>653827</v>
+      </c>
+      <c r="CI27">
+        <v>592085</v>
+      </c>
+      <c r="CJ27">
+        <v>493698</v>
+      </c>
+      <c r="CK27">
+        <v>371122</v>
+      </c>
+      <c r="CL27">
+        <v>220288</v>
+      </c>
+      <c r="CM27">
+        <v>229205</v>
+      </c>
+      <c r="CN27">
+        <v>17605</v>
+      </c>
+      <c r="CO27">
+        <v>40242</v>
+      </c>
+      <c r="CP27">
+        <v>38904</v>
+      </c>
+      <c r="CQ27">
+        <v>37015</v>
+      </c>
+      <c r="CR27">
+        <v>33379</v>
+      </c>
+      <c r="CS27">
+        <v>29516</v>
+      </c>
+      <c r="CT27">
+        <v>25226</v>
+      </c>
+      <c r="CU27">
+        <v>21531</v>
+      </c>
+      <c r="CV27">
+        <v>17855</v>
+      </c>
+      <c r="CW27">
+        <v>14052</v>
+      </c>
+      <c r="CX27">
+        <v>10258</v>
+      </c>
+      <c r="CY27">
+        <v>6782</v>
+      </c>
+      <c r="CZ27">
+        <v>4367</v>
+      </c>
+      <c r="DA27">
+        <v>2240</v>
+      </c>
+      <c r="DB27">
+        <v>1797</v>
+      </c>
+      <c r="DC27">
+        <v>263494</v>
+      </c>
+      <c r="DD27">
+        <v>772047</v>
+      </c>
+      <c r="DE27">
+        <v>914283</v>
+      </c>
+      <c r="DF27">
+        <v>925372</v>
+      </c>
+      <c r="DG27">
+        <v>920882</v>
+      </c>
+      <c r="DH27">
+        <v>838502</v>
+      </c>
+      <c r="DI27">
+        <v>719150</v>
+      </c>
+      <c r="DJ27">
+        <v>697764</v>
+      </c>
+      <c r="DK27">
+        <v>611222</v>
+      </c>
+      <c r="DL27">
+        <v>546115</v>
+      </c>
+      <c r="DM27">
+        <v>473259</v>
+      </c>
+      <c r="DN27">
+        <v>380466</v>
+      </c>
+      <c r="DO27">
+        <v>277201</v>
+      </c>
+      <c r="DP27">
+        <v>162901</v>
+      </c>
+      <c r="DQ27">
+        <v>147295</v>
+      </c>
+      <c r="DR27">
+        <v>75653</v>
+      </c>
+      <c r="DS27">
+        <v>183651</v>
+      </c>
+      <c r="DT27">
+        <v>176234</v>
+      </c>
+      <c r="DU27">
+        <v>173583</v>
+      </c>
+      <c r="DV27">
+        <v>161380</v>
+      </c>
+      <c r="DW27">
+        <v>140995</v>
+      </c>
+      <c r="DX27">
+        <v>124268</v>
+      </c>
+      <c r="DY27">
+        <v>102710</v>
+      </c>
+      <c r="DZ27">
+        <v>87629</v>
+      </c>
+      <c r="EA27">
+        <v>73494</v>
+      </c>
+      <c r="EB27">
+        <v>56541</v>
+      </c>
+      <c r="EC27">
+        <v>40803</v>
+      </c>
+      <c r="ED27">
+        <v>28210</v>
+      </c>
+      <c r="EE27">
+        <v>16753</v>
+      </c>
+      <c r="EF27">
+        <v>16429</v>
+      </c>
+      <c r="EG27">
+        <v>584460</v>
+      </c>
+      <c r="EH27">
+        <v>1482200</v>
+      </c>
+      <c r="EI27">
+        <v>1527009</v>
+      </c>
+      <c r="EJ27">
+        <v>1574718</v>
+      </c>
+      <c r="EK27">
+        <v>1558536</v>
+      </c>
+      <c r="EL27">
+        <v>1450132</v>
+      </c>
+      <c r="EM27">
+        <v>1349896</v>
+      </c>
+      <c r="EN27">
+        <v>1296989</v>
+      </c>
+      <c r="EO27">
+        <v>1301261</v>
+      </c>
+      <c r="EP27">
+        <v>1339400</v>
+      </c>
+      <c r="EQ27">
+        <v>1228252</v>
+      </c>
+      <c r="ER27">
+        <v>972261</v>
+      </c>
+      <c r="ES27">
+        <v>682636</v>
+      </c>
+      <c r="ET27">
+        <v>400558</v>
+      </c>
+      <c r="EU27">
+        <v>372439</v>
+      </c>
+      <c r="EV27">
+        <v>80009</v>
+      </c>
+      <c r="EW27">
+        <v>192075</v>
+      </c>
+      <c r="EX27">
+        <v>182363</v>
+      </c>
+      <c r="EY27">
+        <v>172120</v>
+      </c>
+      <c r="EZ27">
+        <v>154293</v>
+      </c>
+      <c r="FA27">
+        <v>134421</v>
+      </c>
+      <c r="FB27">
+        <v>113023</v>
+      </c>
+      <c r="FC27">
+        <v>92441</v>
+      </c>
+      <c r="FD27">
+        <v>78672</v>
+      </c>
+      <c r="FE27">
+        <v>64059</v>
+      </c>
+      <c r="FF27">
+        <v>48059</v>
+      </c>
+      <c r="FG27">
+        <v>33343</v>
+      </c>
+      <c r="FH27">
+        <v>20578</v>
+      </c>
+      <c r="FI27">
+        <v>11220</v>
+      </c>
+      <c r="FJ27">
+        <v>8834</v>
+      </c>
+      <c r="FK27">
+        <v>597588</v>
+      </c>
+      <c r="FL27">
+        <v>1486091</v>
+      </c>
+      <c r="FM27">
+        <v>1483141</v>
+      </c>
+      <c r="FN27">
+        <v>1464505</v>
+      </c>
+      <c r="FO27">
+        <v>1402384</v>
+      </c>
+      <c r="FP27">
+        <v>1279691</v>
+      </c>
+      <c r="FQ27">
+        <v>1184355</v>
+      </c>
+      <c r="FR27">
+        <v>1130004</v>
+      </c>
+      <c r="FS27">
+        <v>1116828</v>
+      </c>
+      <c r="FT27">
+        <v>1115543</v>
+      </c>
+      <c r="FU27">
+        <v>977121</v>
+      </c>
+      <c r="FV27">
+        <v>719321</v>
+      </c>
+      <c r="FW27">
+        <v>465304</v>
+      </c>
+      <c r="FX27">
+        <v>242183</v>
+      </c>
+      <c r="FY27">
+        <v>178417</v>
+      </c>
+      <c r="FZ27">
+        <v>4662</v>
+      </c>
+      <c r="GA27">
+        <v>11182</v>
+      </c>
+      <c r="GB27">
+        <v>10999</v>
+      </c>
+      <c r="GC27">
+        <v>9886</v>
+      </c>
+      <c r="GD27">
+        <v>9315</v>
+      </c>
+      <c r="GE27">
+        <v>8463</v>
+      </c>
+      <c r="GF27">
+        <v>7860</v>
+      </c>
+      <c r="GG27">
+        <v>6460</v>
+      </c>
+      <c r="GH27">
+        <v>5472</v>
+      </c>
+      <c r="GI27">
+        <v>4620</v>
+      </c>
+      <c r="GJ27">
+        <v>3301</v>
+      </c>
+      <c r="GK27">
+        <v>2375</v>
+      </c>
+      <c r="GL27">
+        <v>1436</v>
+      </c>
+      <c r="GM27">
+        <v>896</v>
+      </c>
+      <c r="GN27">
+        <v>851</v>
+      </c>
+      <c r="GO27">
+        <v>10048</v>
+      </c>
+      <c r="GP27">
+        <v>26344</v>
+      </c>
+      <c r="GQ27">
+        <v>28108</v>
+      </c>
+      <c r="GR27">
+        <v>27272</v>
+      </c>
+      <c r="GS27">
+        <v>26375</v>
+      </c>
+      <c r="GT27">
+        <v>24669</v>
+      </c>
+      <c r="GU27">
+        <v>21736</v>
+      </c>
+      <c r="GV27">
+        <v>19067</v>
+      </c>
+      <c r="GW27">
+        <v>18432</v>
+      </c>
+      <c r="GX27">
+        <v>17649</v>
+      </c>
+      <c r="GY27">
+        <v>14834</v>
+      </c>
+      <c r="GZ27">
+        <v>11307</v>
+      </c>
+      <c r="HA27">
+        <v>7738</v>
+      </c>
+      <c r="HB27">
+        <v>4485</v>
+      </c>
+      <c r="HC27">
+        <v>4248</v>
+      </c>
+      <c r="HD27">
+        <v>5038</v>
+      </c>
+      <c r="HE27">
+        <v>11846</v>
+      </c>
+      <c r="HF27">
+        <v>10950</v>
+      </c>
+      <c r="HG27">
+        <v>10059</v>
+      </c>
+      <c r="HH27">
+        <v>9381</v>
+      </c>
+      <c r="HI27">
+        <v>8513</v>
+      </c>
+      <c r="HJ27">
+        <v>7342</v>
+      </c>
+      <c r="HK27">
+        <v>6018</v>
+      </c>
+      <c r="HL27">
+        <v>5111</v>
+      </c>
+      <c r="HM27">
+        <v>4104</v>
+      </c>
+      <c r="HN27">
+        <v>2881</v>
+      </c>
+      <c r="HO27">
+        <v>1849</v>
+      </c>
+      <c r="HP27">
+        <v>1179</v>
+      </c>
+      <c r="HQ27">
+        <v>566</v>
+      </c>
+      <c r="HR27">
+        <v>505</v>
+      </c>
+      <c r="HS27">
+        <v>10117</v>
+      </c>
+      <c r="HT27">
+        <v>26759</v>
+      </c>
+      <c r="HU27">
+        <v>29015</v>
+      </c>
+      <c r="HV27">
+        <v>28192</v>
+      </c>
+      <c r="HW27">
+        <v>27078</v>
+      </c>
+      <c r="HX27">
+        <v>24491</v>
+      </c>
+      <c r="HY27">
+        <v>21695</v>
+      </c>
+      <c r="HZ27">
+        <v>18822</v>
+      </c>
+      <c r="IA27">
+        <v>17468</v>
+      </c>
+      <c r="IB27">
+        <v>16070</v>
+      </c>
+      <c r="IC27">
+        <v>13394</v>
+      </c>
+      <c r="ID27">
+        <v>9731</v>
+      </c>
+      <c r="IE27">
+        <v>6536</v>
+      </c>
+      <c r="IF27">
+        <v>3475</v>
+      </c>
+      <c r="IG27">
+        <v>2556</v>
+      </c>
+      <c r="IH27">
+        <v>88183</v>
+      </c>
+      <c r="II27">
+        <v>195692</v>
+      </c>
+      <c r="IJ27">
+        <v>162707</v>
+      </c>
+      <c r="IK27">
+        <v>149804</v>
+      </c>
+      <c r="IL27">
+        <v>133620</v>
+      </c>
+      <c r="IM27">
+        <v>117906</v>
+      </c>
+      <c r="IN27">
+        <v>102142</v>
+      </c>
+      <c r="IO27">
+        <v>82850</v>
+      </c>
+      <c r="IP27">
+        <v>69589</v>
+      </c>
+      <c r="IQ27">
+        <v>56617</v>
+      </c>
+      <c r="IR27">
+        <v>43768</v>
+      </c>
+      <c r="IS27">
+        <v>31029</v>
+      </c>
+      <c r="IT27">
+        <v>20920</v>
+      </c>
+      <c r="IU27">
+        <v>11912</v>
+      </c>
+      <c r="IV27">
+        <v>10338</v>
+      </c>
+      <c r="IW27">
+        <v>236876</v>
+      </c>
+      <c r="IX27">
+        <v>532939</v>
+      </c>
+      <c r="IY27">
+        <v>458720</v>
+      </c>
+      <c r="IZ27">
+        <v>419595</v>
+      </c>
+      <c r="JA27">
+        <v>382052</v>
+      </c>
+      <c r="JB27">
+        <v>338547</v>
+      </c>
+      <c r="JC27">
+        <v>296591</v>
+      </c>
+      <c r="JD27">
+        <v>270301</v>
+      </c>
+      <c r="JE27">
+        <v>253524</v>
+      </c>
+      <c r="JF27">
+        <v>249619</v>
+      </c>
+      <c r="JG27">
+        <v>217664</v>
+      </c>
+      <c r="JH27">
+        <v>163548</v>
+      </c>
+      <c r="JI27">
+        <v>117205</v>
+      </c>
+      <c r="JJ27">
+        <v>68128</v>
+      </c>
+      <c r="JK27">
+        <v>65616</v>
+      </c>
+      <c r="JL27">
+        <v>91919</v>
+      </c>
+      <c r="JM27">
+        <v>203690</v>
+      </c>
+      <c r="JN27">
+        <v>167043</v>
+      </c>
+      <c r="JO27">
+        <v>147597</v>
+      </c>
+      <c r="JP27">
+        <v>126757</v>
+      </c>
+      <c r="JQ27">
+        <v>110038</v>
+      </c>
+      <c r="JR27">
+        <v>93046</v>
+      </c>
+      <c r="JS27">
+        <v>74594</v>
+      </c>
+      <c r="JT27">
+        <v>60914</v>
+      </c>
+      <c r="JU27">
+        <v>48507</v>
+      </c>
+      <c r="JV27">
+        <v>35869</v>
+      </c>
+      <c r="JW27">
+        <v>23704</v>
+      </c>
+      <c r="JX27">
+        <v>14669</v>
+      </c>
+      <c r="JY27">
+        <v>7917</v>
+      </c>
+      <c r="JZ27">
+        <v>5871</v>
+      </c>
+      <c r="KA27">
+        <v>241150</v>
+      </c>
+      <c r="KB27">
+        <v>536635</v>
+      </c>
+      <c r="KC27">
+        <v>441513</v>
+      </c>
+      <c r="KD27">
+        <v>387109</v>
+      </c>
+      <c r="KE27">
+        <v>342099</v>
+      </c>
+      <c r="KF27">
+        <v>298979</v>
+      </c>
+      <c r="KG27">
+        <v>259982</v>
+      </c>
+      <c r="KH27">
+        <v>235942</v>
+      </c>
+      <c r="KI27">
+        <v>218198</v>
+      </c>
+      <c r="KJ27">
+        <v>210205</v>
+      </c>
+      <c r="KK27">
+        <v>181416</v>
+      </c>
+      <c r="KL27">
+        <v>131421</v>
+      </c>
+      <c r="KM27">
+        <v>90672</v>
+      </c>
+      <c r="KN27">
+        <v>49595</v>
+      </c>
+      <c r="KO27">
+        <v>41256</v>
+      </c>
+      <c r="KP27">
+        <v>923365</v>
+      </c>
+      <c r="KQ27">
+        <v>2287316</v>
+      </c>
+      <c r="KR27">
+        <v>2208999</v>
+      </c>
+      <c r="KS27">
+        <v>2113180</v>
+      </c>
+      <c r="KT27">
+        <v>1975375</v>
+      </c>
+      <c r="KU27">
+        <v>1891049</v>
+      </c>
+      <c r="KV27">
+        <v>1772909</v>
+      </c>
+      <c r="KW27">
+        <v>1637660</v>
+      </c>
+      <c r="KX27">
+        <v>1456189</v>
+      </c>
+      <c r="KY27">
+        <v>1280650</v>
+      </c>
+      <c r="KZ27">
+        <v>1036950</v>
+      </c>
+      <c r="LA27">
+        <v>790688</v>
+      </c>
+      <c r="LB27">
+        <v>575800</v>
+      </c>
+      <c r="LC27">
+        <v>368433</v>
+      </c>
+      <c r="LD27">
+        <v>369429</v>
+      </c>
+      <c r="LE27">
+        <v>2060030</v>
+      </c>
+      <c r="LF27">
+        <v>5370141</v>
+      </c>
+      <c r="LG27">
+        <v>5674907</v>
+      </c>
+      <c r="LH27">
+        <v>5787131</v>
+      </c>
+      <c r="LI27">
+        <v>6072683</v>
+      </c>
+      <c r="LJ27">
+        <v>5989769</v>
+      </c>
+      <c r="LK27">
+        <v>5576388</v>
+      </c>
+      <c r="LL27">
+        <v>5645699</v>
+      </c>
+      <c r="LM27">
+        <v>6215460</v>
+      </c>
+      <c r="LN27">
+        <v>7108136</v>
+      </c>
+      <c r="LO27">
+        <v>7185575</v>
+      </c>
+      <c r="LP27">
+        <v>6414616</v>
+      </c>
+      <c r="LQ27">
+        <v>5242259</v>
+      </c>
+      <c r="LR27">
+        <v>3383358</v>
+      </c>
+      <c r="LS27">
+        <v>3261714</v>
+      </c>
+      <c r="LT27">
+        <v>965056</v>
+      </c>
+      <c r="LU27">
+        <v>2384203</v>
+      </c>
+      <c r="LV27">
+        <v>2297098</v>
+      </c>
+      <c r="LW27">
+        <v>2182724</v>
+      </c>
+      <c r="LX27">
+        <v>2022671</v>
+      </c>
+      <c r="LY27">
+        <v>1885466</v>
+      </c>
+      <c r="LZ27">
+        <v>1727770</v>
+      </c>
+      <c r="MA27">
+        <v>1550008</v>
+      </c>
+      <c r="MB27">
+        <v>1384590</v>
+      </c>
+      <c r="MC27">
+        <v>1178615</v>
+      </c>
+      <c r="MD27">
+        <v>907047</v>
+      </c>
+      <c r="ME27">
+        <v>646900</v>
+      </c>
+      <c r="MF27">
+        <v>438170</v>
+      </c>
+      <c r="MG27">
+        <v>253896</v>
+      </c>
+      <c r="MH27">
+        <v>212599</v>
+      </c>
+      <c r="MI27">
+        <v>2152666</v>
+      </c>
+      <c r="MJ27">
+        <v>5506299</v>
+      </c>
+      <c r="MK27">
+        <v>5759326</v>
+      </c>
+      <c r="ML27">
+        <v>5881262</v>
+      </c>
+      <c r="MM27">
+        <v>6126534</v>
+      </c>
+      <c r="MN27">
+        <v>6041489</v>
+      </c>
+      <c r="MO27">
+        <v>5607431</v>
+      </c>
+      <c r="MP27">
+        <v>5635091</v>
+      </c>
+      <c r="MQ27">
+        <v>6082487</v>
+      </c>
+      <c r="MR27">
+        <v>6748921</v>
+      </c>
+      <c r="MS27">
+        <v>6610275</v>
+      </c>
+      <c r="MT27">
+        <v>5689947</v>
+      </c>
+      <c r="MU27">
+        <v>4458185</v>
+      </c>
+      <c r="MV27">
+        <v>2642333</v>
+      </c>
+      <c r="MW27">
+        <v>2042505</v>
       </c>
     </row>
   </sheetData>
